--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C5A974-B6A9-440A-8400-B6643FF0FD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385E9DFE-8BB2-4684-9766-5A1348276DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="559">
   <si>
     <t>Sales</t>
   </si>
@@ -3265,6 +3265,9 @@
   </si>
   <si>
     <t>TMT_01</t>
+  </si>
+  <si>
+    <t>CNY</t>
   </si>
 </sst>
 </file>
@@ -4989,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5436,7 +5439,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19755880386409505</v>
+        <v>0.2669054568882856</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5444,18 +5447,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>1-stage DCF Valuation Conclusion</v>
+        <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5471,7 +5474,7 @@
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -5485,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5499,7 +5502,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>308</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5509,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.97362534323128</v>
+        <v>145.40755585335478</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5559,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>65.062158966285907</v>
+        <v>76.32203477740272</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5574,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>80.585842383718784</v>
+        <v>94.699304050216128</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5589,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>98.989253156467655</v>
+        <v>116.50252679180015</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5604,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>111.35854885541431</v>
+        <v>131.16476124492209</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5628,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5655,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5673,7 +5676,7 @@
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -5681,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,7 +5702,7 @@
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -5708,21 +5711,21 @@
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
-        <v>-202343.60953731713</v>
+        <v>-191101</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,17 +5737,17 @@
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5756,7 +5759,7 @@
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
@@ -5771,7 +5774,7 @@
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
@@ -5786,7 +5789,7 @@
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -5800,21 +5803,21 @@
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
-        <v>-174.26602854031819</v>
+        <v>-193.8560225780364</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,11 +5829,11 @@
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,26 +5851,26 @@
       </c>
       <c r="D55" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5879,7 +5882,7 @@
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -5888,11 +5891,11 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -5901,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4645150639706004E-2</v>
+        <v>8.3590084922278637E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5918,7 +5921,7 @@
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.83976961030735076</v>
+        <v>0.83989502603092137</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5938,7 +5941,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.11683147612363115</v>
+        <v>0.1141273682688253</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5952,7 +5955,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -6002,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6027,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6046,7 +6049,7 @@
       </c>
       <c r="D78" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -6056,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.2473398407265082</v>
+        <v>-4.7570206216136892</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6103,7 +6106,7 @@
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -6117,7 +6120,7 @@
       </c>
       <c r="D85" s="339" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -6127,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.0004263853340207</v>
+        <v>4.4804775515741033</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6154,7 +6157,7 @@
       </c>
       <c r="D89" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -6164,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.129284893283694</v>
+        <v>13.58479908047774</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6181,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>11.882371437891207</v>
+        <v>13.308256010438154</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6202,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6276,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2888383928647593</v>
+        <v>1.4434990000085306</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6317,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6325,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6366,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>174.87 HKD</v>
+        <v>210.19 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6374,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-8.259842144731383E-2</v>
+        <v>-8.8130818492621346E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6388,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>129.44 HKD</v>
+        <v>155.6 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6396,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.7909396933599855E-2</v>
+        <v>1.1115382217860131E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6410,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>112.96 HKD</v>
+        <v>135.78 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6418,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>6.7183407407964899E-2</v>
+        <v>5.9758693681778934E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6432,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>99.52 HKD</v>
+        <v>119.61 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6440,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.1153011584223788</v>
+        <v>0.1072641851985464</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6454,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>88.51 HKD</v>
+        <v>106.34 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6462,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.16195220096387539</v>
+        <v>0.15333444846924818</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6480,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.97362534323128</v>
+        <v>145.40755585335478</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6507,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6587,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.748214443885395</v>
+        <v>67.008090255002216</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>65.062158966285907</v>
+        <v>76.32203477740272</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6608,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.876462292119172</v>
+        <v>83.989923958616515</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>80.585842383718784</v>
+        <v>94.699304050216128</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6655,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.709103245439934</v>
+        <v>104.22237688077243</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>98.989253156467655</v>
+        <v>116.50252679180015</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6676,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.061558949103656</v>
+        <v>117.86777133861143</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>111.35854885541431</v>
+        <v>131.16476124492209</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6698,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6741,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6755,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6794,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6810,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6860,50 +6863,50 @@
     <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="101">
-        <v>45747</v>
+        <v>45657</v>
       </c>
       <c r="D1" s="36">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="E1" s="36">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="F1" s="36">
         <f t="shared" si="0"/>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="G1" s="36">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="H1" s="36">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="I1" s="36">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="J1" s="36">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="K1" s="36">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="L1" s="36">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="M1" s="36">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9">
@@ -6940,8 +6943,12 @@
       <c r="D4" s="287">
         <v>1009309</v>
       </c>
-      <c r="E4" s="287"/>
-      <c r="F4" s="287"/>
+      <c r="E4" s="287">
+        <v>937259</v>
+      </c>
+      <c r="F4" s="287">
+        <v>848258</v>
+      </c>
       <c r="G4" s="287"/>
       <c r="H4" s="287"/>
       <c r="I4" s="287"/>
@@ -6962,8 +6969,14 @@
         <f>268895+207132+144333</f>
         <v>620360</v>
       </c>
-      <c r="E5" s="287"/>
-      <c r="F5" s="287"/>
+      <c r="E5" s="287">
+        <f>254182+200077+130157</f>
+        <v>584416</v>
+      </c>
+      <c r="F5" s="287">
+        <f>225010+193045+118680</f>
+        <v>536735</v>
+      </c>
       <c r="G5" s="287"/>
       <c r="H5" s="287"/>
       <c r="I5" s="287"/>
@@ -6984,8 +6997,14 @@
         <f>D7+59319</f>
         <v>254603</v>
       </c>
-      <c r="E6" s="287"/>
-      <c r="F6" s="287"/>
+      <c r="E6" s="287">
+        <f>51409+E7</f>
+        <v>223744</v>
+      </c>
+      <c r="F6" s="287">
+        <f>49234+F7</f>
+        <v>194551</v>
+      </c>
       <c r="G6" s="287"/>
       <c r="H6" s="287"/>
       <c r="I6" s="287"/>
@@ -7006,8 +7025,14 @@
         <f>52477+142807</f>
         <v>195284</v>
       </c>
-      <c r="E7" s="288"/>
-      <c r="F7" s="288"/>
+      <c r="E7" s="288">
+        <f>49592+122743</f>
+        <v>172335</v>
+      </c>
+      <c r="F7" s="288">
+        <f>96083+49234</f>
+        <v>145317</v>
+      </c>
       <c r="G7" s="288"/>
       <c r="H7" s="288"/>
       <c r="I7" s="288"/>
@@ -7042,8 +7067,12 @@
       <c r="D9" s="287">
         <v>8958</v>
       </c>
-      <c r="E9" s="287"/>
-      <c r="F9" s="287"/>
+      <c r="E9" s="287">
+        <v>10986</v>
+      </c>
+      <c r="F9" s="287">
+        <v>11914</v>
+      </c>
       <c r="G9" s="287"/>
       <c r="H9" s="287"/>
       <c r="I9" s="287"/>
@@ -7094,8 +7123,12 @@
       <c r="D12" s="287">
         <v>3730</v>
       </c>
-      <c r="E12" s="287"/>
-      <c r="F12" s="287"/>
+      <c r="E12" s="287">
+        <v>2330</v>
+      </c>
+      <c r="F12" s="287">
+        <v>2679</v>
+      </c>
       <c r="G12" s="287"/>
       <c r="H12" s="287"/>
       <c r="I12" s="287"/>
@@ -7114,8 +7147,12 @@
       <c r="D13" s="287">
         <v>21134</v>
       </c>
-      <c r="E13" s="287"/>
-      <c r="F13" s="287"/>
+      <c r="E13" s="287">
+        <v>15729</v>
+      </c>
+      <c r="F13" s="287">
+        <v>16729</v>
+      </c>
       <c r="G13" s="287"/>
       <c r="H13" s="287"/>
       <c r="I13" s="287"/>
@@ -7134,8 +7171,12 @@
       <c r="D14" s="287">
         <v>38596</v>
       </c>
-      <c r="E14" s="287"/>
-      <c r="F14" s="287"/>
+      <c r="E14" s="287">
+        <v>37278</v>
+      </c>
+      <c r="F14" s="287">
+        <v>35878</v>
+      </c>
       <c r="G14" s="287"/>
       <c r="H14" s="287"/>
       <c r="I14" s="287"/>
@@ -7154,8 +7195,12 @@
       <c r="D15" s="289">
         <v>131935</v>
       </c>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
+      <c r="E15" s="289">
+        <v>125594</v>
+      </c>
+      <c r="F15" s="289">
+        <v>116306</v>
+      </c>
       <c r="G15" s="289"/>
       <c r="H15" s="289"/>
       <c r="I15" s="289"/>
@@ -7174,8 +7219,12 @@
       <c r="D16" s="287">
         <v>169</v>
       </c>
-      <c r="E16" s="287"/>
-      <c r="F16" s="287"/>
+      <c r="E16" s="287">
+        <v>135</v>
+      </c>
+      <c r="F16" s="287">
+        <v>158</v>
+      </c>
       <c r="G16" s="287"/>
       <c r="H16" s="287"/>
       <c r="I16" s="287"/>
@@ -7200,8 +7249,12 @@
       <c r="D19" s="287">
         <v>207132</v>
       </c>
-      <c r="E19" s="287"/>
-      <c r="F19" s="287"/>
+      <c r="E19" s="287">
+        <v>200077</v>
+      </c>
+      <c r="F19" s="287">
+        <v>193045</v>
+      </c>
       <c r="G19" s="287"/>
       <c r="H19" s="287"/>
       <c r="I19" s="287"/>
@@ -7252,8 +7305,12 @@
       <c r="D22" s="287">
         <v>361933</v>
       </c>
-      <c r="E22" s="287"/>
-      <c r="F22" s="287"/>
+      <c r="E22" s="287">
+        <v>280750</v>
+      </c>
+      <c r="F22" s="287">
+        <v>314764</v>
+      </c>
       <c r="G22" s="287"/>
       <c r="H22" s="287"/>
       <c r="I22" s="287"/>
@@ -7272,8 +7329,12 @@
       <c r="D23" s="287">
         <v>-205699</v>
       </c>
-      <c r="E23" s="287"/>
-      <c r="F23" s="287"/>
+      <c r="E23" s="287">
+        <v>-238053</v>
+      </c>
+      <c r="F23" s="287">
+        <v>-238296</v>
+      </c>
       <c r="G23" s="287"/>
       <c r="H23" s="287"/>
       <c r="I23" s="287"/>
@@ -7292,8 +7353,12 @@
       <c r="D24" s="287">
         <v>-123843</v>
       </c>
-      <c r="E24" s="287"/>
-      <c r="F24" s="287"/>
+      <c r="E24" s="287">
+        <v>-120514</v>
+      </c>
+      <c r="F24" s="287">
+        <v>-45201</v>
+      </c>
       <c r="G24" s="287"/>
       <c r="H24" s="287"/>
       <c r="I24" s="287"/>
@@ -7347,9 +7412,18 @@
         <f>BS!C4</f>
         <v>125999</v>
       </c>
-      <c r="D28" s="287"/>
-      <c r="E28" s="287"/>
-      <c r="F28" s="287"/>
+      <c r="D28" s="287">
+        <f>54881+12342+1205</f>
+        <v>68428</v>
+      </c>
+      <c r="E28" s="287">
+        <f>40245+12838+2537</f>
+        <v>55620</v>
+      </c>
+      <c r="F28" s="287">
+        <f>34668+10137+2612</f>
+        <v>47417</v>
+      </c>
       <c r="G28" s="287"/>
       <c r="H28" s="287"/>
       <c r="I28" s="287"/>
@@ -7366,9 +7440,15 @@
         <f>BS!C6</f>
         <v>11378</v>
       </c>
-      <c r="D29" s="287"/>
-      <c r="E29" s="287"/>
-      <c r="F29" s="287"/>
+      <c r="D29" s="287">
+        <v>12026</v>
+      </c>
+      <c r="E29" s="287">
+        <v>11696</v>
+      </c>
+      <c r="F29" s="287">
+        <v>10203</v>
+      </c>
       <c r="G29" s="287"/>
       <c r="H29" s="287"/>
       <c r="I29" s="287"/>
@@ -7385,9 +7465,15 @@
         <f>BS!C33+BS!C42</f>
         <v>693546</v>
       </c>
-      <c r="D30" s="289"/>
-      <c r="E30" s="289"/>
-      <c r="F30" s="289"/>
+      <c r="D30" s="289">
+        <v>646672</v>
+      </c>
+      <c r="E30" s="289">
+        <v>634115</v>
+      </c>
+      <c r="F30" s="289">
+        <v>631035</v>
+      </c>
       <c r="G30" s="289"/>
       <c r="H30" s="289"/>
       <c r="I30" s="289"/>
@@ -7404,9 +7490,15 @@
         <f>BS!G27</f>
         <v>1434194</v>
       </c>
-      <c r="D31" s="289"/>
-      <c r="E31" s="289"/>
-      <c r="F31" s="289"/>
+      <c r="D31" s="289">
+        <v>1345985</v>
+      </c>
+      <c r="E31" s="289">
+        <v>1301423</v>
+      </c>
+      <c r="F31" s="289">
+        <v>1210292</v>
+      </c>
       <c r="G31" s="289"/>
       <c r="H31" s="289"/>
       <c r="I31" s="289"/>
@@ -7423,9 +7515,15 @@
         <f>BS!G28</f>
         <v>4523</v>
       </c>
-      <c r="D32" s="287"/>
-      <c r="E32" s="287"/>
-      <c r="F32" s="287"/>
+      <c r="D32" s="287">
+        <v>4253</v>
+      </c>
+      <c r="E32" s="287">
+        <v>4075</v>
+      </c>
+      <c r="F32" s="287">
+        <v>3942</v>
+      </c>
       <c r="G32" s="287"/>
       <c r="H32" s="287"/>
       <c r="I32" s="287"/>
@@ -7467,13 +7565,13 @@
         <f t="shared" si="1"/>
         <v>1009309</v>
       </c>
-      <c r="E36" s="270" t="str">
+      <c r="E36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="270" t="str">
+        <v>937259</v>
+      </c>
+      <c r="F36" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>848258</v>
       </c>
       <c r="G36" s="270" t="str">
         <f t="shared" si="1"/>
@@ -7516,13 +7614,13 @@
         <f t="shared" si="2"/>
         <v>-620360</v>
       </c>
-      <c r="E37" s="270" t="str">
+      <c r="E37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F37" s="270" t="str">
+        <v>-584416</v>
+      </c>
+      <c r="F37" s="270">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-536735</v>
       </c>
       <c r="G37" s="270" t="str">
         <f t="shared" si="2"/>
@@ -7565,13 +7663,13 @@
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>388949</v>
       </c>
-      <c r="E38" s="267" t="str">
+      <c r="E38" s="267">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="267" t="str">
+        <v>352843</v>
+      </c>
+      <c r="F38" s="267">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v/>
+        <v>311523</v>
       </c>
       <c r="G38" s="267" t="str">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
@@ -7614,13 +7712,13 @@
         <f t="shared" si="13"/>
         <v>-254603</v>
       </c>
-      <c r="E39" s="270" t="str">
+      <c r="E39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="F39" s="270" t="str">
+        <v>-223744</v>
+      </c>
+      <c r="F39" s="270">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-194551</v>
       </c>
       <c r="G39" s="270" t="str">
         <f t="shared" si="13"/>
@@ -7663,13 +7761,13 @@
         <f t="shared" si="14"/>
         <v>-195284</v>
       </c>
-      <c r="E40" s="282" t="str">
+      <c r="E40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F40" s="282" t="str">
+        <v>-172335</v>
+      </c>
+      <c r="F40" s="282">
         <f t="shared" si="14"/>
-        <v/>
+        <v>-145317</v>
       </c>
       <c r="G40" s="282" t="str">
         <f t="shared" si="14"/>
@@ -7712,13 +7810,13 @@
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-59319</v>
       </c>
-      <c r="E41" s="282" t="str">
+      <c r="E41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="F41" s="282" t="str">
+        <v>-51409</v>
+      </c>
+      <c r="F41" s="282">
         <f t="shared" si="15"/>
-        <v/>
+        <v>-49234</v>
       </c>
       <c r="G41" s="282" t="str">
         <f t="shared" si="15"/>
@@ -7761,13 +7859,13 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="270" t="str">
+      <c r="E42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F42" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="F42" s="270">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="270" t="str">
         <f t="shared" si="16"/>
@@ -7810,13 +7908,13 @@
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>134346</v>
       </c>
-      <c r="E43" s="271" t="str">
+      <c r="E43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F43" s="271" t="str">
+        <v>129099</v>
+      </c>
+      <c r="F43" s="271">
         <f t="shared" si="17"/>
-        <v/>
+        <v>116972</v>
       </c>
       <c r="G43" s="271" t="str">
         <f t="shared" si="17"/>
@@ -7859,13 +7957,13 @@
         <f t="shared" si="18"/>
         <v>18781</v>
       </c>
-      <c r="E44" s="290" t="str">
+      <c r="E44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="F44" s="290" t="str">
+        <v>20374</v>
+      </c>
+      <c r="F44" s="290">
         <f t="shared" si="18"/>
-        <v/>
+        <v>21162</v>
       </c>
       <c r="G44" s="290" t="str">
         <f t="shared" si="18"/>
@@ -7908,13 +8006,13 @@
         <f t="shared" si="19"/>
         <v>17404</v>
       </c>
-      <c r="E45" s="285" t="str">
+      <c r="E45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="F45" s="285" t="str">
+        <v>13399</v>
+      </c>
+      <c r="F45" s="285">
         <f t="shared" si="19"/>
-        <v/>
+        <v>14050</v>
       </c>
       <c r="G45" s="285" t="str">
         <f t="shared" si="19"/>
@@ -7957,13 +8055,13 @@
         <f t="shared" ref="D46:M46" si="20">IF(D$4="","",-D14)</f>
         <v>-38596</v>
       </c>
-      <c r="E46" s="270" t="str">
+      <c r="E46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="F46" s="270" t="str">
+        <v>-37278</v>
+      </c>
+      <c r="F46" s="270">
         <f t="shared" si="20"/>
-        <v/>
+        <v>-35878</v>
       </c>
       <c r="G46" s="270" t="str">
         <f t="shared" si="20"/>
@@ -8006,13 +8104,13 @@
         <f t="shared" si="21"/>
         <v>131935</v>
       </c>
-      <c r="E47" s="271" t="str">
+      <c r="E47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="F47" s="271" t="str">
+        <v>125594</v>
+      </c>
+      <c r="F47" s="271">
         <f t="shared" si="21"/>
-        <v/>
+        <v>116306</v>
       </c>
       <c r="G47" s="271" t="str">
         <f t="shared" si="21"/>
@@ -8055,13 +8153,13 @@
         <f t="shared" si="22"/>
         <v>-169</v>
       </c>
-      <c r="E48" s="270" t="str">
+      <c r="E48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="F48" s="270" t="str">
+        <v>-135</v>
+      </c>
+      <c r="F48" s="270">
         <f t="shared" si="22"/>
-        <v/>
+        <v>-158</v>
       </c>
       <c r="G48" s="270" t="str">
         <f t="shared" si="22"/>
@@ -8109,13 +8207,13 @@
         <f t="shared" si="23"/>
         <v>-3730</v>
       </c>
-      <c r="E51" s="270" t="str">
+      <c r="E51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="F51" s="270" t="str">
+        <v>-2330</v>
+      </c>
+      <c r="F51" s="270">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-2679</v>
       </c>
       <c r="G51" s="270" t="str">
         <f t="shared" si="23"/>
@@ -8158,13 +8256,13 @@
         <f t="shared" ref="D52:M52" si="24">IF(D$4="","",D13)</f>
         <v>21134</v>
       </c>
-      <c r="E52" s="270" t="str">
+      <c r="E52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="F52" s="270" t="str">
+        <v>15729</v>
+      </c>
+      <c r="F52" s="270">
         <f t="shared" si="24"/>
-        <v/>
+        <v>16729</v>
       </c>
       <c r="G52" s="270" t="str">
         <f t="shared" si="24"/>
@@ -8212,13 +8310,13 @@
         <f t="shared" si="25"/>
         <v>8958</v>
       </c>
-      <c r="E55" s="285" t="str">
+      <c r="E55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="F55" s="285" t="str">
+        <v>10986</v>
+      </c>
+      <c r="F55" s="285">
         <f t="shared" si="25"/>
-        <v/>
+        <v>11914</v>
       </c>
       <c r="G55" s="285" t="str">
         <f t="shared" si="25"/>
@@ -8261,13 +8359,13 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="285" t="str">
+      <c r="E56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="F56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="F56" s="285">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="285" t="str">
         <f t="shared" si="26"/>
@@ -8310,13 +8408,13 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="E57" s="285" t="str">
+      <c r="E57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="F57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="F57" s="285">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G57" s="285" t="str">
         <f t="shared" si="27"/>
@@ -8359,13 +8457,13 @@
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>9823</v>
       </c>
-      <c r="E58" s="285" t="str">
+      <c r="E58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="F58" s="285" t="str">
+        <v>9388</v>
+      </c>
+      <c r="F58" s="285">
         <f t="shared" si="28"/>
-        <v/>
+        <v>9248</v>
       </c>
       <c r="G58" s="285" t="str">
         <f t="shared" si="28"/>
@@ -8414,13 +8512,13 @@
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-207132</v>
       </c>
-      <c r="E61" s="270" t="str">
+      <c r="E61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="F61" s="270" t="str">
+        <v>-200077</v>
+      </c>
+      <c r="F61" s="270">
         <f t="shared" si="29"/>
-        <v/>
+        <v>-193045</v>
       </c>
       <c r="G61" s="270" t="str">
         <f t="shared" si="29"/>
@@ -8463,13 +8561,13 @@
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-207132</v>
       </c>
-      <c r="E62" s="270" t="str">
+      <c r="E62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="F62" s="270" t="str">
+        <v>-200077</v>
+      </c>
+      <c r="F62" s="270">
         <f t="shared" si="30"/>
-        <v/>
+        <v>-193045</v>
       </c>
       <c r="G62" s="270" t="str">
         <f t="shared" si="30"/>
@@ -8512,13 +8610,13 @@
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="270" t="str">
+      <c r="E63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="F63" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="F63" s="270">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G63" s="270" t="str">
         <f t="shared" si="31"/>
@@ -8561,13 +8659,13 @@
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>32391</v>
       </c>
-      <c r="E64" s="270" t="str">
+      <c r="E64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="F64" s="270" t="str">
+        <v>-77817</v>
+      </c>
+      <c r="F64" s="270">
         <f t="shared" si="32"/>
-        <v/>
+        <v>31267</v>
       </c>
       <c r="G64" s="270" t="str">
         <f t="shared" si="32"/>
@@ -8610,13 +8708,13 @@
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
         <v>4.83</v>
       </c>
-      <c r="E65" s="70" t="str">
+      <c r="E65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="F65" s="70" t="str">
+        <v>4.41</v>
+      </c>
+      <c r="F65" s="70">
         <f t="shared" si="33"/>
-        <v/>
+        <v>4.0600000000000005</v>
       </c>
       <c r="G65" s="70" t="str">
         <f t="shared" si="33"/>
@@ -8661,13 +8759,13 @@
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>3.115993219123192E-2</v>
       </c>
-      <c r="D68" s="89" t="str">
+      <c r="D68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="E68" s="89" t="str">
+        <v>7.687309484358118E-2</v>
+      </c>
+      <c r="E68" s="89">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0.10492208738379127</v>
       </c>
       <c r="F68" s="89" t="str">
         <f t="shared" si="34"/>
@@ -8710,13 +8808,13 @@
         <f>IF(D$36="","",C38/D38-1)</f>
         <v>6.5365896300028981E-2</v>
       </c>
-      <c r="D69" s="89" t="str">
+      <c r="D69" s="89">
         <f t="shared" ref="D69:M69" si="35">IF(E$36="","",D38/E38-1)</f>
-        <v/>
-      </c>
-      <c r="E69" s="89" t="str">
+        <v>0.10232879779391957</v>
+      </c>
+      <c r="E69" s="89">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.13263868157407321</v>
       </c>
       <c r="F69" s="89" t="str">
         <f t="shared" si="35"/>
@@ -8760,13 +8858,13 @@
         <f>IF(D$36="","",C43/D43-1)</f>
         <v>6.1363940869099132E-2</v>
       </c>
-      <c r="D70" s="98" t="str">
+      <c r="D70" s="98">
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
-        <v/>
-      </c>
-      <c r="E70" s="98" t="str">
+        <v>4.0643227290683814E-2</v>
+      </c>
+      <c r="E70" s="98">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0.10367438361317238</v>
       </c>
       <c r="F70" s="98" t="str">
         <f t="shared" si="36"/>
@@ -8809,13 +8907,13 @@
         <f>IF(D$36="","",C44/D44-1)</f>
         <v>-0.14450774719131032</v>
       </c>
-      <c r="D71" s="98" t="str">
+      <c r="D71" s="98">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
-        <v/>
-      </c>
-      <c r="E71" s="98" t="str">
+        <v>-7.8187886522037897E-2</v>
+      </c>
+      <c r="E71" s="98">
         <f t="shared" si="37"/>
-        <v/>
+        <v>-3.7236556091106654E-2</v>
       </c>
       <c r="F71" s="98" t="str">
         <f t="shared" si="37"/>
@@ -8859,13 +8957,13 @@
         <f>IF(D$36="","",C47/D47-1)</f>
         <v>4.9956417933073149E-2</v>
       </c>
-      <c r="D72" s="98" t="str">
+      <c r="D72" s="98">
         <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D47/E47-1)</f>
-        <v/>
-      </c>
-      <c r="E72" s="98" t="str">
+        <v>5.0488080640795019E-2</v>
+      </c>
+      <c r="E72" s="98">
         <f t="shared" si="38"/>
-        <v/>
+        <v>7.9858304816604386E-2</v>
       </c>
       <c r="F72" s="98" t="str">
         <f t="shared" si="38"/>
@@ -8932,15 +9030,15 @@
       </c>
       <c r="D76" s="285">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="285" t="str">
+        <v>1992657</v>
+      </c>
+      <c r="E76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="F76" s="285" t="str">
+        <v>1935538</v>
+      </c>
+      <c r="F76" s="285">
         <f t="shared" si="39"/>
-        <v/>
+        <v>1841327</v>
       </c>
       <c r="G76" s="285" t="str">
         <f t="shared" si="39"/>
@@ -8981,15 +9079,15 @@
       </c>
       <c r="D77" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="E77" s="282" t="str">
+        <v>68428</v>
+      </c>
+      <c r="E77" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="F77" s="282" t="str">
+        <v>55620</v>
+      </c>
+      <c r="F77" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>47417</v>
       </c>
       <c r="G77" s="282" t="str">
         <f t="shared" si="40"/>
@@ -9015,15 +9113,15 @@
       </c>
       <c r="D78" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="E78" s="282" t="str">
+        <v>12026</v>
+      </c>
+      <c r="E78" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="F78" s="282" t="str">
+        <v>11696</v>
+      </c>
+      <c r="F78" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>10203</v>
       </c>
       <c r="G78" s="282" t="str">
         <f t="shared" si="40"/>
@@ -9049,15 +9147,15 @@
       </c>
       <c r="D79" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="E79" s="270" t="str">
+        <v>646672</v>
+      </c>
+      <c r="E79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="F79" s="270" t="str">
+        <v>634115</v>
+      </c>
+      <c r="F79" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>631035</v>
       </c>
       <c r="G79" s="270" t="str">
         <f t="shared" si="41"/>
@@ -9098,15 +9196,15 @@
       </c>
       <c r="D80" s="270">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="E80" s="270" t="str">
+        <v>1345985</v>
+      </c>
+      <c r="E80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="F80" s="270" t="str">
+        <v>1301423</v>
+      </c>
+      <c r="F80" s="270">
         <f t="shared" si="42"/>
-        <v/>
+        <v>1210292</v>
       </c>
       <c r="G80" s="270" t="str">
         <f t="shared" si="42"/>
@@ -9154,7 +9252,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9968,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>66.052066717044198</v>
+        <v>73.978314723089511</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2888383928647593</v>
+        <v>1.4434990000085306</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10378,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-91932</v>
+        <v>-102963.84000000001</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.2473398407265082</v>
+        <v>-4.7570206216136892</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10395,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>86587.65539082</v>
+        <v>96978.174037718403</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>4.0004263853340207</v>
+        <v>4.4804775515741033</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10412,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>262533.59999999998</v>
+        <v>294037.63199999998</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>12.129284893283694</v>
+        <v>13.58479908047774</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10429,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>257189.25539081998</v>
+        <v>288051.96603771835</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>11.882371437891207</v>
+        <v>13.308256010438154</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10475,7 +10573,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="50" t="s">
         <v>54</v>
@@ -10485,47 +10583,47 @@
       <c r="F1" s="50"/>
       <c r="G1" s="36">
         <f>Data!C1</f>
-        <v>45747</v>
+        <v>45657</v>
       </c>
       <c r="H1" s="36">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="I1" s="36">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="J1" s="36">
         <f t="shared" si="0"/>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="K1" s="36">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="L1" s="36">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="M1" s="36">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="N1" s="36">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="O1" s="36">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="P1" s="36">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="Q1" s="36">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
@@ -10591,13 +10689,13 @@
         <f>Data!D36</f>
         <v>1009309</v>
       </c>
-      <c r="I4" s="270" t="str">
+      <c r="I4" s="270">
         <f>Data!E36</f>
-        <v/>
-      </c>
-      <c r="J4" s="270" t="str">
+        <v>937259</v>
+      </c>
+      <c r="J4" s="270">
         <f>Data!F36</f>
-        <v/>
+        <v>848258</v>
       </c>
       <c r="K4" s="270" t="str">
         <f>Data!G36</f>
@@ -10646,13 +10744,13 @@
         <f t="shared" si="1"/>
         <v>-815644</v>
       </c>
-      <c r="I5" s="270" t="str">
+      <c r="I5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J5" s="270" t="str">
+        <v>-756751</v>
+      </c>
+      <c r="J5" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-682052</v>
       </c>
       <c r="K5" s="270" t="str">
         <f t="shared" si="1"/>
@@ -10701,13 +10799,13 @@
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>193665</v>
       </c>
-      <c r="I6" s="267" t="str">
+      <c r="I6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J6" s="267" t="str">
+        <v>180508</v>
+      </c>
+      <c r="J6" s="267">
         <f t="shared" si="2"/>
-        <v/>
+        <v>166206</v>
       </c>
       <c r="K6" s="267" t="str">
         <f t="shared" si="2"/>
@@ -10756,13 +10854,13 @@
         <f t="shared" si="3"/>
         <v>-59319</v>
       </c>
-      <c r="I7" s="266" t="str">
+      <c r="I7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J7" s="266" t="str">
+        <v>-51409</v>
+      </c>
+      <c r="J7" s="266">
         <f t="shared" si="3"/>
-        <v/>
+        <v>-49234</v>
       </c>
       <c r="K7" s="266" t="str">
         <f t="shared" si="3"/>
@@ -10813,13 +10911,13 @@
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>134346</v>
       </c>
-      <c r="I8" s="267" t="str">
+      <c r="I8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J8" s="267" t="str">
+        <v>129099</v>
+      </c>
+      <c r="J8" s="267">
         <f t="shared" si="4"/>
-        <v/>
+        <v>116972</v>
       </c>
       <c r="K8" s="267" t="str">
         <f t="shared" si="4"/>
@@ -10870,13 +10968,13 @@
         <f t="shared" ref="H9:Q9" si="5">H59</f>
         <v>8958</v>
       </c>
-      <c r="I9" s="270" t="str">
+      <c r="I9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J9" s="270" t="str">
+        <v>10986</v>
+      </c>
+      <c r="J9" s="270">
         <f t="shared" si="5"/>
-        <v/>
+        <v>11914</v>
       </c>
       <c r="K9" s="270" t="str">
         <f t="shared" si="5"/>
@@ -10925,13 +11023,13 @@
         <f t="shared" ref="H10:Q10" si="6">H48</f>
         <v>10130.138577182464</v>
       </c>
-      <c r="I10" s="266" t="str">
+      <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J10" s="266" t="str">
+        <v>7985.4215804155847</v>
+      </c>
+      <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v/>
+        <v>8292.2434114547868</v>
       </c>
       <c r="K10" s="266" t="str">
         <f t="shared" si="6"/>
@@ -10980,13 +11078,13 @@
         <f t="shared" si="7"/>
         <v>153434.13857718246</v>
       </c>
-      <c r="I11" s="267" t="str">
+      <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J11" s="267" t="str">
+        <v>148070.4215804156</v>
+      </c>
+      <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v/>
+        <v>137178.24341145478</v>
       </c>
       <c r="K11" s="267" t="str">
         <f t="shared" si="7"/>
@@ -11035,13 +11133,13 @@
         <f>Data!D46</f>
         <v>-38596</v>
       </c>
-      <c r="I12" s="266" t="str">
+      <c r="I12" s="266">
         <f>Data!E46</f>
-        <v/>
-      </c>
-      <c r="J12" s="266" t="str">
+        <v>-37278</v>
+      </c>
+      <c r="J12" s="266">
         <f>Data!F46</f>
-        <v/>
+        <v>-35878</v>
       </c>
       <c r="K12" s="266" t="str">
         <f>Data!G46</f>
@@ -11079,7 +11177,7 @@
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
-        <v>-174.26602854031819</v>
+        <v>-193.8560225780364</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="242"/>
@@ -11092,13 +11190,13 @@
         <f>Data!D48</f>
         <v>-169</v>
       </c>
-      <c r="I13" s="270" t="str">
+      <c r="I13" s="270">
         <f>Data!E48</f>
-        <v/>
-      </c>
-      <c r="J13" s="270" t="str">
+        <v>-135</v>
+      </c>
+      <c r="J13" s="270">
         <f>Data!F48</f>
-        <v/>
+        <v>-158</v>
       </c>
       <c r="K13" s="270" t="str">
         <f>Data!G48</f>
@@ -11136,7 +11234,7 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
@@ -11149,13 +11247,13 @@
         <f t="shared" si="8"/>
         <v>114669.13857718246</v>
       </c>
-      <c r="I14" s="267" t="str">
+      <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J14" s="267" t="str">
+        <v>110657.4215804156</v>
+      </c>
+      <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v/>
+        <v>101142.24341145478</v>
       </c>
       <c r="K14" s="267" t="str">
         <f t="shared" si="8"/>
@@ -11204,13 +11302,13 @@
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>207132</v>
       </c>
-      <c r="I15" s="266" t="str">
+      <c r="I15" s="266">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v/>
-      </c>
-      <c r="J15" s="266" t="str">
+        <v>200077</v>
+      </c>
+      <c r="J15" s="266">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v/>
+        <v>193045</v>
       </c>
       <c r="K15" s="266" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
@@ -11248,7 +11346,7 @@
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
-        <v>-202343.60953731713</v>
+        <v>-191101</v>
       </c>
       <c r="E16" s="237"/>
       <c r="G16" s="266">
@@ -11259,13 +11357,13 @@
         <f>Data!D62</f>
         <v>-207132</v>
       </c>
-      <c r="I16" s="266" t="str">
+      <c r="I16" s="266">
         <f>Data!E62</f>
-        <v/>
-      </c>
-      <c r="J16" s="266" t="str">
+        <v>-200077</v>
+      </c>
+      <c r="J16" s="266">
         <f>Data!F62</f>
-        <v/>
+        <v>-193045</v>
       </c>
       <c r="K16" s="266" t="str">
         <f>Data!G62</f>
@@ -11354,7 +11452,7 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -11367,13 +11465,13 @@
         <f t="shared" si="9"/>
         <v>114669.13857718246</v>
       </c>
-      <c r="I19" s="271" t="str">
+      <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="J19" s="271" t="str">
+        <v>110657.4215804156</v>
+      </c>
+      <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v/>
+        <v>101142.24341145478</v>
       </c>
       <c r="K19" s="271" t="str">
         <f t="shared" si="9"/>
@@ -11487,13 +11585,13 @@
         <f>Data!D37</f>
         <v>-620360</v>
       </c>
-      <c r="I23" s="270" t="str">
+      <c r="I23" s="270">
         <f>Data!E37</f>
-        <v/>
-      </c>
-      <c r="J23" s="270" t="str">
+        <v>-584416</v>
+      </c>
+      <c r="J23" s="270">
         <f>Data!F37</f>
-        <v/>
+        <v>-536735</v>
       </c>
       <c r="K23" s="270" t="str">
         <f>Data!G37</f>
@@ -11544,13 +11642,13 @@
         <f>Data!D40</f>
         <v>-195284</v>
       </c>
-      <c r="I24" s="270" t="str">
+      <c r="I24" s="270">
         <f>Data!E40</f>
-        <v/>
-      </c>
-      <c r="J24" s="270" t="str">
+        <v>-172335</v>
+      </c>
+      <c r="J24" s="270">
         <f>Data!F40</f>
-        <v/>
+        <v>-145317</v>
       </c>
       <c r="K24" s="270" t="str">
         <f>Data!G40</f>
@@ -11601,13 +11699,13 @@
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I25" s="270" t="str">
+      <c r="I25" s="270">
         <f>Data!E42</f>
-        <v/>
-      </c>
-      <c r="J25" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="J25" s="270">
         <f>Data!F42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K25" s="270" t="str">
         <f>Data!G42</f>
@@ -11658,13 +11756,13 @@
         <f t="shared" ref="H26:Q26" si="10">IF(H$4="","",SUM(H23:H25))</f>
         <v>-815644</v>
       </c>
-      <c r="I26" s="267" t="str">
+      <c r="I26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J26" s="267" t="str">
+        <v>-756751</v>
+      </c>
+      <c r="J26" s="267">
         <f t="shared" si="10"/>
-        <v/>
+        <v>-682052</v>
       </c>
       <c r="K26" s="267" t="str">
         <f t="shared" si="10"/>
@@ -11725,13 +11823,13 @@
         <f t="shared" si="11"/>
         <v>0.61463833176955718</v>
       </c>
-      <c r="I29" s="13" t="str">
+      <c r="I29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="J29" s="13" t="str">
+        <v>0.62353735733665938</v>
+      </c>
+      <c r="J29" s="13">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.63274970586779022</v>
       </c>
       <c r="K29" s="13" t="str">
         <f t="shared" si="11"/>
@@ -11782,13 +11880,13 @@
         <f t="shared" si="12"/>
         <v>0.19348286798195596</v>
       </c>
-      <c r="I30" s="13" t="str">
+      <c r="I30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J30" s="13" t="str">
+        <v>0.18387126717374813</v>
+      </c>
+      <c r="J30" s="13">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0.17131226584364662</v>
       </c>
       <c r="K30" s="13" t="str">
         <f t="shared" si="12"/>
@@ -11839,13 +11937,13 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I31" s="13" t="str">
+      <c r="I31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K31" s="13" t="str">
         <f t="shared" si="13"/>
@@ -11894,13 +11992,13 @@
         <f t="shared" si="14"/>
         <v>0.8081211997515132</v>
       </c>
-      <c r="I32" s="29" t="str">
+      <c r="I32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J32" s="29" t="str">
+        <v>0.80740862451040751</v>
+      </c>
+      <c r="J32" s="29">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0.8040619717114369</v>
       </c>
       <c r="K32" s="29" t="str">
         <f t="shared" si="14"/>
@@ -11962,13 +12060,13 @@
         <f>IF(H4="","",Data!D41)</f>
         <v>-59319</v>
       </c>
-      <c r="I35" s="267" t="str">
+      <c r="I35" s="267">
         <f>IF(I4="","",Data!E41)</f>
-        <v/>
-      </c>
-      <c r="J35" s="267" t="str">
+        <v>-51409</v>
+      </c>
+      <c r="J35" s="267">
         <f>IF(J4="","",Data!F41)</f>
-        <v/>
+        <v>-49234</v>
       </c>
       <c r="K35" s="267" t="str">
         <f>IF(K4="","",Data!G41)</f>
@@ -12028,13 +12126,13 @@
         <f t="shared" si="15"/>
         <v>5.877189245315359E-2</v>
       </c>
-      <c r="I38" s="29" t="str">
+      <c r="I38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="J38" s="29" t="str">
+        <v>5.4850366867642775E-2</v>
+      </c>
+      <c r="J38" s="29">
         <f t="shared" si="15"/>
-        <v/>
+        <v>5.8041303471349517E-2</v>
       </c>
       <c r="K38" s="29" t="str">
         <f t="shared" si="15"/>
@@ -12098,13 +12196,13 @@
         <f t="shared" si="16"/>
         <v>0.25154766962493769</v>
       </c>
-      <c r="I41" s="6" t="str">
+      <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="J41" s="6" t="str">
+        <v>0.25175858623293434</v>
+      </c>
+      <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0.26154293208425849</v>
       </c>
       <c r="K41" s="6" t="str">
         <f t="shared" si="16"/>
@@ -12186,13 +12284,13 @@
         <f>Data!D51</f>
         <v>-3730</v>
       </c>
-      <c r="I45" s="266" t="str">
+      <c r="I45" s="266">
         <f>Data!E51</f>
-        <v/>
-      </c>
-      <c r="J45" s="266" t="str">
+        <v>-2330</v>
+      </c>
+      <c r="J45" s="266">
         <f>Data!F51</f>
-        <v/>
+        <v>-2679</v>
       </c>
       <c r="K45" s="266" t="str">
         <f>Data!G51</f>
@@ -12241,13 +12339,13 @@
         <f t="shared" si="17"/>
         <v>13860.138577182464</v>
       </c>
-      <c r="I46" s="274" t="str">
+      <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="J46" s="274" t="str">
+        <v>10315.421580415585</v>
+      </c>
+      <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v/>
+        <v>10971.243411454787</v>
       </c>
       <c r="K46" s="274" t="str">
         <f t="shared" si="17"/>
@@ -12298,13 +12396,13 @@
         <f>Data!D52</f>
         <v>21134</v>
       </c>
-      <c r="I47" s="278" t="str">
+      <c r="I47" s="278">
         <f>Data!E52</f>
-        <v/>
-      </c>
-      <c r="J47" s="278" t="str">
+        <v>15729</v>
+      </c>
+      <c r="J47" s="278">
         <f>Data!F52</f>
-        <v/>
+        <v>16729</v>
       </c>
       <c r="K47" s="278" t="str">
         <f>Data!G52</f>
@@ -12353,13 +12451,13 @@
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
         <v>10130.138577182464</v>
       </c>
-      <c r="I48" s="267" t="str">
+      <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="J48" s="267" t="str">
+        <v>7985.4215804155847</v>
+      </c>
+      <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v/>
+        <v>8292.2434114547868</v>
       </c>
       <c r="K48" s="267" t="str">
         <f t="shared" si="18"/>
@@ -12470,13 +12568,13 @@
         <f t="shared" si="19"/>
         <v>36.017694369973192</v>
       </c>
-      <c r="I53" s="40" t="str">
+      <c r="I53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J53" s="40" t="str">
+        <v>55.407296137339053</v>
+      </c>
+      <c r="J53" s="40">
         <f t="shared" si="19"/>
-        <v/>
+        <v>43.662560656961553</v>
       </c>
       <c r="K53" s="40" t="str">
         <f t="shared" si="19"/>
@@ -12539,13 +12637,13 @@
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="266" t="str">
+      <c r="I56" s="266">
         <f>Data!E56</f>
-        <v/>
-      </c>
-      <c r="J56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" s="266">
         <f>Data!F56</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K56" s="266" t="str">
         <f>Data!G56</f>
@@ -12594,13 +12692,13 @@
         <f>Data!D55</f>
         <v>8958</v>
       </c>
-      <c r="I57" s="266" t="str">
+      <c r="I57" s="266">
         <f>Data!E55</f>
-        <v/>
-      </c>
-      <c r="J57" s="266" t="str">
+        <v>10986</v>
+      </c>
+      <c r="J57" s="266">
         <f>Data!F55</f>
-        <v/>
+        <v>11914</v>
       </c>
       <c r="K57" s="266" t="str">
         <f>Data!G55</f>
@@ -12649,13 +12747,13 @@
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I58" s="266" t="str">
+      <c r="I58" s="266">
         <f>Data!E57</f>
-        <v/>
-      </c>
-      <c r="J58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" s="266">
         <f>Data!F57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K58" s="266" t="str">
         <f>Data!G57</f>
@@ -12704,13 +12802,13 @@
         <f t="shared" si="20"/>
         <v>8958</v>
       </c>
-      <c r="I59" s="267" t="str">
+      <c r="I59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J59" s="267" t="str">
+        <v>10986</v>
+      </c>
+      <c r="J59" s="267">
         <f t="shared" si="20"/>
-        <v/>
+        <v>11914</v>
       </c>
       <c r="K59" s="267" t="str">
         <f t="shared" si="20"/>
@@ -12760,13 +12858,13 @@
         <f>Data!D58</f>
         <v>9823</v>
       </c>
-      <c r="I60" s="266" t="str">
+      <c r="I60" s="266">
         <f>Data!E58</f>
-        <v/>
-      </c>
-      <c r="J60" s="266" t="str">
+        <v>9388</v>
+      </c>
+      <c r="J60" s="266">
         <f>Data!F58</f>
-        <v/>
+        <v>9248</v>
       </c>
       <c r="K60" s="266" t="str">
         <f>Data!G58</f>
@@ -12815,13 +12913,13 @@
         <f t="shared" si="21"/>
         <v>18781</v>
       </c>
-      <c r="I61" s="267" t="str">
+      <c r="I61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="J61" s="267" t="str">
+        <v>20374</v>
+      </c>
+      <c r="J61" s="267">
         <f t="shared" si="21"/>
-        <v/>
+        <v>21162</v>
       </c>
       <c r="K61" s="267" t="str">
         <f t="shared" si="21"/>
@@ -13035,13 +13133,13 @@
         <f t="shared" si="23"/>
         <v>0.8081211997515132</v>
       </c>
-      <c r="I71" s="6" t="str">
+      <c r="I71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="J71" s="6" t="str">
+        <v>0.80740862451040751</v>
+      </c>
+      <c r="J71" s="6">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.8040619717114369</v>
       </c>
       <c r="K71" s="6" t="str">
         <f t="shared" si="23"/>
@@ -13092,13 +13190,13 @@
         <f t="shared" si="24"/>
         <v>0.19187880024848683</v>
       </c>
-      <c r="I72" s="62" t="str">
+      <c r="I72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="J72" s="62" t="str">
+        <v>0.19259137548959251</v>
+      </c>
+      <c r="J72" s="62">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0.19593802828856316</v>
       </c>
       <c r="K72" s="62" t="str">
         <f t="shared" si="24"/>
@@ -13149,13 +13247,13 @@
         <f t="shared" si="25"/>
         <v>5.877189245315359E-2</v>
       </c>
-      <c r="I73" s="6" t="str">
+      <c r="I73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="J73" s="6" t="str">
+        <v>5.4850366867642775E-2</v>
+      </c>
+      <c r="J73" s="6">
         <f t="shared" si="25"/>
-        <v/>
+        <v>5.8041303471349517E-2</v>
       </c>
       <c r="K73" s="6" t="str">
         <f t="shared" si="25"/>
@@ -13206,13 +13304,13 @@
         <f t="shared" si="26"/>
         <v>0.13310690779533324</v>
       </c>
-      <c r="I74" s="62" t="str">
+      <c r="I74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="J74" s="62" t="str">
+        <v>0.13774100862194974</v>
+      </c>
+      <c r="J74" s="62">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.13789672481721363</v>
       </c>
       <c r="K74" s="62" t="str">
         <f t="shared" si="26"/>
@@ -13263,13 +13361,13 @@
         <f t="shared" si="27"/>
         <v>8.8753790959953793E-3</v>
       </c>
-      <c r="I75" s="6" t="str">
+      <c r="I75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="J75" s="6" t="str">
+        <v>1.1721413184615993E-2</v>
+      </c>
+      <c r="J75" s="6">
         <f t="shared" si="27"/>
-        <v/>
+        <v>1.4045255099274042E-2</v>
       </c>
       <c r="K75" s="6" t="str">
         <f t="shared" si="27"/>
@@ -13320,13 +13418,13 @@
         <f t="shared" si="28"/>
         <v>1.0036706872902614E-2</v>
       </c>
-      <c r="I76" s="6" t="str">
+      <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="J76" s="6" t="str">
+        <v>8.51997322022577E-3</v>
+      </c>
+      <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v/>
+        <v>9.7756147439278934E-3</v>
       </c>
       <c r="K76" s="6" t="str">
         <f t="shared" si="28"/>
@@ -13377,13 +13475,13 @@
         <f t="shared" si="29"/>
         <v>0.15201899376423123</v>
       </c>
-      <c r="I77" s="62" t="str">
+      <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J77" s="62" t="str">
+        <v>0.15798239502679151</v>
+      </c>
+      <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0.16171759466041555</v>
       </c>
       <c r="K77" s="62" t="str">
         <f t="shared" si="29"/>
@@ -13434,13 +13532,13 @@
         <f t="shared" si="30"/>
         <v>3.82400236201203E-2</v>
       </c>
-      <c r="I78" s="6" t="str">
+      <c r="I78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="J78" s="6" t="str">
+        <v>3.977342442163799E-2</v>
+      </c>
+      <c r="J78" s="6">
         <f t="shared" si="30"/>
-        <v/>
+        <v>4.2296093877098713E-2</v>
       </c>
       <c r="K78" s="6" t="str">
         <f t="shared" si="30"/>
@@ -13479,7 +13577,7 @@
       </c>
       <c r="C79" s="233">
         <f>MIN(BS!C62,MAX(G79:K79))</f>
-        <v>1.6744128904032363E-4</v>
+        <v>1.862640847478008E-4</v>
       </c>
       <c r="D79" s="26"/>
       <c r="E79" s="234"/>
@@ -13492,13 +13590,13 @@
         <f t="shared" si="31"/>
         <v>1.6744128904032363E-4</v>
       </c>
-      <c r="I79" s="6" t="str">
+      <c r="I79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="J79" s="6" t="str">
+        <v>1.4403702711843791E-4</v>
+      </c>
+      <c r="J79" s="6">
         <f t="shared" si="31"/>
-        <v/>
+        <v>1.862640847478008E-4</v>
       </c>
       <c r="K79" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13536,7 +13634,7 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>0.12605415047335763</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -13549,13 +13647,13 @@
         <f t="shared" si="32"/>
         <v>0.1136115288550706</v>
       </c>
-      <c r="I80" s="62" t="str">
+      <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J80" s="62" t="str">
+        <v>0.1180649335780351</v>
+      </c>
+      <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v/>
+        <v>0.11923523669856904</v>
       </c>
       <c r="K80" s="62" t="str">
         <f t="shared" si="32"/>
@@ -13606,13 +13704,13 @@
         <f t="shared" si="33"/>
         <v>0.20522159219822672</v>
       </c>
-      <c r="I81" s="6" t="str">
+      <c r="I81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J81" s="6" t="str">
+        <v>0.21347034277611632</v>
+      </c>
+      <c r="J81" s="6">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0.2275781660768304</v>
       </c>
       <c r="K81" s="6" t="str">
         <f t="shared" si="33"/>
@@ -13649,8 +13747,8 @@
         <v>77</v>
       </c>
       <c r="C82" s="85">
-        <f>MAX(AVERAGE(G82:J82),C81)</f>
-        <v>0.19441927433470874</v>
+        <f>C81</f>
+        <v>0.18361695647119072</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
@@ -13665,13 +13763,13 @@
         <f t="shared" si="34"/>
         <v>0.20522159219822672</v>
       </c>
-      <c r="I82" s="6" t="str">
+      <c r="I82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J82" s="6" t="str">
+        <v>0.21347034277611632</v>
+      </c>
+      <c r="J82" s="6">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0.2275781660768304</v>
       </c>
       <c r="K82" s="6" t="str">
         <f t="shared" si="34"/>
@@ -13759,7 +13857,7 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>0.12605415047335763</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
@@ -13772,13 +13870,13 @@
         <f t="shared" si="35"/>
         <v>0.1136115288550706</v>
       </c>
-      <c r="I85" s="62" t="str">
+      <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J85" s="62" t="str">
+        <v>0.1180649335780351</v>
+      </c>
+      <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.11923523669856904</v>
       </c>
       <c r="K85" s="62" t="str">
         <f t="shared" si="35"/>
@@ -13839,13 +13937,13 @@
         <f>Data!D65</f>
         <v>4.83</v>
       </c>
-      <c r="I88" s="109" t="str">
+      <c r="I88" s="109">
         <f>Data!E65</f>
-        <v/>
-      </c>
-      <c r="J88" s="109" t="str">
+        <v>4.41</v>
+      </c>
+      <c r="J88" s="109">
         <f>Data!F65</f>
-        <v/>
+        <v>4.0600000000000005</v>
       </c>
       <c r="K88" s="109" t="str">
         <f>Data!G65</f>
@@ -13895,13 +13993,13 @@
         <f t="shared" si="36"/>
         <v>104543.44993596</v>
       </c>
-      <c r="I89" s="71" t="str">
+      <c r="I89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J89" s="71" t="str">
+        <v>95452.715158919993</v>
+      </c>
+      <c r="J89" s="71">
         <f t="shared" si="36"/>
-        <v/>
+        <v>87877.102844720022</v>
       </c>
       <c r="K89" s="71" t="str">
         <f t="shared" si="36"/>
@@ -13939,7 +14037,7 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.83976961030735076</v>
+        <v>0.83989502603092137</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
@@ -13950,13 +14048,13 @@
         <f t="shared" si="37"/>
         <v>0.91169647939400045</v>
       </c>
-      <c r="I90" s="152" t="str">
+      <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J90" s="152" t="str">
+        <v>0.86259659583296711</v>
+      </c>
+      <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0.8688466844385575</v>
       </c>
       <c r="K90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14026,13 +14124,13 @@
         <f t="shared" si="38"/>
         <v>5.9482758620689656E-2</v>
       </c>
-      <c r="I92" s="22" t="str">
+      <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J92" s="22" t="str">
+        <v>5.4310344827586204E-2</v>
+      </c>
+      <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14104,13 +14202,13 @@
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
         <v>3.115993219123192E-2</v>
       </c>
-      <c r="H95" s="6" t="str">
+      <c r="H95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="I95" s="6" t="str">
+        <v>7.687309484358118E-2</v>
+      </c>
+      <c r="I95" s="6">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0.10492208738379127</v>
       </c>
       <c r="J95" s="6" t="str">
         <f t="shared" si="39"/>
@@ -14161,13 +14259,13 @@
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
         <v>7.8646400063074884E-2</v>
       </c>
-      <c r="H96" s="6" t="str">
+      <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I96" s="6" t="str">
+        <v>3.6224094856472489E-2</v>
+      </c>
+      <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v/>
+        <v>7.9401644882495237E-2</v>
       </c>
       <c r="J96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -14256,15 +14354,15 @@
       </c>
       <c r="H100" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="270" t="str">
+        <v>1992657</v>
+      </c>
+      <c r="I100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="J100" s="270" t="str">
+        <v>1935538</v>
+      </c>
+      <c r="J100" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>1841327</v>
       </c>
       <c r="K100" s="270" t="str">
         <f t="shared" si="41"/>
@@ -14309,15 +14407,15 @@
       <c r="F101" s="86"/>
       <c r="G101" s="282">
         <f>IF(G$4="","",Data!D77)</f>
-        <v>0</v>
-      </c>
-      <c r="H101" s="282" t="str">
+        <v>68428</v>
+      </c>
+      <c r="H101" s="282">
         <f>IF(H$4="","",Data!E77)</f>
-        <v/>
-      </c>
-      <c r="I101" s="282" t="str">
+        <v>55620</v>
+      </c>
+      <c r="I101" s="282">
         <f>IF(I$4="","",Data!F77)</f>
-        <v/>
+        <v>47417</v>
       </c>
       <c r="J101" s="282" t="str">
         <f>IF(J$4="","",Data!G77)</f>
@@ -14366,15 +14464,15 @@
       <c r="F102" s="86"/>
       <c r="G102" s="282">
         <f>IF(G$4="","",Data!D78)</f>
-        <v>0</v>
-      </c>
-      <c r="H102" s="282" t="str">
+        <v>12026</v>
+      </c>
+      <c r="H102" s="282">
         <f>IF(H$4="","",Data!E78)</f>
-        <v/>
-      </c>
-      <c r="I102" s="282" t="str">
+        <v>11696</v>
+      </c>
+      <c r="I102" s="282">
         <f>IF(I$4="","",Data!F78)</f>
-        <v/>
+        <v>10203</v>
       </c>
       <c r="J102" s="282" t="str">
         <f>IF(J$4="","",Data!G78)</f>
@@ -14427,15 +14525,15 @@
       </c>
       <c r="H103" s="270">
         <f>Data!D79</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="270" t="str">
+        <v>646672</v>
+      </c>
+      <c r="I103" s="270">
         <f>Data!E79</f>
-        <v/>
-      </c>
-      <c r="J103" s="270" t="str">
+        <v>634115</v>
+      </c>
+      <c r="J103" s="270">
         <f>Data!F79</f>
-        <v/>
+        <v>631035</v>
       </c>
       <c r="K103" s="270" t="str">
         <f>Data!G79</f>
@@ -14484,15 +14582,15 @@
       </c>
       <c r="H104" s="270">
         <f>Data!D80</f>
-        <v>0</v>
-      </c>
-      <c r="I104" s="270" t="str">
+        <v>1345985</v>
+      </c>
+      <c r="I104" s="270">
         <f>Data!E80</f>
-        <v/>
-      </c>
-      <c r="J104" s="270" t="str">
+        <v>1301423</v>
+      </c>
+      <c r="J104" s="270">
         <f>Data!F80</f>
-        <v/>
+        <v>1210292</v>
       </c>
       <c r="K104" s="270" t="str">
         <f>Data!G80</f>
@@ -14564,19 +14662,19 @@
       <c r="F107" s="25"/>
       <c r="G107" s="91">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H107" s="91" t="e">
+        <v>6.5748170325694993E-2</v>
+      </c>
+      <c r="H107" s="91">
+        <f t="shared" si="42"/>
+        <v>5.510700885457278E-2</v>
+      </c>
+      <c r="I107" s="91">
+        <f t="shared" si="42"/>
+        <v>5.0591138628703486E-2</v>
+      </c>
+      <c r="J107" s="91" t="e">
         <f t="shared" si="42"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="I107" s="91" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="J107" s="91" t="str">
-        <f t="shared" si="42"/>
-        <v/>
       </c>
       <c r="K107" s="91" t="str">
         <f t="shared" si="42"/>
@@ -14621,19 +14719,19 @@
       <c r="F108" s="25"/>
       <c r="G108" s="91">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H108" s="91" t="e">
+        <v>1.1555028589711932E-2</v>
+      </c>
+      <c r="H108" s="91">
+        <f t="shared" si="43"/>
+        <v>1.1588126133820266E-2</v>
+      </c>
+      <c r="I108" s="91">
+        <f t="shared" si="43"/>
+        <v>1.0885998427329052E-2</v>
+      </c>
+      <c r="J108" s="91" t="e">
         <f t="shared" si="43"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="I108" s="91" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="J108" s="91" t="str">
-        <f t="shared" si="43"/>
-        <v/>
       </c>
       <c r="K108" s="91" t="str">
         <f t="shared" si="43"/>
@@ -14719,13 +14817,13 @@
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>2.7432675180960322</v>
       </c>
-      <c r="I112" s="251" t="str">
+      <c r="I112" s="251">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v/>
-      </c>
-      <c r="J112" s="251" t="str">
+        <v>2.2353774861856457</v>
+      </c>
+      <c r="J112" s="251">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v/>
+        <v>2.7063436108197343</v>
       </c>
       <c r="K112" s="251" t="str">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
@@ -14774,13 +14872,13 @@
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>3.156324399841786</v>
       </c>
-      <c r="I113" s="251" t="str">
+      <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v/>
-      </c>
-      <c r="J113" s="251" t="str">
+        <v>2.537109540330079</v>
+      </c>
+      <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v/>
+        <v>3.1120923303976435</v>
       </c>
       <c r="K113" s="251" t="str">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -14826,7 +14924,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>31yrs Projection</v>
+        <v>15yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14885,7 +14983,7 @@
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
@@ -14895,13 +14993,13 @@
         <f t="shared" si="44"/>
         <v>0.15201899376423123</v>
       </c>
-      <c r="I116" s="22" t="str">
+      <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="J116" s="22" t="str">
+        <v>0.15798239502679151</v>
+      </c>
+      <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v/>
+        <v>0.16171759466041555</v>
       </c>
       <c r="K116" s="22" t="str">
         <f t="shared" si="44"/>
@@ -14948,17 +15046,17 @@
         <f t="shared" ref="G117:Q117" si="45">IF(G4="","",G4/G100)</f>
         <v>0.48913824057450628</v>
       </c>
-      <c r="H117" s="40" t="e">
+      <c r="H117" s="40">
         <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I117" s="40" t="str">
+        <v>0.50651416676327132</v>
+      </c>
+      <c r="I117" s="40">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="J117" s="40" t="str">
+        <v>0.48423694084022118</v>
+      </c>
+      <c r="J117" s="40">
         <f t="shared" si="45"/>
-        <v/>
+        <v>0.46067754396693256</v>
       </c>
       <c r="K117" s="40" t="str">
         <f t="shared" si="45"/>
@@ -15007,17 +15105,17 @@
         <f t="shared" ref="G118:Q118" si="46">IF(G$4="","",G100/G104)</f>
         <v>1.4835789300471205</v>
       </c>
-      <c r="H118" s="15" t="e">
+      <c r="H118" s="15">
         <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I118" s="15" t="str">
+        <v>1.4804451758377695</v>
+      </c>
+      <c r="I118" s="15">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="J118" s="15" t="str">
+        <v>1.4872474207079482</v>
+      </c>
+      <c r="J118" s="15">
         <f t="shared" si="46"/>
-        <v/>
+        <v>1.521390705713993</v>
       </c>
       <c r="K118" s="15" t="str">
         <f t="shared" si="46"/>
@@ -15059,25 +15157,25 @@
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <f>C119</f>
-        <v>0.11683147612363115</v>
+        <f>AVERAGE(G119:J119)</f>
+        <v>0.1141273682688253</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
         <v>0.11539664872608364</v>
       </c>
-      <c r="H119" s="99" t="e">
+      <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I119" s="99" t="str">
+        <v>0.11399394389772728</v>
+      </c>
+      <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="J119" s="99" t="str">
+        <v>0.11377578356953549</v>
+      </c>
+      <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v/>
+        <v>0.11334309688195475</v>
       </c>
       <c r="K119" s="99" t="str">
         <f t="shared" si="47"/>
@@ -15179,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>6.0611862319441281</v>
+        <v>6.787514895689025</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>5.797526537326231</v>
+        <v>6.4932297218053794</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.2978157853702301</v>
-      </c>
-      <c r="I123" s="159" t="str">
+        <v>5.9335536796146586</v>
+      </c>
+      <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J123" s="159" t="str">
+        <v>5.7259674149658082</v>
+      </c>
+      <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v/>
+        <v>5.2336045949676029</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15236,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4645150639706004E-2</v>
+        <v>8.3590084922278637E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1398110065593975E-2</v>
+        <v>7.9965883273465266E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.5244036765643221E-2</v>
-      </c>
-      <c r="I124" s="74" t="str">
+        <v>7.3073321177520426E-2</v>
+      </c>
+      <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="J124" s="74" t="str">
+        <v>7.0516840085785806E-2</v>
+      </c>
+      <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v/>
+        <v>6.4453258558714324E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15299,13 +15397,13 @@
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>7.5067904908705782E-2</v>
       </c>
-      <c r="I125" s="22" t="str">
+      <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="J125" s="22" t="str">
+        <v>7.1460025384499901E-2</v>
+      </c>
+      <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
+        <v>6.6175372329646681E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16084,11 +16182,11 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
         <v>431</v>
@@ -16099,7 +16197,7 @@
       </c>
       <c r="G4" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H4" s="308" t="s">
         <v>394</v>
@@ -16127,7 +16225,7 @@
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H5" s="308" t="s">
         <v>395</v>
@@ -16144,11 +16242,11 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2548872.9795114528</v>
+        <v>2548492.3739130064</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>433</v>
@@ -16159,7 +16257,7 @@
       </c>
       <c r="G6" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H6" s="308" t="s">
         <v>416</v>
@@ -16188,7 +16286,7 @@
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H7" s="312" t="s">
         <v>417</v>
@@ -16207,18 +16305,18 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>2806062.2349022729</v>
+        <v>2805681.6293038265</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
         <v>464</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>11.882371437891207</v>
+        <v>13.308256010438154</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16239,15 +16337,15 @@
     <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
-        <v>*HKD</v>
+        <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="F9" s="322"/>
       <c r="H9" s="308" t="str">
@@ -16256,7 +16354,7 @@
       </c>
       <c r="I9" s="144">
         <f>Normalized_FCF!C79</f>
-        <v>1.6744128904032363E-4</v>
+        <v>1.862640847478008E-4</v>
       </c>
       <c r="J9" s="306"/>
       <c r="N9" s="304"/>
@@ -16268,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2806062.2349022729</v>
+        <v>3142363.4248202858</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16290,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16327,7 +16425,7 @@
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>413</v>
@@ -16343,11 +16441,11 @@
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Terminal Year</v>
+        <v>Change year</v>
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>429</v>
@@ -16387,7 +16485,7 @@
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16399,21 +16497,21 @@
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="308" t="s">
         <v>423</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="140" t="s">
         <v>97</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.96976544293689</v>
+        <v>145.41634829911979</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16488,19 +16586,19 @@
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>122962.286022985</v>
+        <v>134467.2068110503</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>-6.2730243436495137E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16508,7 +16606,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>114650.15013798136</v>
+        <v>125377.3490079723</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16537,11 +16635,11 @@
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>126050.86849920047</v>
+        <v>137844.77136368572</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16549,7 +16647,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16557,7 +16655,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>109585.03246489682</v>
+        <v>119838.31547421345</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16586,11 +16684,11 @@
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>129217.03038631438</v>
+        <v>141307.1740160911</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16598,7 +16696,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16606,7 +16704,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>104743.68612583427</v>
+        <v>114543.99035653504</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16643,19 +16741,19 @@
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>132462.72033392297</v>
+        <v>144856.545742541</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298607934E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16663,7 +16761,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>100116.22514910219</v>
+        <v>109483.56270596269</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16700,11 +16798,11 @@
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>135789.9359380531</v>
+        <v>148495.07104339535</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16712,7 +16810,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16720,7 +16818,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>95693.200314377333</v>
+        <v>104646.69918937043</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16757,11 +16855,11 @@
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>139200.72497060488</v>
+        <v>152224.98928957427</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
@@ -16769,7 +16867,7 @@
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16777,7 +16875,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>91465.579857508856</v>
+        <v>100023.52298893694</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16806,11 +16904,11 @@
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>142697.18663967581</v>
+        <v>156048.59610080408</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
@@ -16818,7 +16916,7 @@
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983968</v>
+        <v>0.12603532767765022</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16826,7 +16924,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>87424.731027763526</v>
+        <v>95604.593633801283</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16855,11 +16953,11 @@
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>146281.47288154159</v>
+        <v>159968.24475848171</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
@@ -16867,7 +16965,7 @@
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16973,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>83562.402459850971</v>
+        <v>91380.887722733212</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16904,11 +17002,11 @@
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>149955.78968508952</v>
+        <v>163986.34765402842</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
@@ -16916,7 +17014,7 @@
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16924,7 +17022,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>79870.707324734205</v>
+        <v>87343.780498455497</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -16953,19 +17051,19 @@
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>153722.39844951872</v>
+        <v>168105.37777362246</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983968</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -16973,7 +17071,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>76342.107224818159</v>
+        <v>83485.028235991776</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17002,19 +17100,19 @@
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>157583.61737614346</v>
+        <v>172327.87022022629</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17022,7 +17120,7 @@
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>72969.396800631454</v>
+        <v>79796.751409078177</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17051,19 +17149,19 @@
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>161541.82289515622</v>
+        <v>176656.42377384385</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298608378E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12603532767765022</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17071,7 +17169,7 @@
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>69745.68901756806</v>
+        <v>76271.418600264369</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17100,19 +17198,19 @@
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>165599.45112822778</v>
+        <v>181093.70249096851</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298607934E-2</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12603532767765019</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17120,7 +17218,7 @@
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>66664.401102644435</v>
+        <v>72901.831121848605</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17157,11 +17255,11 @@
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>169758.99938784572</v>
+        <v>185642.43734420667</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
@@ -17169,7 +17267,7 @@
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12603532767765022</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17177,7 +17275,7 @@
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>63719.241102555286</v>
+        <v>69681.108316243073</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17191,7 +17289,7 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
@@ -17206,27 +17304,27 @@
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>243095.24868737685</v>
+        <v>237468.71897764431</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>174023.02771431298</v>
+        <v>185894.22861065448</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>1.3563238559561874E-3</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983968</v>
+        <v>0.12311388211301814</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17234,7 +17332,7 @@
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>60904.195035579694</v>
+        <v>65058.851716328078</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -17248,7 +17346,7 @@
     <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B36" s="117">
         <v>16</v>
@@ -17263,27 +17361,27 @@
       </c>
       <c r="E36" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F36" s="277">
         <f t="shared" si="7"/>
-        <v>249201.34633268844</v>
+        <v>243433.4887278309</v>
       </c>
       <c r="G36" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="277">
         <f t="shared" si="8"/>
-        <v>178394.16045135332</v>
+        <v>190563.54369486767</v>
       </c>
       <c r="I36" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298607934E-2</v>
       </c>
       <c r="J36" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
@@ -17291,13 +17389,13 @@
       </c>
       <c r="L36" s="277">
         <f t="shared" si="4"/>
-        <v>58213.514611101949</v>
+        <v>62184.623124194797</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B37" s="117">
         <v>17</v>
@@ -17312,27 +17410,27 @@
       </c>
       <c r="E37" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F37" s="277">
         <f t="shared" si="7"/>
-        <v>255460.81772205877</v>
+        <v>249548.08232987433</v>
       </c>
       <c r="G37" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H37" s="277">
         <f t="shared" si="8"/>
-        <v>182875.08786129288</v>
+        <v>195350.14323443276</v>
       </c>
       <c r="I37" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J37" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
@@ -17340,13 +17438,13 @@
       </c>
       <c r="L37" s="277">
         <f t="shared" si="4"/>
-        <v>55641.705491670386</v>
+        <v>59437.374793500145</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B38" s="117">
         <v>18</v>
@@ -17361,27 +17459,27 @@
       </c>
       <c r="E38" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F38" s="277">
         <f t="shared" si="7"/>
-        <v>261877.51531686881</v>
+        <v>255816.26307850773</v>
       </c>
       <c r="G38" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="277">
         <f t="shared" si="8"/>
-        <v>187468.5677808121</v>
+        <v>200256.97319534674</v>
       </c>
       <c r="I38" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J38" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301814</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
@@ -17389,13 +17487,13 @@
       </c>
       <c r="L38" s="277">
         <f t="shared" si="4"/>
-        <v>53183.516073625688</v>
+        <v>56811.496875800236</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B39" s="117">
         <v>19</v>
@@ -17410,27 +17508,27 @@
       </c>
       <c r="E39" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F39" s="277">
         <f t="shared" si="7"/>
-        <v>268455.38834511861</v>
+        <v>262241.88879538415</v>
       </c>
       <c r="G39" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H39" s="277">
         <f t="shared" si="8"/>
-        <v>192177.42731828682</v>
+        <v>205287.05354075832</v>
       </c>
       <c r="I39" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298607711E-2</v>
       </c>
       <c r="J39" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.1231138821130181</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
@@ -17438,13 +17536,13 @@
       </c>
       <c r="L39" s="277">
         <f t="shared" si="4"/>
-        <v>50833.926763388437</v>
+        <v>54301.627359592116</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B40" s="117">
         <v>20</v>
@@ -17459,27 +17557,27 @@
       </c>
       <c r="E40" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F40" s="277">
         <f t="shared" si="7"/>
-        <v>275198.48523202399</v>
+        <v>268828.91420341597</v>
       </c>
       <c r="G40" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="277">
         <f t="shared" si="8"/>
-        <v>197004.56459376399</v>
+        <v>210443.48008963838</v>
       </c>
       <c r="I40" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298608378E-2</v>
       </c>
       <c r="J40" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301814</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
@@ -17487,13 +17585,13 @@
       </c>
       <c r="L40" s="277">
         <f t="shared" si="4"/>
-        <v>48588.139727508875</v>
+        <v>51902.641121150184</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B41" s="117">
         <v>21</v>
@@ -17508,27 +17606,27 @@
       </c>
       <c r="E41" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F41" s="277">
         <f t="shared" si="7"/>
-        <v>282110.95609166456</v>
+        <v>275581.3933607529</v>
       </c>
       <c r="G41" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="277">
         <f t="shared" si="8"/>
-        <v>201952.95052264156</v>
+        <v>215729.4264221355</v>
       </c>
       <c r="I41" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J41" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983964</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K41" s="119">
         <f t="shared" si="3"/>
@@ -17536,13 +17634,13 @@
       </c>
       <c r="L41" s="277">
         <f t="shared" si="4"/>
-        <v>46441.569095547908</v>
+        <v>49609.639459084232</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B42" s="117">
         <v>22</v>
@@ -17557,27 +17655,27 @@
       </c>
       <c r="E42" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F42" s="277">
         <f t="shared" si="7"/>
-        <v>289197.05528121802</v>
+        <v>282503.48215589748</v>
       </c>
       <c r="G42" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="277">
         <f t="shared" si="8"/>
-        <v>207025.6306441518</v>
+        <v>221148.14583279184</v>
       </c>
       <c r="I42" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J42" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301812</v>
       </c>
       <c r="K42" s="119">
         <f t="shared" si="3"/>
@@ -17585,13 +17683,13 @@
       </c>
       <c r="L42" s="277">
         <f t="shared" si="4"/>
-        <v>44389.831595784213</v>
+        <v>47417.940091249606</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B43" s="117">
         <v>23</v>
@@ -17606,27 +17704,27 @@
       </c>
       <c r="E43" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F43" s="277">
         <f t="shared" si="7"/>
-        <v>296461.14401935134</v>
+        <v>289599.44086549291</v>
       </c>
       <c r="G43" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="277">
         <f t="shared" si="8"/>
-        <v>212225.72699577184</v>
+        <v>226702.97333281927</v>
       </c>
       <c r="I43" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298608378E-2</v>
       </c>
       <c r="J43" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12311388211301814</v>
       </c>
       <c r="K43" s="119">
         <f t="shared" si="3"/>
@@ -17634,13 +17732,13 @@
       </c>
       <c r="L43" s="277">
         <f t="shared" si="4"/>
-        <v>42428.737604625392</v>
+        <v>45323.067593582608</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B44" s="117">
         <v>24</v>
@@ -17655,27 +17753,27 @@
       </c>
       <c r="E44" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F44" s="277">
         <f t="shared" si="7"/>
-        <v>303907.69307038159</v>
+        <v>296873.63677635754</v>
       </c>
       <c r="G44" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="277">
         <f t="shared" si="8"/>
-        <v>217556.44003471706</v>
+        <v>232397.32770266893</v>
       </c>
       <c r="I44" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.5118128298607934E-2</v>
       </c>
       <c r="J44" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301812</v>
       </c>
       <c r="K44" s="119">
         <f t="shared" si="3"/>
@@ -17683,13 +17781,13 @@
       </c>
       <c r="L44" s="277">
         <f t="shared" si="4"/>
-        <v>40554.282591446485</v>
+        <v>43320.744261337713</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B45" s="117">
         <v>25</v>
@@ -17704,19 +17802,19 @@
       </c>
       <c r="E45" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F45" s="277">
         <f t="shared" si="7"/>
-        <v>311541.28549585748</v>
+        <v>304330.54687338049</v>
       </c>
       <c r="G45" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H45" s="277">
         <f t="shared" si="8"/>
-        <v>223021.05060769754</v>
+        <v>238234.71359615825</v>
       </c>
       <c r="I45" s="299">
         <f t="shared" si="9"/>
@@ -17724,7 +17822,7 @@
       </c>
       <c r="J45" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301812</v>
       </c>
       <c r="K45" s="119">
         <f t="shared" si="3"/>
@@ -17732,13 +17830,13 @@
       </c>
       <c r="L45" s="277">
         <f t="shared" si="4"/>
-        <v>38762.638941385965</v>
+        <v>41406.881374065437</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B46" s="117">
         <v>26</v>
@@ -17753,27 +17851,27 @@
       </c>
       <c r="E46" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F46" s="277">
         <f t="shared" si="7"/>
-        <v>319366.61947525572</v>
+        <v>311974.76059493166</v>
       </c>
       <c r="G46" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H46" s="277">
         <f t="shared" si="8"/>
-        <v>228622.92197015206</v>
+        <v>244218.72369744876</v>
       </c>
       <c r="I46" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.5118128298608378E-2</v>
       </c>
       <c r="J46" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983965</v>
+        <v>0.12311388211301814</v>
       </c>
       <c r="K46" s="119">
         <f t="shared" si="3"/>
@@ -17781,13 +17879,13 @@
       </c>
       <c r="L46" s="277">
         <f t="shared" si="4"/>
-        <v>37050.14813940171</v>
+        <v>39577.570846493683</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B47" s="117">
         <v>27</v>
@@ -17802,19 +17900,19 @@
       </c>
       <c r="E47" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F47" s="277">
         <f t="shared" si="7"/>
-        <v>327388.51119752799</v>
+        <v>319810.98265748273</v>
       </c>
       <c r="G47" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H47" s="277">
         <f t="shared" si="8"/>
-        <v>234365.50185620104</v>
+        <v>250353.04093220361</v>
       </c>
       <c r="I47" s="299">
         <f t="shared" si="9"/>
@@ -17822,7 +17920,7 @@
       </c>
       <c r="J47" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K47" s="119">
         <f t="shared" si="3"/>
@@ -17830,7 +17928,7 @@
       </c>
       <c r="L47" s="277">
         <f t="shared" si="4"/>
-        <v>35413.313299626701</v>
+        <v>37829.077248264017</v>
       </c>
       <c r="N47" s="275"/>
       <c r="O47" s="275"/>
@@ -17844,7 +17942,7 @@
     <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B48" s="117">
         <v>28</v>
@@ -17859,19 +17957,19 @@
       </c>
       <c r="E48" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F48" s="277">
         <f t="shared" si="7"/>
-        <v>335611.89782527782</v>
+        <v>327844.0359511773</v>
       </c>
       <c r="G48" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="277">
         <f t="shared" si="8"/>
-        <v>240252.32460059281</v>
+        <v>256641.4407342854</v>
       </c>
       <c r="I48" s="299">
         <f t="shared" si="9"/>
@@ -17879,7 +17977,7 @@
       </c>
       <c r="J48" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983968</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K48" s="119">
         <f t="shared" si="3"/>
@@ -17887,7 +17985,7 @@
       </c>
       <c r="L48" s="277">
         <f t="shared" si="4"/>
-        <v>33848.792024769726</v>
+        <v>36157.830176227391</v>
       </c>
       <c r="N48" s="275"/>
       <c r="O48" s="275"/>
@@ -17901,7 +17999,7 @@
     <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B49" s="117">
         <v>29</v>
@@ -17916,27 +18014,27 @@
       </c>
       <c r="E49" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F49" s="277">
         <f t="shared" si="7"/>
-        <v>344041.8405333925</v>
+        <v>336078.86450813251</v>
       </c>
       <c r="G49" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H49" s="277">
         <f t="shared" si="8"/>
-        <v>246287.01331394931</v>
+        <v>263087.79336938879</v>
       </c>
       <c r="I49" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.5118128298608156E-2</v>
       </c>
       <c r="J49" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301812</v>
       </c>
       <c r="K49" s="119">
         <f t="shared" si="3"/>
@@ -17944,7 +18042,7 @@
       </c>
       <c r="L49" s="277">
         <f t="shared" si="4"/>
-        <v>32353.389580979754</v>
+        <v>34560.416963723212</v>
       </c>
       <c r="N49" s="275"/>
       <c r="O49" s="275"/>
@@ -17958,7 +18056,7 @@
     <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B50" s="117">
         <v>30</v>
@@ -17973,19 +18071,19 @@
       </c>
       <c r="E50" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F50" s="277">
         <f t="shared" si="7"/>
-        <v>352683.52762399957</v>
+        <v>344520.53654529835</v>
       </c>
       <c r="G50" s="299">
         <f t="shared" si="2"/>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="277">
         <f t="shared" si="8"/>
-        <v>252473.28211265014</v>
+        <v>269696.06631703884</v>
       </c>
       <c r="I50" s="299">
         <f t="shared" si="9"/>
@@ -17993,7 +18091,7 @@
       </c>
       <c r="J50" s="299">
         <f t="shared" si="10"/>
-        <v>0.11525183260983966</v>
+        <v>0.12311388211301813</v>
       </c>
       <c r="K50" s="119">
         <f t="shared" si="3"/>
@@ -18001,7 +18099,7 @@
       </c>
       <c r="L50" s="277">
         <f t="shared" si="4"/>
-        <v>30924.052374237446</v>
+        <v>33033.575711954691</v>
       </c>
       <c r="N50" s="275"/>
       <c r="O50" s="275"/>
@@ -18030,19 +18128,19 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>359737.19817647961</v>
+        <v>351410.94727620436</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
-        <v>-1.0802317863518013E-2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>3552037.9000676302</v>
+        <v>3794344.6571500646</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18055,7 +18153,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>435069.42650651315</v>
+        <v>464748.23760267306</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18068,7 +18166,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>2361153.7295674607</v>
+        <v>2553060.4355806289</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18092,7 +18190,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>2361153.7295674607</v>
+        <v>2553060.4355806289</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18127,19 +18225,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>1685326.9016354138</v>
+        <v>1803128.5918062211</v>
       </c>
       <c r="C56" s="118">
-        <v>1702180.1706517683</v>
+        <v>1821159.8777242838</v>
       </c>
       <c r="D56" s="118">
-        <v>1719033.439668122</v>
+        <v>1839191.1636423455</v>
       </c>
       <c r="E56" s="118">
-        <v>1735886.7086844763</v>
+        <v>1857222.449560408</v>
       </c>
       <c r="F56" s="118">
-        <v>1769593.2467171843</v>
+        <v>1893285.0213965327</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18153,19 +18251,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>1683241.290154404</v>
+        <v>1800900.7077006742</v>
       </c>
       <c r="C57" s="118">
-        <v>1715944.8468382484</v>
+        <v>1835863.5287029452</v>
       </c>
       <c r="D57" s="118">
-        <v>1748962.6835969908</v>
+        <v>1871162.0687928458</v>
       </c>
       <c r="E57" s="118">
-        <v>1782294.8004306296</v>
+        <v>1906796.3279703753</v>
       </c>
       <c r="F57" s="118">
-        <v>1849901.8743225993</v>
+        <v>1979072.0035883207</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18179,19 +18277,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>1681296.664064884</v>
+        <v>1798823.4264833808</v>
       </c>
       <c r="C58" s="118">
-        <v>1728907.3857178248</v>
+        <v>1849710.3235639695</v>
       </c>
       <c r="D58" s="118">
-        <v>1777426.859641229</v>
+        <v>1901567.9646003142</v>
       </c>
       <c r="E58" s="118">
-        <v>1826863.8768861429</v>
+        <v>1954405.7403361243</v>
       </c>
       <c r="F58" s="118">
-        <v>1928525.7055446832</v>
+        <v>2063059.2588809803</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18205,19 +18303,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>1679483.4928858441</v>
+        <v>1796886.5675395173</v>
       </c>
       <c r="C59" s="118">
-        <v>1741114.5318888009</v>
+        <v>1862750.1956475452</v>
       </c>
       <c r="D59" s="118">
-        <v>1804497.6844105744</v>
+        <v>1930485.4599137106</v>
       </c>
       <c r="E59" s="118">
-        <v>1869666.8127828129</v>
+        <v>2000128.5326314354</v>
       </c>
       <c r="F59" s="118">
-        <v>2005500.0857621075</v>
+        <v>2145284.5437828843</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18231,19 +18329,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>1677792.8903879053</v>
+        <v>1797723.9805482342</v>
       </c>
       <c r="C60" s="118">
-        <v>1752610.3059052913</v>
+        <v>1877726.641695542</v>
       </c>
       <c r="D60" s="118">
-        <v>1830243.3639114914</v>
+        <v>1960737.5466129768</v>
       </c>
       <c r="E60" s="118">
-        <v>1910773.5950425516</v>
+        <v>2046843.7876520243</v>
       </c>
       <c r="F60" s="118">
-        <v>2080859.618842104</v>
+        <v>2228699.1073663551</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18257,19 +18355,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>1676216.5710425074</v>
+        <v>1796040.1305853557</v>
       </c>
       <c r="C61" s="118">
-        <v>1763436.1630210537</v>
+        <v>1889290.9983442929</v>
       </c>
       <c r="D61" s="118">
-        <v>1854728.7653948802</v>
+        <v>1986893.250721568</v>
       </c>
       <c r="E61" s="118">
-        <v>1950251.4372127438</v>
+        <v>2089014.6607475593</v>
       </c>
       <c r="F61" s="118">
-        <v>2154638.1826966461</v>
+        <v>2307510.5692509133</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18283,19 +18381,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>1674746.8094150973</v>
+        <v>1796934.761942955</v>
       </c>
       <c r="C62" s="118">
-        <v>1773631.1426825176</v>
+        <v>1902720.7775684698</v>
       </c>
       <c r="D62" s="118">
-        <v>1878015.5807916697</v>
+        <v>2014384.1168917788</v>
       </c>
       <c r="E62" s="118">
-        <v>1988164.889366868</v>
+        <v>2132207.6216469961</v>
       </c>
       <c r="F62" s="118">
-        <v>2226868.9445122816</v>
+        <v>2387521.7896427466</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18309,19 +18407,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>1673376.4023032926</v>
+        <v>1795470.8707770703</v>
       </c>
       <c r="C63" s="118">
-        <v>1783232.009310097</v>
+        <v>1912976.579453825</v>
       </c>
       <c r="D63" s="118">
-        <v>1900162.4821480571</v>
+        <v>2038041.7971300543</v>
       </c>
       <c r="E63" s="118">
-        <v>2024575.9436500827</v>
+        <v>2171102.5020417371</v>
       </c>
       <c r="F63" s="118">
-        <v>2297584.3756604558</v>
+        <v>2463061.1633498883</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18335,19 +18433,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>1672098.633434477</v>
+        <v>1796403.9835669312</v>
       </c>
       <c r="C64" s="118">
-        <v>1792273.3848754629</v>
+        <v>1925026.0800585649</v>
       </c>
       <c r="D64" s="118">
-        <v>1921225.2694520331</v>
+        <v>2063028.8883012477</v>
       </c>
       <c r="E64" s="118">
-        <v>2059544.1356423539</v>
+        <v>2211042.5648013111</v>
       </c>
       <c r="F64" s="118">
-        <v>2366816.2662950326</v>
+        <v>2539809.0845648199</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18361,19 +18459,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>1670907.2405498007</v>
+        <v>1795131.3183100508</v>
       </c>
       <c r="C65" s="118">
-        <v>1800787.8737528706</v>
+        <v>1934121.3955617417</v>
       </c>
       <c r="D65" s="118">
-        <v>1941257.0112236473</v>
+        <v>2084427.1206689507</v>
       </c>
       <c r="E65" s="118">
-        <v>2093126.6417048622</v>
+        <v>2246915.9439816289</v>
       </c>
       <c r="F65" s="118">
-        <v>2434595.7396435691</v>
+        <v>2612212.2203983553</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18387,19 +18485,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>1666054.8200467599</v>
+        <v>1795951.2429734594</v>
       </c>
       <c r="C66" s="277">
-        <v>1836471.1922480257</v>
+        <v>1978608.8375075681</v>
       </c>
       <c r="D66" s="118">
-        <v>2027632.5413782506</v>
+        <v>2183450.2664018157</v>
       </c>
       <c r="E66" s="118">
-        <v>2242101.3840322774</v>
+        <v>2413213.720746126</v>
       </c>
       <c r="F66" s="118">
-        <v>2752751.2137071649</v>
+        <v>2960104.2301325845</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18422,19 +18520,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>1662635.2466888428</v>
+        <v>1795654.7457131369</v>
       </c>
       <c r="C67" s="277">
-        <v>1862900.4886138171</v>
+        <v>2010493.0207018843</v>
       </c>
       <c r="D67" s="118">
-        <v>2094838.0822295498</v>
+        <v>2259210.762496735</v>
       </c>
       <c r="E67" s="118">
-        <v>2363807.460556563</v>
+        <v>2547535.3954563397</v>
       </c>
       <c r="F67" s="118">
-        <v>3038904.9303456852</v>
+        <v>3270856.7715516072</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18457,19 +18555,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>1660225.422160476</v>
+        <v>1797311.1890186374</v>
       </c>
       <c r="C68" s="277">
-        <v>1882475.6776895099</v>
+        <v>2036121.5323853511</v>
       </c>
       <c r="D68" s="118">
-        <v>2147128.177734971</v>
+        <v>2320324.0144922468</v>
       </c>
       <c r="E68" s="118">
-        <v>2463236.1880812659</v>
+        <v>2659596.6334090345</v>
       </c>
       <c r="F68" s="118">
-        <v>3296275.7952884985</v>
+        <v>3553009.655774218</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18492,19 +18590,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>1658527.1827458795</v>
+        <v>1797862.3697535563</v>
       </c>
       <c r="C69" s="277">
-        <v>1896974.2864320837</v>
+        <v>2054314.0659700555</v>
       </c>
       <c r="D69" s="118">
-        <v>2187813.1280133422</v>
+        <v>2366873.5929891476</v>
       </c>
       <c r="E69" s="118">
-        <v>2544465.2617603345</v>
+        <v>2749890.6059227362</v>
       </c>
       <c r="F69" s="118">
-        <v>3527758.9397310656</v>
+        <v>3804851.3817301556</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18601,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18632,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>89.745967290959314</v>
+        <v>106.61113090322245</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>90.524603249490028</v>
+        <v>107.54415965215033</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>91.303239208020671</v>
+        <v>108.47718840107815</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>92.081875166551356</v>
+        <v>109.41021715000599</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>93.639147083612727</v>
+        <v>111.2762746478617</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18663,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>89.649610192935029</v>
+        <v>106.49584905759032</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>91.160543483157696</v>
+        <v>108.30499995714209</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>92.685996791255079</v>
+        <v>110.13152263825978</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>94.225970117227163</v>
+        <v>111.97541710094347</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>97.349476822795467</v>
+        <v>115.71532137100861</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18694,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.559766744893693</v>
+        <v>106.38836015723402</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>91.759424262648949</v>
+        <v>109.02150224902246</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>94.00106694034514</v>
+        <v>111.70487547921577</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>96.285100932328419</v>
+        <v>114.43896577177385</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>100.98196747654076</v>
+        <v>120.06124123982377</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18725,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>89.475996630169846</v>
+        <v>106.28813740631907</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>92.323405229815535</v>
+        <v>109.69625032808933</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>95.251763026193004</v>
+        <v>113.20121104823686</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>98.262634489022375</v>
+        <v>116.80489130180207</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>104.53825203265502</v>
+        <v>124.3159879645379</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18756,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>89.397889297094025</v>
+        <v>106.33146933591129</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>92.854520173254485</v>
+        <v>110.47120641181213</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>96.44123622671971</v>
+        <v>114.7666050380908</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>100.16180424510141</v>
+        <v>119.22217180779437</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.01992922045925</v>
+        <v>128.63227390533626</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18787,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>89.325061946906757</v>
+        <v>106.2443385327403</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>93.354684362413764</v>
+        <v>111.06960395623415</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>97.572483466381428</v>
+        <v>116.12003174280073</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>101.98571552599783</v>
+        <v>121.404303306586</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>111.42856422949833</v>
+        <v>132.71037238469455</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18819,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>89.257157657687884</v>
+        <v>106.29063122534833</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>93.82570145430266</v>
+        <v>111.76452777724455</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>98.648354967038742</v>
+        <v>117.54254639795579</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>103.73735060228998</v>
+        <v>123.63932273080364</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>114.76568941317295</v>
+        <v>136.85055235863646</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18850,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>89.193843635106148</v>
+        <v>106.21488218840894</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>94.269269997713238</v>
+        <v>112.29521416566011</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>99.671561429202342</v>
+        <v>118.76671287701663</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>105.4195735660018</v>
+        <v>125.65193801289236</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>118.03280497760963</v>
+        <v>140.75933666082349</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18882,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>89.134809581416889</v>
+        <v>106.26316610242866</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>94.686989558407546</v>
+        <v>112.91871548029368</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>100.64468086174951</v>
+        <v>120.05966971441283</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>107.03513501366906</v>
+        <v>127.718636248282</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>121.23137965607914</v>
+        <v>144.73065724435708</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18914,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>89.079766174713626</v>
+        <v>106.19731204865639</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>95.080366487359782</v>
+        <v>113.38935250993184</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>101.57016507731886</v>
+        <v>121.16692108106692</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>108.58667654382973</v>
+        <v>129.57490397364137</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>124.36285136926607</v>
+        <v>148.47715694228191</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18946,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>88.855580048810538</v>
+        <v>106.23973904395731</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.728967412976587</v>
+        <v>115.69135484577937</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>105.56079108882214</v>
+        <v>126.29087298321522</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>115.46944161311133</v>
+        <v>138.17998113281578</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>139.06191611859751</v>
+        <v>166.47882626743919</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18978,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>88.69759273034289</v>
+        <v>106.22439679553885</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>97.950024318263047</v>
+        <v>117.34120165601598</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>108.66574661220133</v>
+        <v>130.21109926162984</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>121.0923701655208</v>
+        <v>145.1304551410629</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>152.2824713251714</v>
+        <v>182.55871409484587</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19010,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>88.586256702316831</v>
+        <v>106.31010944143802</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>98.854415394829914</v>
+        <v>118.66734879280753</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>111.08159534730522</v>
+        <v>133.37340400857894</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>125.68606545909007</v>
+        <v>150.92906302324241</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>164.17323328524898</v>
+        <v>197.1587128841112</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19042,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>88.507796536926008</v>
+        <v>106.33863028425927</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>99.524263962765332</v>
+        <v>119.60872130098572</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>112.96127609215253</v>
+        <v>135.78211158414766</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>129.43892062228045</v>
+        <v>155.60132392537767</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.86795962479957</v>
+        <v>210.19026102572866</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19105,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>174.86795962479957</v>
+        <v>210.19026102572866</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19133,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>129.43892062228045</v>
+        <v>155.60132392537767</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19161,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>112.96127609215253</v>
+        <v>135.78211158414766</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19189,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>99.524263962765332</v>
+        <v>119.60872130098572</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19217,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>88.507796536926008</v>
+        <v>106.33863028425927</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19400,7 +19498,7 @@
       </c>
       <c r="C6" s="446" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
-        <v>1000000 HKD</v>
+        <v>1000000 CNY</v>
       </c>
       <c r="D6" s="469"/>
       <c r="E6" s="469"/>
@@ -19439,7 +19537,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19467,9 +19565,9 @@
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="249" t="e">
+      <c r="C12" s="249">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>5.3768659363842009E-2</v>
       </c>
       <c r="D12" s="469"/>
       <c r="E12" s="469"/>
@@ -19480,9 +19578,9 @@
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="249" t="e">
+      <c r="C13" s="249">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>5.0952518792346746E-2</v>
       </c>
       <c r="D13" s="469"/>
       <c r="E13" s="469"/>
@@ -19493,9 +19591,9 @@
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="249" t="e">
+      <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>#VALUE!</v>
+        <v>6.4892940159722023E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19577,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>129.43892062228045</v>
+        <v>155.60132392537767</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19601,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>112.96127609215253</v>
+        <v>135.78211158414766</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19624,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>99.524263962765332</v>
+        <v>119.60872130098572</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19640,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>112.89755196583133</v>
+        <v>135.70260648160317</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19687,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>174.86795962479957</v>
+        <v>210.19026102572866</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19710,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>88.507796536926008</v>
+        <v>106.33863028425927</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19766,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19755880386409505</v>
+        <v>0.2669054568882856</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19775,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19786,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>1.7354863351611165E-2</v>
+        <v>3.5564309549845491E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19795,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.97362534323128</v>
+        <v>145.40755585335478</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19821,7 +19919,7 @@
     <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>1-stage DCF</v>
+        <v>2-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
         <v>251</v>
@@ -19833,7 +19931,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -19898,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.96976544293689</v>
+        <v>145.41634829911979</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19914,7 +20012,7 @@
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E49" s="222" t="s">
         <v>254</v>
@@ -19926,7 +20024,7 @@
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E50" s="126"/>
     </row>
@@ -19936,7 +20034,7 @@
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E51" s="221" t="s">
         <v>247</v>
@@ -19965,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.8222826704399913E-2</v>
+        <v>9.1523827165210625E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20043,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.748214443885395</v>
+        <v>67.008090255002216</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>65.062158966285907</v>
+        <v>76.32203477740272</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20055,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46217897676713493</v>
+        <v>0.47511644543166387</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20068,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.876462292119172</v>
+        <v>83.989923958616515</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>80.585842383718784</v>
+        <v>94.699304050216128</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20080,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33385610164961688</v>
+        <v>0.34873189020712592</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20114,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.709103245439934</v>
+        <v>104.22237688077243</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>98.989253156467655</v>
+        <v>116.50252679180015</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20126,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18172863815884388</v>
+        <v>0.19878629340765264</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20139,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>98.061558949103656</v>
+        <v>117.86777133861143</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>111.35854885541431</v>
+        <v>131.16476124492209</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20151,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>7.9480766659151381E-2</v>
+        <v>9.7950856300732525E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20385,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19755880386409505</v>
+        <v>0.2669054568882856</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20295,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20323,7 +20421,7 @@
       </c>
       <c r="E15" s="344" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -20339,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20355,7 +20453,7 @@
       </c>
       <c r="E17" s="344" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -20365,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.97362534323128</v>
+        <v>145.40755585335478</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20381,7 +20479,7 @@
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="343" t="s">
         <v>363</v>
@@ -20417,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>65.062158966285907</v>
+        <v>76.32203477740272</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20433,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>80.585842383718784</v>
+        <v>94.699304050216128</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20449,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>98.989253156467655</v>
+        <v>116.50252679180015</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20465,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>111.35854885541431</v>
+        <v>131.16476124492209</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20486,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20531,7 +20629,7 @@
       </c>
       <c r="D34" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -20557,7 +20655,7 @@
       </c>
       <c r="D37" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -20566,11 +20664,11 @@
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
-        <v>-202343.60953731713</v>
+        <v>-191101</v>
       </c>
       <c r="D38" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -20592,7 +20690,7 @@
       </c>
       <c r="D41" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -20614,7 +20712,7 @@
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
@@ -20629,7 +20727,7 @@
       </c>
       <c r="D45" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
@@ -20644,7 +20742,7 @@
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -20658,11 +20756,11 @@
       </c>
       <c r="C49" s="373">
         <f>Normalized_FCF!C13</f>
-        <v>-174.26602854031819</v>
+        <v>-193.8560225780364</v>
       </c>
       <c r="D49" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -20684,17 +20782,17 @@
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20706,26 +20804,26 @@
       </c>
       <c r="D55" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20737,7 +20835,7 @@
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -20746,11 +20844,11 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>131191.99159250123</v>
+        <v>131172.40159846353</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -20759,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4645150639706004E-2</v>
+        <v>8.3590084922278637E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20776,7 +20874,7 @@
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.83976961030735076</v>
+        <v>0.83989502603092137</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20796,7 +20894,7 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.11683147612363115</v>
+        <v>0.1141273682688253</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
@@ -20810,7 +20908,7 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.16099692826836479</v>
+        <v>0.15727059464000756</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
@@ -20860,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20883,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20901,7 +20999,7 @@
       </c>
       <c r="D78" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -20910,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.2473398407265082</v>
+        <v>-4.7570206216136892</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20950,7 +21048,7 @@
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -20963,7 +21061,7 @@
       </c>
       <c r="D85" s="391" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -20972,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.0004263853340207</v>
+        <v>4.4804775515741033</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20994,7 +21092,7 @@
       </c>
       <c r="D89" s="343" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -21003,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.129284893283694</v>
+        <v>13.58479908047774</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21016,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>11.882371437891207</v>
+        <v>13.308256010438154</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21038,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21127,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21161,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.2888383928647593</v>
+        <v>1.4434990000085306</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21175,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>129.64256108709142</v>
+        <v>145.17997398382496</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21187,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21238,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>174.87 HKD</v>
+        <v>210.19 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21261,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>129.44 HKD</v>
+        <v>155.6 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21283,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>112.96 HKD</v>
+        <v>135.78 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21305,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>99.52 HKD</v>
+        <v>119.61 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21327,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>88.51 HKD</v>
+        <v>106.34 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21349,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.97362534323128</v>
+        <v>145.40755585335478</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21357,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21376,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21456,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.748214443885395</v>
+        <v>67.008090255002216</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>65.062158966285907</v>
+        <v>76.32203477740272</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21477,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.876462292119172</v>
+        <v>83.989923958616515</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>80.585842383718784</v>
+        <v>94.699304050216128</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21517,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.709103245439934</v>
+        <v>104.22237688077243</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>98.989253156467655</v>
+        <v>116.50252679180015</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21538,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>98.061558949103656</v>
+        <v>117.86777133861143</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>111.35854885541431</v>
+        <v>131.16476124492209</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21560,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21574,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21617,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21656,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21676,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385E9DFE-8BB2-4684-9766-5A1348276DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A76C4-A96A-4B35-AA52-FF846E492883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>81.2</v>
+        <v>80.849999999999994</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1757542.0568944002</v>
+        <v>1749966.4445801999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2669054568882856</v>
+        <v>0.26995508046657685</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1200000000000001</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>145.40755585335478</v>
+        <v>145.83104162734193</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,13 +5562,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>76.32203477740272</v>
+        <v>76.517189511959018</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5577,13 +5577,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>94.699304050216128</v>
+        <v>94.943916771652752</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>116.50252679180015</v>
+        <v>116.80606462159936</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>131.16476124492209</v>
+        <v>131.50803999739497</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.3590084922278637E-2</v>
+        <v>8.4196448878206431E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2684729064039407E-2</v>
+        <v>6.2956091527520103E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7570206216136892</v>
+        <v>-4.7708749949163298</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.4804775515741033</v>
+        <v>4.4935265193022591</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.58479908047774</v>
+        <v>13.624363524837548</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>13.308256010438154</v>
+        <v>13.347015049223478</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4434990000085306</v>
+        <v>1.4477030545205587</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>210.19 HKD</v>
+        <v>210.8 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-8.8130818492621346E-2</v>
+        <v>-8.8210336783332843E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>155.6 HKD</v>
+        <v>156.05 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.1115382217860131E-2</v>
+        <v>1.1018299838509224E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>135.78 HKD</v>
+        <v>136.18 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9758693681778934E-2</v>
+        <v>5.9652160428142066E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>119.61 HKD</v>
+        <v>119.96 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.1072641851985464</v>
+        <v>0.10714786570188685</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>106.34 HKD</v>
+        <v>106.65 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.15333444846924818</v>
+        <v>0.15320809866972171</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>145.40755585335478</v>
+        <v>145.83104162734193</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,19 +6586,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>9.3139445224005097</v>
+        <v>9.313944522400508</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>67.008090255002216</v>
+        <v>67.203244989558513</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>76.32203477740272</v>
+        <v>76.517189511959018</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6607,19 +6607,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>10.709380091599613</v>
+        <v>10.709380091599607</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>83.989923958616515</v>
+        <v>84.234536680053139</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>94.699304050216128</v>
+        <v>94.943916771652752</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>104.22237688077243</v>
+        <v>104.52591471057164</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>116.50252679180015</v>
+        <v>116.80606462159936</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>117.86777133861143</v>
+        <v>118.21105009108433</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>131.16476124492209</v>
+        <v>131.50803999739497</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>73.978314723089511</v>
+        <v>74.193769578134095</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4434990000085306</v>
+        <v>1.4477030545205587</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-102963.84000000001</v>
+        <v>-103263.71245999145</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7570206216136892</v>
+        <v>-4.7708749949163298</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>96978.174037718403</v>
+        <v>97260.613810887007</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>4.4804775515741033</v>
+        <v>4.4935265193022582</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>294037.63199999998</v>
+        <v>294893.98883399041</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.58479908047774</v>
+        <v>13.624363524837548</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>288051.96603771835</v>
+        <v>288890.89018488594</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>13.308256010438154</v>
+        <v>13.347015049223476</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2684729064039407E-2</v>
+        <v>6.2956091527520103E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.2684729064039407E-2</v>
+        <v>6.2956091527520103E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9482758620689656E-2</v>
+        <v>5.9740259740259746E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4310344827586204E-2</v>
+        <v>5.454545454545455E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.05</v>
+        <v>5.0216450216450229E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>6.787514895689025</v>
+        <v>6.8072828918029895</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.4932297218053794</v>
+        <v>6.5121406401429951</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9335536796146586</v>
+        <v>5.9508345943357615</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.7259674149658082</v>
+        <v>5.7426437542957771</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.2336045949676029</v>
+        <v>5.2488469740835662</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3590084922278637E-2</v>
+        <v>8.4196448878206431E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9965883273465266E-2</v>
+        <v>8.0545957206468718E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.3073321177520426E-2</v>
+        <v>7.3603396343052088E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0516840085785806E-2</v>
+        <v>7.1028370492217413E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.4453258558714324E-2</v>
+        <v>6.4920803637397231E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8818028539685281E-2</v>
+        <v>7.9159232126437176E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5067904908705782E-2</v>
+        <v>7.5392874194024864E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1460025384499901E-2</v>
+        <v>7.1769376143740168E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6175372329646681E-2</v>
+        <v>6.6461845802935196E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>13.308256010438154</v>
+        <v>13.347015049223478</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1200000000000001</v>
+        <v>1.1232618942260741</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>3142363.4248202858</v>
+        <v>3151515.2615271141</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>145.41634829911979</v>
+        <v>145.83985968027483</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>106.61113090322245</v>
+        <v>106.9216257535157</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>107.54415965215033</v>
+        <v>107.85737186055866</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>108.47718840107815</v>
+        <v>108.79311796760156</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>109.41021715000599</v>
+        <v>109.72886407464449</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>111.2762746478617</v>
+        <v>111.60035628873035</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>106.49584905759032</v>
+        <v>106.80600816039551</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>108.30499995714209</v>
+        <v>108.62042804108418</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>110.13152263825978</v>
+        <v>110.45227029701201</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>111.97541710094347</v>
+        <v>112.30153492817901</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>115.71532137100861</v>
+        <v>116.05233131623039</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>106.38836015723402</v>
+        <v>106.69820620876828</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>109.02150224902246</v>
+        <v>109.33901707822247</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>111.70487547921577</v>
+        <v>112.03020537952824</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>114.43896577177385</v>
+        <v>114.77225845185316</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>120.06124123982377</v>
+        <v>120.41090826623044</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>106.28813740631907</v>
+        <v>106.59769156855641</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>109.69625032808933</v>
+        <v>110.01573029734573</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>113.20121104823686</v>
+        <v>113.53089888457866</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>116.80489130180207</v>
+        <v>117.14507451654721</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>124.3159879645379</v>
+        <v>124.67804653895773</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>106.33146933591129</v>
+        <v>106.64114969830128</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>110.47120641181213</v>
+        <v>110.79294336747475</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>114.7666050380908</v>
+        <v>115.10085193659067</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>119.22217180779437</v>
+        <v>119.5693951237228</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>128.63227390533626</v>
+        <v>129.00690325492431</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>106.2443385327403</v>
+        <v>106.55376513489477</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>111.06960395623415</v>
+        <v>111.39308368823161</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>116.12003174280073</v>
+        <v>116.45822036875911</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>121.404303306586</v>
+        <v>121.75788187442198</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>132.71037238469455</v>
+        <v>133.09687881096397</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>106.29063122534833</v>
+        <v>106.60019265059809</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>111.76452777724455</v>
+        <v>112.09003140924142</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>117.54254639795579</v>
+        <v>117.88487796350358</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>123.63932273080364</v>
+        <v>123.99941058163517</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>136.85055235863646</v>
+        <v>137.24911666807725</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>106.21488218840894</v>
+        <v>106.52422300174243</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>112.29521416566011</v>
+        <v>112.62226337164468</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>118.76671287701663</v>
+        <v>119.11260971182318</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>125.65193801289236</v>
+        <v>126.01788741565956</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>140.75933666082349</v>
+        <v>141.16928493539487</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>106.26316610242866</v>
+        <v>106.57264753810173</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>112.91871548029368</v>
+        <v>113.24758057497303</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>120.05966971441283</v>
+        <v>120.40933216390016</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>127.718636248282</v>
+        <v>128.0906047144787</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>144.73065724435708</v>
+        <v>145.15217161507249</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>106.19731204865639</v>
+        <v>106.50660169061719</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>113.38935250993184</v>
+        <v>113.71958829051256</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>121.16692108106692</v>
+        <v>121.51980829558968</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>129.57490397364137</v>
+        <v>129.95227864428043</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>148.47715694228191</v>
+        <v>148.90958263954434</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>106.23973904395731</v>
+        <v>106.54915225053509</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>115.69135484577937</v>
+        <v>116.02829499075985</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>126.29087298321522</v>
+        <v>126.65868322374183</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>138.17998113281578</v>
+        <v>138.58241727800879</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>166.47882626743919</v>
+        <v>166.96368012651538</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>106.22439679553885</v>
+        <v>106.53376531926703</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>117.34120165601598</v>
+        <v>117.68294682401807</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>130.21109926162984</v>
+        <v>130.59032679096222</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>145.1304551410629</v>
+        <v>145.55313388539517</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>182.55871409484587</v>
+        <v>183.09039910861861</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>106.31010944143802</v>
+        <v>106.61972759515258</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>118.66734879280753</v>
+        <v>119.01295623910286</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.37340400857894</v>
+        <v>133.76184145183558</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>150.92906302324241</v>
+        <v>151.36862966540517</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>197.1587128841112</v>
+        <v>197.73291901551912</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>106.33863028425927</v>
+        <v>106.64833150223502</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>119.60872130098572</v>
+        <v>119.95707040580695</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>135.78211158414766</v>
+        <v>136.17756416073738</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>155.60132392537767</v>
+        <v>156.05449808616487</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>210.19026102572866</v>
+        <v>210.80242031038654</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>210.19026102572866</v>
+        <v>210.80242031038654</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>155.60132392537767</v>
+        <v>156.05449808616487</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>135.78211158414766</v>
+        <v>136.17756416073738</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>119.60872130098572</v>
+        <v>119.95707040580695</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>106.33863028425927</v>
+        <v>106.64833150223502</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>155.60132392537767</v>
+        <v>156.05449808616487</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>135.78211158414766</v>
+        <v>136.17756416073738</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>119.60872130098572</v>
+        <v>119.95707040580695</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>135.70260648160317</v>
+        <v>136.09782750709027</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>210.19026102572866</v>
+        <v>210.80242031038654</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>106.33863028425927</v>
+        <v>106.64833150223502</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>81.2</v>
+        <v>80.849999999999994</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2669054568882856</v>
+        <v>0.26995508046657685</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.5564309549845491E-2</v>
+        <v>3.5462548049219778E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>145.40755585335478</v>
+        <v>145.83104162734193</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>145.41634829911979</v>
+        <v>145.83985968027483</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.1523827165210625E-2</v>
+        <v>9.1523827165210597E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20137,23 +20137,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>9.3139445224005097</v>
+        <v>9.313944522400508</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>67.008090255002216</v>
+        <v>67.203244989558513</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>76.32203477740272</v>
+        <v>76.517189511959018</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47511644543166387</v>
+        <v>0.47530245510080227</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20162,23 +20162,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>10.709380091599613</v>
+        <v>10.709380091599607</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>83.989923958616515</v>
+        <v>84.234536680053139</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>94.699304050216128</v>
+        <v>94.943916771652752</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34873189020712592</v>
+        <v>0.34894576825232204</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>104.22237688077243</v>
+        <v>104.52591471057164</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>116.50252679180015</v>
+        <v>116.80606462159936</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19878629340765264</v>
+        <v>0.19903154144584168</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>117.86777133861143</v>
+        <v>118.21105009108433</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>131.16476124492209</v>
+        <v>131.50803999739497</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.7950856300732525E-2</v>
+        <v>9.8216411746876897E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>81.2</v>
+        <v>80.849999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1757542.0568944002</v>
+        <v>1749966.4445801999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2669054568882856</v>
+        <v>0.26995508046657685</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1200000000000001</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>145.40755585335478</v>
+        <v>145.83104162734193</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,14 +20515,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>76.32203477740272</v>
+        <v>76.517189511959018</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20531,14 +20531,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>94.699304050216128</v>
+        <v>94.943916771652752</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>116.50252679180015</v>
+        <v>116.80606462159936</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>131.16476124492209</v>
+        <v>131.50803999739497</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.3590084922278637E-2</v>
+        <v>8.4196448878206431E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.2684729064039407E-2</v>
+        <v>6.2956091527520103E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7570206216136892</v>
+        <v>-4.7708749949163298</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.4804775515741033</v>
+        <v>4.4935265193022591</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.58479908047774</v>
+        <v>13.624363524837548</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>13.308256010438154</v>
+        <v>13.347015049223478</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4434990000085306</v>
+        <v>1.4477030545205587</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>145.17997398382496</v>
+        <v>145.60279694711016</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>210.19 HKD</v>
+        <v>210.8 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>155.6 HKD</v>
+        <v>156.05 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>135.78 HKD</v>
+        <v>136.18 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>119.61 HKD</v>
+        <v>119.96 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>106.34 HKD</v>
+        <v>106.65 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>145.40755585335478</v>
+        <v>145.83104162734193</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21550,19 +21550,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>9.3139445224005097</v>
+        <v>9.313944522400508</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>67.008090255002216</v>
+        <v>67.203244989558513</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>76.32203477740272</v>
+        <v>76.517189511959018</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21571,19 +21571,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>10.709380091599613</v>
+        <v>10.709380091599607</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>83.989923958616515</v>
+        <v>84.234536680053139</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>94.699304050216128</v>
+        <v>94.943916771652752</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>104.22237688077243</v>
+        <v>104.52591471057164</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>116.50252679180015</v>
+        <v>116.80606462159936</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>117.86777133861143</v>
+        <v>118.21105009108433</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>131.16476124492209</v>
+        <v>131.50803999739497</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A76C4-A96A-4B35-AA52-FF846E492883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D920D52-8678-42F4-91C6-D86007F61FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.26995508046657685</v>
+        <v>0.19048841663164309</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,18 +5447,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>2-stage DCF Valuation Conclusion</v>
+        <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>145.83104162734193</v>
+        <v>119.8858252143587</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>76.517189511959018</v>
+        <v>63.629474132076922</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>94.943916771652752</v>
+        <v>78.886572170155901</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>116.80606462159936</v>
+        <v>96.981546117472632</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>131.50803999739497</v>
+        <v>109.14707603879739</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
-        <v>160987.97999999998</v>
+        <v>135679.51550364122</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>989.94206765508</v>
+        <v>507.62526607571937</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-4525.9779323449202</v>
+        <v>-5008.294733924281</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-36192.744446613491</v>
+        <v>-34661.355192429241</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>125485.1812230568</v>
+        <v>118134.44704364182</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.4196448878206431E-2</v>
+        <v>6.6620470208222565E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2956091527520103E-2</v>
+        <v>5.6660482374768097E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.83989502603092137</v>
+        <v>1.0614782273563756</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5941,11 +5941,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.1141273682688253</v>
+        <v>9.6671315574961933E-2</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11539664872608364</v>
+        <v>0.11027130711998644</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.15901969737764152</v>
+        <v>0.15195683827249326</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.57104884476468376</v>
+        <v>0.67756727799881356</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>86587.65539082</v>
+        <v>166973.7889873801</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.4935265193022591</v>
+        <v>8.6652207575852511</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>13.347015049223478</v>
+        <v>17.518709287506468</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,11 +6365,11 @@
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>210.8 HKD</v>
+        <v>151.51 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-8.8210336783332843E-2</v>
+        <v>-4.2374743671833602E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>156.05 HKD</v>
+        <v>131.78 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.1018299838509224E-2</v>
+        <v>4.830060428741568E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>136.18 HKD</v>
+        <v>115.76 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9652160428142066E-2</v>
+        <v>5.0865119237549494E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>119.96 HKD</v>
+        <v>102.7 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.10714786570188685</v>
+        <v>9.5382641270521373E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>106.65 HKD</v>
+        <v>91.99 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.15320809866972171</v>
+        <v>0.13810364947030609</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>145.83104162734193</v>
+        <v>119.8858252143587</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>5.09</v>
+        <v>4.5810000000000004</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,15 +6586,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>9.313944522400508</v>
+        <v>8.3825500701604572</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>67.203244989558513</v>
+        <v>55.246924061916467</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>76.517189511959018</v>
+        <v>63.629474132076922</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,15 +6607,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>10.709380091599607</v>
+        <v>9.6384420824396493</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>84.234536680053139</v>
+        <v>69.248130087716248</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>94.943916771652752</v>
+        <v>78.886572170155901</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>12.280149911027722</v>
+        <v>11.052134919924953</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>104.52591471057164</v>
+        <v>85.92941119754768</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>116.80606462159936</v>
+        <v>96.981546117472632</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>13.296989906310651</v>
+        <v>11.967290915679589</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>118.21105009108433</v>
+        <v>97.17978512311781</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>131.50803999739497</v>
+        <v>109.14707603879739</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.57104884476468376</v>
+        <v>0.67756727799881356</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.12990748444019815</v>
+        <v>0.10948509664599118</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
-        <v>1.2489743823502599E-2</v>
+        <v>8.975012633808635E-3</v>
       </c>
       <c r="D55" s="89">
         <f>Normalized_FCF!G9/G40</f>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>86587.65539082</v>
+        <v>166973.7889873801</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-82495.17230459</v>
+        <v>-84604.211012619897</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>3.0496087585721945</v>
+        <v>2.9735872126089995</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10361,7 +10361,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>164990.34460918</v>
+        <v>84604.211012619897</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10374,7 +10374,7 @@
       <c r="C76" s="230"/>
       <c r="D76" s="248">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="223" t="s">
         <v>261</v>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>97260.613810887007</v>
+        <v>187555.29450406937</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>4.4935265193022582</v>
+        <v>8.6652207575852511</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>288890.89018488594</v>
+        <v>379185.57087806833</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>13.347015049223476</v>
+        <v>17.518709287506468</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C5" s="266">
         <f>C26</f>
-        <v>-811792.02</v>
+        <v>-837100.48449635878</v>
       </c>
       <c r="E5" s="237"/>
       <c r="G5" s="270">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
-        <v>228966.97999999998</v>
+        <v>203658.51550364122</v>
       </c>
       <c r="E6" s="237"/>
       <c r="G6" s="267">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
-        <v>160987.97999999998</v>
+        <v>135679.51550364122</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="241"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C9" s="300">
         <f>C61</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="D9" s="55"/>
       <c r="E9" s="236"/>
@@ -11012,24 +11012,24 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-4525.9779323449202</v>
+        <v>-5008.294733924281</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>11814.181223056808</v>
+        <v>4463.4470436418151</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>10130.138577182464</v>
+        <v>3377.2406789970064</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>7985.4215804155847</v>
+        <v>2959.5707693737058</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>8292.2434114547868</v>
+        <v>2946.8649247156673</v>
       </c>
       <c r="K10" s="266" t="str">
         <f t="shared" si="6"/>
@@ -11067,24 +11067,24 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>167559.00206765506</v>
+        <v>138645.42076971696</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>165501.1812230568</v>
+        <v>158150.44704364182</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>153434.13857718246</v>
+        <v>146681.24067899701</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>148070.4215804156</v>
+        <v>143044.57076937371</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>137178.24341145478</v>
+        <v>131832.86492471566</v>
       </c>
       <c r="K11" s="267" t="str">
         <f t="shared" si="7"/>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-36192.744446613491</v>
+        <v>-34661.355192429241</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11234,26 +11234,26 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>125485.1812230568</v>
+        <v>118134.44704364182</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>114669.13857718246</v>
+        <v>107916.24067899701</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>110657.4215804156</v>
+        <v>105631.57076937371</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>101142.24341145478</v>
+        <v>95796.864924715657</v>
       </c>
       <c r="K14" s="267" t="str">
         <f t="shared" si="8"/>
@@ -11452,26 +11452,26 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>125485.1812230568</v>
+        <v>118134.44704364182</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>114669.13857718246</v>
+        <v>107916.24067899701</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>110657.4215804156</v>
+        <v>105631.57076937371</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>101142.24341145478</v>
+        <v>95796.864924715657</v>
       </c>
       <c r="K19" s="271" t="str">
         <f t="shared" si="9"/>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
-        <v>-489156.73</v>
+        <v>-643392.11078693799</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="236"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
-        <v>-322635.28999999998</v>
+        <v>-193708.37370942079</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="234"/>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
-        <v>-811792.02</v>
+        <v>-837100.48449635878</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="240"/>
@@ -11810,7 +11810,8 @@
         <v>40</v>
       </c>
       <c r="C29" s="60">
-        <v>0.47</v>
+        <f>AVERAGE(G29:J29)</f>
+        <v>0.6181950968350387</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="235"/>
@@ -11867,7 +11868,8 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C30" s="60">
-        <v>0.31</v>
+        <f>AVERAGE(G30:J30)</f>
+        <v>0.18612221821710961</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="235"/>
@@ -11981,7 +11983,7 @@
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
-        <v>0.78</v>
+        <v>0.80431731505214832</v>
       </c>
       <c r="E32" s="237"/>
       <c r="G32" s="29">
@@ -12180,8 +12182,7 @@
         <v>142</v>
       </c>
       <c r="C41" s="457">
-        <f>25%*60%+16.5%*40%</f>
-        <v>0.216</v>
+        <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
@@ -12190,19 +12191,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>0.24086232923180179</v>
+        <v>0.25205746012845448</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.25154766962493769</v>
+        <v>0.26312839884184647</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.25175858623293434</v>
+        <v>0.26060408863823398</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>0.26154293208425849</v>
+        <v>0.27214761676072546</v>
       </c>
       <c r="K41" s="6" t="str">
         <f t="shared" si="16"/>
@@ -12328,24 +12329,24 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>989.94206765508</v>
+        <v>507.62526607571937</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>15087.181223056808</v>
+        <v>7736.4470436418151</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>13860.138577182464</v>
+        <v>7107.2406789970064</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>10315.421580415585</v>
+        <v>5289.5707693737058</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>10971.243411454787</v>
+        <v>5625.8649247156673</v>
       </c>
       <c r="K46" s="274" t="str">
         <f t="shared" si="17"/>
@@ -12440,24 +12441,24 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-4525.9779323449202</v>
+        <v>-5008.294733924281</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>11814.181223056808</v>
+        <v>4463.4470436418151</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>10130.138577182464</v>
+        <v>3377.2406789970064</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>7985.4215804155847</v>
+        <v>2959.5707693737058</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>8292.2434114547868</v>
+        <v>2946.8649247156673</v>
       </c>
       <c r="K48" s="267" t="str">
         <f t="shared" si="18"/>
@@ -12557,7 +12558,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>29.186061436714088</v>
+        <v>24.597803358939437</v>
       </c>
       <c r="E53" s="237"/>
       <c r="G53" s="40">
@@ -12681,7 +12682,7 @@
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="E57" s="237"/>
       <c r="G57" s="266">
@@ -12791,7 +12792,7 @@
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="E59" s="237"/>
       <c r="G59" s="267">
@@ -12902,7 +12903,7 @@
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="E61" s="237"/>
       <c r="G61" s="267">
@@ -12995,8 +12996,7 @@
         <v>132</v>
       </c>
       <c r="C65" s="158">
-        <f>G65</f>
-        <v>5.5664518070778261E-2</v>
+        <v>0.04</v>
       </c>
       <c r="E65" s="237"/>
       <c r="G65" s="22">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
-        <v>2.4608977386884525E-2</v>
+        <v>1.7683780073758187E-2</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="240"/>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
-        <v>0.78</v>
+        <v>0.80431731505214832</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="234"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>0.21999999999999997</v>
+        <v>0.19568268494785174</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="234"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>0.1546832455928798</v>
+        <v>0.13036593054073153</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="234"/>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
-        <v>1.0662410798273183E-2</v>
+        <v>7.6619082803992085E-3</v>
       </c>
       <c r="D75" s="26"/>
       <c r="E75" s="234"/>
@@ -13405,26 +13405,26 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>4.3487281227881959E-3</v>
+        <v>4.8121560648760001E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>1.1351505221724538E-2</v>
+        <v>4.2886461165762826E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>1.0036706872902614E-2</v>
+        <v>3.3460919094122875E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>8.51997322022577E-3</v>
+        <v>3.1576872234608637E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>9.7756147439278934E-3</v>
+        <v>3.474019608085827E-3</v>
       </c>
       <c r="K76" s="6" t="str">
         <f t="shared" si="28"/>
@@ -13462,26 +13462,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.15901969737764152</v>
+        <v>0.15195683827249326</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.15201899376423123</v>
+        <v>0.14532837880074093</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.15798239502679151</v>
+        <v>0.1526201090300266</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.16171759466041555</v>
+        <v>0.15541599952457349</v>
       </c>
       <c r="K77" s="62" t="str">
         <f t="shared" si="29"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.4775336505966793E-2</v>
+        <v>3.3303920689063696E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13634,26 +13634,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>0.12057083457655116</v>
+        <v>0.11350797547140291</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1136115288550706</v>
+        <v>0.10692091389158029</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1180649335780351</v>
+        <v>0.11270264758127017</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11923523669856904</v>
+        <v>0.11293364156272698</v>
       </c>
       <c r="K80" s="62" t="str">
         <f t="shared" si="32"/>
@@ -13857,26 +13857,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.12057083457655116</v>
+        <v>0.11350797547140291</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1136115288550706</v>
+        <v>0.10692091389158029</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1180649335780351</v>
+        <v>0.11270264758127017</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11923523669856904</v>
+        <v>0.11293364156272698</v>
       </c>
       <c r="K85" s="62" t="str">
         <f t="shared" si="35"/>
@@ -14037,24 +14037,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.83989502603092137</v>
+        <v>1.0614782273563756</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.87796062117681373</v>
+        <v>0.93259036980449961</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.91169647939400045</v>
+        <v>0.96874621723462762</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>0.86259659583296711</v>
+        <v>0.9036381307565966</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>0.8688466844385575</v>
+        <v>0.91732754421327267</v>
       </c>
       <c r="K90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14091,7 +14091,7 @@
         <v>331</v>
       </c>
       <c r="C91" s="292">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E91" s="237"/>
       <c r="G91" s="293"/>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2956091527520103E-2</v>
+        <v>5.6660482374768097E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.2956091527520103E-2</v>
+        <v>5.6660482374768097E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9740259740259746E-2</v>
+        <v>5.3766233766233774E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.454545454545455E-2</v>
+        <v>4.9090909090909095E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0216450216450229E-2</v>
+        <v>4.5194805194805204E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14250,22 +14250,22 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>1.2433874062957928E-2</v>
+        <v>-0.12333209699080028</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>7.8646400063074884E-2</v>
+        <v>7.8191364564092147E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>3.6224094856472489E-2</v>
+        <v>2.542333407037578E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>7.9401644882495237E-2</v>
+        <v>8.5044847133228796E-2</v>
       </c>
       <c r="J96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -14866,19 +14866,19 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>2.8241820790779029</v>
+        <v>2.99991246303526</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>3.156324399841786</v>
+        <v>3.3538325438576968</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>2.537109540330079</v>
+        <v>2.6578228265956949</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.1120923303976435</v>
+        <v>3.2857442698919752</v>
       </c>
       <c r="K113" s="251" t="str">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -14924,7 +14924,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>15yrs Projection</v>
+        <v>31yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14979,27 +14979,27 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.15901969737764152</v>
+        <v>0.15195683827249326</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.15201899376423123</v>
+        <v>0.14532837880074093</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.15798239502679151</v>
+        <v>0.1526201090300266</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.16171759466041555</v>
+        <v>0.15541599952457349</v>
       </c>
       <c r="K116" s="22" t="str">
         <f t="shared" si="44"/>
@@ -15153,29 +15153,29 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.11683147612363115</v>
+        <v>9.6671315574961933E-2</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <f>AVERAGE(G119:J119)</f>
-        <v>0.1141273682688253</v>
+        <f>C119</f>
+        <v>9.6671315574961933E-2</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11539664872608364</v>
+        <v>0.11027130711998644</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11399394389772728</v>
+        <v>0.10897687617543807</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11377578356953549</v>
+        <v>0.10991397168282234</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11334309688195475</v>
+        <v>0.10892649453579438</v>
       </c>
       <c r="K119" s="99" t="str">
         <f t="shared" si="47"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>6.8072828918029895</v>
+        <v>5.3862650163347947</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.5121406401429951</v>
+        <v>6.1306691841663188</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.9508345943357615</v>
+        <v>5.6003882674237397</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.7426437542957771</v>
+        <v>5.4818237355582342</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.2488469740835662</v>
+        <v>4.971444844675446</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.4196448878206431E-2</v>
+        <v>6.6620470208222565E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.0545957206468718E-2</v>
+        <v>7.5827695536998377E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.3603396343052088E-2</v>
+        <v>6.9268871582235506E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.1028370492217413E-2</v>
+        <v>6.7802396234486514E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.4920803637397231E-2</v>
+        <v>6.1489732154303603E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>86587.65539082</v>
+        <v>166973.7889873801</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2548492.3739130064</v>
+        <v>2016495.4999200744</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>6571.0220676550798</v>
+        <v>2965.9052660757188</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16275,14 +16275,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>257189.25539081998</v>
+        <v>337575.38898738008</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>257189.25539081998</v>
+        <v>337575.38898738008</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="I7" s="313">
         <f>Normalized_FCF!C9</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="J7" s="313"/>
       <c r="N7" s="304"/>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>2805681.6293038265</v>
+        <v>2354070.8889074544</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>13.347015049223478</v>
+        <v>17.518709287506468</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-4525.9779323449202</v>
+        <v>-5008.294733924281</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>3151515.2615271141</v>
+        <v>2644238.1258166456</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="I10" s="306">
         <f>Normalized_FCF!C41</f>
-        <v>0.216</v>
+        <v>0.25</v>
       </c>
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>413</v>
@@ -16441,11 +16441,11 @@
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Change year</v>
+        <v>Terminal Year</v>
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>429</v>
@@ -16462,14 +16462,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E16" s="308" t="s">
         <v>400</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16478,14 +16478,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>145.83985968027483</v>
+        <v>119.89000081625294</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16570,19 +16570,19 @@
       </c>
       <c r="C21" s="277">
         <f>I4*(1+D21)</f>
-        <v>1066900.9180899311</v>
+        <v>1064469.1098419346</v>
       </c>
       <c r="D21" s="299">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>171767.77057917719</v>
+        <v>141803.97924053608</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16590,15 +16590,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>134467.2068110503</v>
+        <v>106154.71206591504</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>2.5118128298608156E-2</v>
+        <v>2.278155638522894E-2</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>125377.3490079723</v>
+        <v>98978.752509011683</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16619,19 +16619,19 @@
       </c>
       <c r="C22" s="277">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>1093699.4722324167</v>
+        <v>1088719.3728881334</v>
       </c>
       <c r="D22" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>176082.25547815082</v>
+        <v>145034.49458925423</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16639,15 +16639,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>137844.77136368572</v>
+        <v>108573.08162440246</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229385E-2</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>119838.31547421345</v>
+        <v>94390.342694858176</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16668,19 +16668,19 @@
       </c>
       <c r="C23" s="277">
         <f t="shared" si="5"/>
-        <v>1121171.1558960706</v>
+        <v>1113522.0946692757</v>
       </c>
       <c r="D23" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>180505.11216235932</v>
+        <v>148338.60610554254</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16688,15 +16688,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>141307.1740160911</v>
+        <v>111046.54540534689</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>114543.99035653504</v>
+        <v>90014.640195041691</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16725,19 +16725,19 @@
       </c>
       <c r="C24" s="277">
         <f t="shared" si="5"/>
-        <v>1149332.8768345669</v>
+        <v>1138889.8610551823</v>
       </c>
       <c r="D24" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>185039.06272820811</v>
+        <v>151717.99042464225</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16745,15 +16745,15 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>144856.545742541</v>
+        <v>113576.35854088371</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443304E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>109483.56270596269</v>
+        <v>85841.784425306425</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16782,19 +16782,19 @@
       </c>
       <c r="C25" s="277">
         <f t="shared" si="5"/>
-        <v>1178201.9674927059</v>
+        <v>1164835.5446413767</v>
       </c>
       <c r="D25" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>189686.89764606944</v>
+        <v>155174.36237815488</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16802,15 +16802,15 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>148495.07104339535</v>
+        <v>116163.80475701184</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.278155638522894E-2</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>104646.69918937043</v>
+        <v>81862.371913659881</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16839,19 +16839,19 @@
       </c>
       <c r="C26" s="277">
         <f t="shared" si="5"/>
-        <v>1207796.1956738601</v>
+        <v>1191372.3112811435</v>
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>194451.47747770834</v>
+        <v>158709.47586421482</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16859,15 +16859,15 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>152224.98928957427</v>
+        <v>118810.19702500646</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>100023.52298893694</v>
+        <v>78067.435109780447</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16888,19 +16888,19 @@
       </c>
       <c r="C27" s="277">
         <f t="shared" si="5"/>
-        <v>1238133.775475367</v>
+        <v>1218513.6267663955</v>
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>199335.73463684734</v>
+        <v>162325.1247374856</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16908,15 +16908,15 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>156048.59610080408</v>
+        <v>121516.87822767184</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765022</v>
+        <v>9.9725497982443304E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>95604.593633801283</v>
+        <v>74448.422176768421</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16937,19 +16937,19 @@
       </c>
       <c r="C28" s="277">
         <f t="shared" si="5"/>
-        <v>1269233.3784985973</v>
+        <v>1246273.2636607443</v>
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>204342.67519395295</v>
+        <v>166023.14371943197</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16957,15 +16957,15 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>159968.24475848171</v>
+        <v>124285.22184077256</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.278155638522894E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>91380.887722733212</v>
+        <v>70997.17771970146</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16986,19 +16986,19 @@
       </c>
       <c r="C29" s="277">
         <f t="shared" si="5"/>
-        <v>1301114.145340601</v>
+        <v>1274665.3082882352</v>
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>209475.38072635548</v>
+        <v>169805.40932932924</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -17006,15 +17006,15 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>163986.34765402842</v>
+        <v>127116.63262998885</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>87343.780498455497</v>
+        <v>67705.924407566403</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17035,19 +17035,19 @@
       </c>
       <c r="C30" s="277">
         <f t="shared" si="5"/>
-        <v>1333795.6973744</v>
+        <v>1303704.1678812993</v>
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>214737.01021483986</v>
+        <v>173673.8408364823</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -17055,15 +17055,15 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>168105.37777362246</v>
+        <v>130012.54736374941</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229385E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>83485.028235991776</v>
+        <v>64567.245447152869</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17084,19 +17084,19 @@
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>1367298.1488251816</v>
+        <v>1333404.5778915454</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>220130.80198787572</v>
+        <v>177630.40123413794</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -17104,15 +17104,15 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>172327.87022022629</v>
+        <v>132974.43554230395</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>79796.751409078177</v>
+        <v>61574.06786941363</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17133,19 +17133,19 @@
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>1401642.119149822</v>
+        <v>1363781.6094671043</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>225660.07571468269</v>
+        <v>181677.09823558433</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17153,15 +17153,15 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>176656.42377384385</v>
+        <v>136003.80014340498</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765022</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>76271.418600264369</v>
+        <v>58719.646590628065</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17182,19 +17182,19 @@
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>1436848.7457273602</v>
+        <v>1394850.6771003178</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>231328.23444835772</v>
+        <v>185815.98529294311</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17202,15 +17202,15 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>181093.70249096851</v>
+        <v>139102.17838497739</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765019</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>72901.831121848605</v>
+        <v>55997.549212450518</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17239,19 +17239,19 @@
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>1472939.6968682343</v>
+        <v>1426627.5464496538</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0.16099692826836479</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>237138.76672032211</v>
+        <v>190049.16263917121</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17259,15 +17259,15 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>185642.43734420667</v>
+        <v>142271.14250516295</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0.12603532767765022</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>69681.108316243073</v>
+        <v>53401.641526590771</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17289,26 +17289,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>1509937.1851502836</v>
+        <v>1459128.3423398177</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>237468.71897764431</v>
+        <v>194378.77835380108</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17316,15 +17316,15 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>185894.22861065448</v>
+        <v>145512.30056013531</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>1.3563238559561874E-3</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301814</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>65058.851716328078</v>
+        <v>50926.073691461635</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -17346,26 +17346,26 @@
     <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B36" s="117">
         <v>16</v>
       </c>
       <c r="C36" s="277">
         <f t="shared" si="5"/>
-        <v>1547863.9810897277</v>
+        <v>1492369.5569441181</v>
       </c>
       <c r="D36" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E36" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F36" s="277">
         <f t="shared" si="7"/>
-        <v>243433.4887278309</v>
+        <v>198807.02945296015</v>
       </c>
       <c r="G36" s="299">
         <f t="shared" si="2"/>
@@ -17373,15 +17373,15 @@
       </c>
       <c r="H36" s="277">
         <f t="shared" si="8"/>
-        <v>190563.54369486767</v>
+        <v>148827.29724009044</v>
       </c>
       <c r="I36" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J36" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
@@ -17389,32 +17389,32 @@
       </c>
       <c r="L36" s="277">
         <f t="shared" si="4"/>
-        <v>62184.623124194797</v>
+        <v>48565.267049642898</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B37" s="117">
         <v>17</v>
       </c>
       <c r="C37" s="277">
         <f t="shared" si="5"/>
-        <v>1586743.4271555338</v>
+        <v>1526368.05815324</v>
       </c>
       <c r="D37" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E37" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F37" s="277">
         <f t="shared" si="7"/>
-        <v>249548.08232987433</v>
+        <v>203336.16300422268</v>
       </c>
       <c r="G37" s="299">
         <f t="shared" si="2"/>
@@ -17422,15 +17422,15 @@
       </c>
       <c r="H37" s="277">
         <f t="shared" si="8"/>
-        <v>195350.14323443276</v>
+        <v>152217.81470382682</v>
       </c>
       <c r="I37" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J37" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
@@ -17438,32 +17438,32 @@
       </c>
       <c r="L37" s="277">
         <f t="shared" si="4"/>
-        <v>59437.374793500145</v>
+        <v>46313.90155645505</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B38" s="117">
         <v>18</v>
       </c>
       <c r="C38" s="277">
         <f t="shared" si="5"/>
-        <v>1626599.4521357997</v>
+        <v>1561141.0981346709</v>
       </c>
       <c r="D38" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E38" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F38" s="277">
         <f t="shared" si="7"/>
-        <v>255816.26307850773</v>
+        <v>207968.47726685953</v>
       </c>
       <c r="G38" s="299">
         <f t="shared" si="2"/>
@@ -17471,15 +17471,15 @@
       </c>
       <c r="H38" s="277">
         <f t="shared" si="8"/>
-        <v>200256.97319534674</v>
+        <v>155685.57343233842</v>
       </c>
       <c r="I38" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J38" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301814</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
@@ -17487,32 +17487,32 @@
       </c>
       <c r="L38" s="277">
         <f t="shared" si="4"/>
-        <v>56811.496875800236</v>
+        <v>44166.903791313183</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B39" s="117">
         <v>19</v>
       </c>
       <c r="C39" s="277">
         <f t="shared" si="5"/>
-        <v>1667456.5858649923</v>
+        <v>1596706.3220871245</v>
       </c>
       <c r="D39" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E39" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F39" s="277">
         <f t="shared" si="7"/>
-        <v>262241.88879538415</v>
+        <v>212706.32285806473</v>
       </c>
       <c r="G39" s="299">
         <f t="shared" si="2"/>
@@ -17520,15 +17520,15 @@
       </c>
       <c r="H39" s="277">
         <f t="shared" si="8"/>
-        <v>205287.05354075832</v>
+        <v>159232.33310185396</v>
       </c>
       <c r="I39" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607711E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J39" s="299">
         <f t="shared" si="10"/>
-        <v>0.1231138821130181</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
@@ -17536,32 +17536,32 @@
       </c>
       <c r="L39" s="277">
         <f t="shared" si="4"/>
-        <v>54301.627359592116</v>
+        <v>42119.435524844732</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B40" s="117">
         <v>20</v>
       </c>
       <c r="C40" s="277">
         <f t="shared" si="5"/>
-        <v>1709339.9743211083</v>
+        <v>1633081.777194404</v>
       </c>
       <c r="D40" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E40" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F40" s="277">
         <f t="shared" si="7"/>
-        <v>268828.91420341597</v>
+        <v>217552.10394575048</v>
       </c>
       <c r="G40" s="299">
         <f t="shared" si="2"/>
@@ -17569,15 +17569,15 @@
       </c>
       <c r="H40" s="277">
         <f t="shared" si="8"/>
-        <v>210443.48008963838</v>
+        <v>162859.89347676543</v>
       </c>
       <c r="I40" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J40" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301814</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
@@ -17585,32 +17585,32 @@
       </c>
       <c r="L40" s="277">
         <f t="shared" si="4"/>
-        <v>51902.641121150184</v>
+        <v>40166.882816007455</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B41" s="117">
         <v>21</v>
       </c>
       <c r="C41" s="277">
         <f t="shared" si="5"/>
-        <v>1752275.3951020455</v>
+        <v>1670285.9217832487</v>
       </c>
       <c r="D41" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E41" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F41" s="277">
         <f t="shared" si="7"/>
-        <v>275581.3933607529</v>
+        <v>222508.27946851583</v>
       </c>
       <c r="G41" s="299">
         <f t="shared" si="2"/>
@@ -17618,15 +17618,15 @@
       </c>
       <c r="H41" s="277">
         <f t="shared" si="8"/>
-        <v>215729.4264221355</v>
+        <v>166570.09532289876</v>
       </c>
       <c r="I41" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J41" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K41" s="119">
         <f t="shared" si="3"/>
@@ -17634,32 +17634,32 @@
       </c>
       <c r="L41" s="277">
         <f t="shared" si="4"/>
-        <v>49609.639459084232</v>
+        <v>38304.845614637961</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B42" s="117">
         <v>22</v>
       </c>
       <c r="C42" s="277">
         <f t="shared" si="5"/>
-        <v>1796289.2732907131</v>
+        <v>1708337.6346898081</v>
       </c>
       <c r="D42" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E42" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F42" s="277">
         <f t="shared" si="7"/>
-        <v>282503.48215589748</v>
+        <v>227577.36438340816</v>
       </c>
       <c r="G42" s="299">
         <f t="shared" si="2"/>
@@ -17667,15 +17667,15 @@
       </c>
       <c r="H42" s="277">
         <f t="shared" si="8"/>
-        <v>221148.14583279184</v>
+        <v>170364.8213415904</v>
       </c>
       <c r="I42" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229385E-2</v>
       </c>
       <c r="J42" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301812</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K42" s="119">
         <f t="shared" si="3"/>
@@ -17683,32 +17683,32 @@
       </c>
       <c r="L42" s="277">
         <f t="shared" si="4"/>
-        <v>47417.940091249606</v>
+        <v>36529.127846000323</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B43" s="117">
         <v>23</v>
       </c>
       <c r="C43" s="277">
         <f t="shared" si="5"/>
-        <v>1841408.6977186429</v>
+        <v>1747256.2248395029</v>
       </c>
       <c r="D43" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E43" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F43" s="277">
         <f t="shared" si="7"/>
-        <v>289599.44086549291</v>
+        <v>232761.9309421106</v>
       </c>
       <c r="G43" s="299">
         <f t="shared" si="2"/>
@@ -17716,15 +17716,15 @@
       </c>
       <c r="H43" s="277">
         <f t="shared" si="8"/>
-        <v>226702.97333281927</v>
+        <v>174245.99712504333</v>
       </c>
       <c r="I43" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J43" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301814</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K43" s="119">
         <f t="shared" si="3"/>
@@ -17732,32 +17732,32 @@
       </c>
       <c r="L43" s="277">
         <f t="shared" si="4"/>
-        <v>45323.067593582608</v>
+        <v>34835.72795499042</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B44" s="117">
         <v>24</v>
       </c>
       <c r="C44" s="277">
         <f t="shared" si="5"/>
-        <v>1887661.4376381128</v>
+        <v>1787061.4410451266</v>
       </c>
       <c r="D44" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E44" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F44" s="277">
         <f t="shared" si="7"/>
-        <v>296873.63677635754</v>
+        <v>238064.6099962031</v>
       </c>
       <c r="G44" s="299">
         <f t="shared" si="2"/>
@@ -17765,15 +17765,15 @@
       </c>
       <c r="H44" s="277">
         <f t="shared" si="8"/>
-        <v>232397.32770266893</v>
+        <v>178215.59213344796</v>
       </c>
       <c r="I44" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298607934E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J44" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301812</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K44" s="119">
         <f t="shared" si="3"/>
@@ -17781,32 +17781,32 @@
       </c>
       <c r="L44" s="277">
         <f t="shared" si="4"/>
-        <v>43320.744261337713</v>
+        <v>33220.829888687673</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B45" s="117">
         <v>25</v>
       </c>
       <c r="C45" s="277">
         <f t="shared" si="5"/>
-        <v>1935075.9598130421</v>
+        <v>1827773.4820281651</v>
       </c>
       <c r="D45" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E45" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F45" s="277">
         <f t="shared" si="7"/>
-        <v>304330.54687338049</v>
+        <v>243488.0923321592</v>
       </c>
       <c r="G45" s="299">
         <f t="shared" si="2"/>
@@ -17814,15 +17814,15 @@
       </c>
       <c r="H45" s="277">
         <f t="shared" si="8"/>
-        <v>238234.71359615825</v>
+        <v>182275.62069436314</v>
       </c>
       <c r="I45" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229385E-2</v>
       </c>
       <c r="J45" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301812</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K45" s="119">
         <f t="shared" si="3"/>
@@ -17830,32 +17830,32 @@
       </c>
       <c r="L45" s="277">
         <f t="shared" si="4"/>
-        <v>41406.881374065437</v>
+        <v>31680.79449693326</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B46" s="117">
         <v>26</v>
       </c>
       <c r="C46" s="277">
         <f t="shared" si="5"/>
-        <v>1983681.4460391784</v>
+        <v>1869413.0066684163</v>
       </c>
       <c r="D46" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E46" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F46" s="277">
         <f t="shared" si="7"/>
-        <v>311974.76059493166</v>
+        <v>249035.13003675616</v>
       </c>
       <c r="G46" s="299">
         <f t="shared" si="2"/>
@@ -17863,15 +17863,15 @@
       </c>
       <c r="H46" s="277">
         <f t="shared" si="8"/>
-        <v>244218.72369744876</v>
+        <v>186428.1430248644</v>
       </c>
       <c r="I46" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J46" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301814</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K46" s="119">
         <f t="shared" si="3"/>
@@ -17879,32 +17879,32 @@
       </c>
       <c r="L46" s="277">
         <f t="shared" si="4"/>
-        <v>39577.570846493683</v>
+        <v>30212.151331556186</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B47" s="117">
         <v>27</v>
       </c>
       <c r="C47" s="277">
         <f t="shared" si="5"/>
-        <v>2033507.8111043591</v>
+        <v>1912001.1444871137</v>
       </c>
       <c r="D47" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E47" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F47" s="277">
         <f t="shared" si="7"/>
-        <v>319810.98265748273</v>
+        <v>254708.53789359139</v>
       </c>
       <c r="G47" s="299">
         <f t="shared" si="2"/>
@@ -17912,15 +17912,15 @@
       </c>
       <c r="H47" s="277">
         <f t="shared" si="8"/>
-        <v>250353.04093220361</v>
+        <v>190675.26627697889</v>
       </c>
       <c r="I47" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.278155638522894E-2</v>
       </c>
       <c r="J47" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K47" s="119">
         <f t="shared" si="3"/>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="L47" s="277">
         <f t="shared" si="4"/>
-        <v>37829.077248264017</v>
+        <v>28811.590825766991</v>
       </c>
       <c r="N47" s="275"/>
       <c r="O47" s="275"/>
@@ -17942,26 +17942,26 @@
     <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B48" s="117">
         <v>28</v>
       </c>
       <c r="C48" s="277">
         <f t="shared" si="5"/>
-        <v>2084585.7211999001</v>
+        <v>1955559.5063688694</v>
       </c>
       <c r="D48" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E48" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F48" s="277">
         <f t="shared" si="7"/>
-        <v>327844.0359511773</v>
+        <v>260511.19481141353</v>
       </c>
       <c r="G48" s="299">
         <f t="shared" si="2"/>
@@ -17969,15 +17969,15 @@
       </c>
       <c r="H48" s="277">
         <f t="shared" si="8"/>
-        <v>256641.4407342854</v>
+        <v>195019.14560693648</v>
       </c>
       <c r="I48" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.2781556385229162E-2</v>
       </c>
       <c r="J48" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K48" s="119">
         <f t="shared" si="3"/>
@@ -17985,7 +17985,7 @@
       </c>
       <c r="L48" s="277">
         <f t="shared" si="4"/>
-        <v>36157.830176227391</v>
+        <v>27475.956836095436</v>
       </c>
       <c r="N48" s="275"/>
       <c r="O48" s="275"/>
@@ -17999,26 +17999,26 @@
     <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B49" s="117">
         <v>29</v>
       </c>
       <c r="C49" s="277">
         <f t="shared" si="5"/>
-        <v>2136946.6127944458</v>
+        <v>2000110.1955278828</v>
       </c>
       <c r="D49" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E49" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F49" s="277">
         <f t="shared" si="7"/>
-        <v>336078.86450813251</v>
+        <v>266446.04528499313</v>
       </c>
       <c r="G49" s="299">
         <f t="shared" si="2"/>
@@ -18026,15 +18026,15 @@
       </c>
       <c r="H49" s="277">
         <f t="shared" si="8"/>
-        <v>263087.79336938879</v>
+        <v>199461.98526878009</v>
       </c>
       <c r="I49" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608156E-2</v>
+        <v>2.278155638522894E-2</v>
       </c>
       <c r="J49" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301812</v>
+        <v>9.9725497982443276E-2</v>
       </c>
       <c r="K49" s="119">
         <f t="shared" si="3"/>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="L49" s="277">
         <f t="shared" si="4"/>
-        <v>34560.416963723212</v>
+        <v>26202.239530065322</v>
       </c>
       <c r="N49" s="275"/>
       <c r="O49" s="275"/>
@@ -18056,26 +18056,26 @@
     <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B50" s="117">
         <v>30</v>
       </c>
       <c r="C50" s="277">
         <f t="shared" si="5"/>
-        <v>2190622.7119818931</v>
+        <v>2045675.8187239729</v>
       </c>
       <c r="D50" s="299">
         <f t="shared" si="1"/>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E50" s="299">
         <f t="shared" si="6"/>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625478</v>
       </c>
       <c r="F50" s="277">
         <f t="shared" si="7"/>
-        <v>344520.53654529835</v>
+        <v>272516.10088927456</v>
       </c>
       <c r="G50" s="299">
         <f t="shared" si="2"/>
@@ -18083,15 +18083,15 @@
       </c>
       <c r="H50" s="277">
         <f t="shared" si="8"/>
-        <v>269696.06631703884</v>
+        <v>204006.03973289058</v>
       </c>
       <c r="I50" s="299">
         <f t="shared" si="9"/>
-        <v>2.5118128298608378E-2</v>
+        <v>2.2781556385229385E-2</v>
       </c>
       <c r="J50" s="299">
         <f t="shared" si="10"/>
-        <v>0.12311388211301813</v>
+        <v>9.972549798244329E-2</v>
       </c>
       <c r="K50" s="119">
         <f t="shared" si="3"/>
@@ -18099,7 +18099,7 @@
       </c>
       <c r="L50" s="277">
         <f t="shared" si="4"/>
-        <v>33033.575711954691</v>
+        <v>24987.568603579293</v>
       </c>
       <c r="N50" s="275"/>
       <c r="O50" s="275"/>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>2234435.1662215311</v>
+        <v>2086589.3350984524</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18128,11 +18128,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>351410.94727620436</v>
+        <v>277966.42290705995</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18140,11 +18140,11 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>3794344.6571500646</v>
+        <v>2870153.9383110115</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>2.000000000000024E-2</v>
+        <v>1.9999999999999574E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>464748.23760267306</v>
+        <v>351549.24104346032</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18166,7 +18166,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>2553060.4355806289</v>
+        <v>1972635.5401994288</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18190,7 +18190,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>2553060.4355806289</v>
+        <v>1972635.5401994288</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="F55" s="123">
         <f>C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18225,19 +18225,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>1803128.5918062211</v>
+        <v>1458285.397489209</v>
       </c>
       <c r="C56" s="118">
-        <v>1821159.8777242838</v>
+        <v>1472868.2514641015</v>
       </c>
       <c r="D56" s="118">
-        <v>1839191.1636423455</v>
+        <v>1487451.1054389931</v>
       </c>
       <c r="E56" s="118">
-        <v>1857222.449560408</v>
+        <v>1502033.9594138854</v>
       </c>
       <c r="F56" s="118">
-        <v>1893285.0213965327</v>
+        <v>1516616.8133887777</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18251,19 +18251,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>1800900.7077006742</v>
+        <v>1456480.7524885023</v>
       </c>
       <c r="C57" s="118">
-        <v>1835863.5287029452</v>
+        <v>1484778.5973230759</v>
       </c>
       <c r="D57" s="118">
-        <v>1871162.0687928458</v>
+        <v>1513348.3834905147</v>
       </c>
       <c r="E57" s="118">
-        <v>1906796.3279703753</v>
+        <v>1542190.1109908191</v>
       </c>
       <c r="F57" s="118">
-        <v>1979072.0035883207</v>
+        <v>1571303.779823988</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18277,19 +18277,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>1798823.4264833808</v>
+        <v>1454798.0998071909</v>
       </c>
       <c r="C58" s="118">
-        <v>1849710.3235639695</v>
+        <v>1495994.8670830433</v>
       </c>
       <c r="D58" s="118">
-        <v>1901567.9646003142</v>
+        <v>1537977.9626164376</v>
       </c>
       <c r="E58" s="118">
-        <v>1954405.7403361243</v>
+        <v>1580754.9931579432</v>
       </c>
       <c r="F58" s="118">
-        <v>2063059.2588809803</v>
+        <v>1624333.565458131</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18303,19 +18303,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>1796886.5675395173</v>
+        <v>1453229.1928782286</v>
       </c>
       <c r="C59" s="118">
-        <v>1862750.1956475452</v>
+        <v>1506557.5080691192</v>
       </c>
       <c r="D59" s="118">
-        <v>1930485.4599137106</v>
+        <v>1561401.8980089228</v>
       </c>
       <c r="E59" s="118">
-        <v>2000128.5326314354</v>
+        <v>1617791.6632112195</v>
       </c>
       <c r="F59" s="118">
-        <v>2145284.5437828843</v>
+        <v>1675756.3878912393</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18329,19 +18329,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>1797723.9805482342</v>
+        <v>1451766.3425948145</v>
       </c>
       <c r="C60" s="118">
-        <v>1877726.641695542</v>
+        <v>1516504.610536193</v>
       </c>
       <c r="D60" s="118">
-        <v>1960737.5466129768</v>
+        <v>1583679.2071933849</v>
       </c>
       <c r="E60" s="118">
-        <v>2046843.7876520243</v>
+        <v>1653360.6796726405</v>
       </c>
       <c r="F60" s="118">
-        <v>2228699.1073663551</v>
+        <v>1725620.9429778901</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18355,19 +18355,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>1796040.1305853557</v>
+        <v>1450402.3796265959</v>
       </c>
       <c r="C61" s="118">
-        <v>1889290.9983442929</v>
+        <v>1525872.0450273303</v>
       </c>
       <c r="D61" s="118">
-        <v>1986893.250721568</v>
+        <v>1604866.0187254604</v>
       </c>
       <c r="E61" s="118">
-        <v>2089014.6607475593</v>
+        <v>1687520.2013092497</v>
       </c>
       <c r="F61" s="118">
-        <v>2307510.5692509133</v>
+        <v>1773974.450940703</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18381,19 +18381,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>1796934.761942955</v>
+        <v>1449130.6192832687</v>
       </c>
       <c r="C62" s="118">
-        <v>1902720.7775684698</v>
+        <v>1534693.5917276088</v>
       </c>
       <c r="D62" s="118">
-        <v>2014384.1168917788</v>
+        <v>1625015.7136091131</v>
       </c>
       <c r="E62" s="118">
-        <v>2132207.6216469961</v>
+        <v>1720326.0822283251</v>
       </c>
       <c r="F62" s="118">
-        <v>2387521.7896427466</v>
+        <v>1820862.7010864606</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18407,19 +18407,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>1795470.8707770703</v>
+        <v>1447944.8287533598</v>
       </c>
       <c r="C63" s="118">
-        <v>1912976.579453825</v>
+        <v>1543001.0622798526</v>
       </c>
       <c r="D63" s="118">
-        <v>2038041.7971300543</v>
+        <v>1644179.0597921673</v>
       </c>
       <c r="E63" s="118">
-        <v>2171102.5020417371</v>
+        <v>1751831.9632042199</v>
       </c>
       <c r="F63" s="118">
-        <v>2463061.1633498883</v>
+        <v>1866330.0951671959</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18433,19 +18433,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>1796403.9835669312</v>
+        <v>1446839.1965576406</v>
       </c>
       <c r="C64" s="118">
-        <v>1925026.0800585649</v>
+        <v>1550824.4145015455</v>
       </c>
       <c r="D64" s="118">
-        <v>2063028.8883012477</v>
+        <v>1662404.3400781485</v>
       </c>
       <c r="E64" s="118">
-        <v>2211042.5648013111</v>
+        <v>1782089.3593861978</v>
       </c>
       <c r="F64" s="118">
-        <v>2539809.0845648199</v>
+        <v>1910419.6894273022</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18459,19 +18459,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>1795131.3183100508</v>
+        <v>1445808.3040674594</v>
       </c>
       <c r="C65" s="118">
-        <v>1934121.3955617417</v>
+        <v>1558191.8604166135</v>
       </c>
       <c r="D65" s="118">
-        <v>2084427.1206689507</v>
+        <v>1679737.4737767042</v>
       </c>
       <c r="E65" s="118">
-        <v>2246915.9439816289</v>
+        <v>1811147.744530662</v>
       </c>
       <c r="F65" s="118">
-        <v>2612212.2203983553</v>
+        <v>1953173.2353764968</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18485,19 +18485,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>1795951.2429734594</v>
+        <v>1441609.585139283</v>
       </c>
       <c r="C66" s="277">
-        <v>1978608.8375075681</v>
+        <v>1589068.0436929537</v>
       </c>
       <c r="D66" s="118">
-        <v>2183450.2664018157</v>
+        <v>1754476.7864896371</v>
       </c>
       <c r="E66" s="118">
-        <v>2413213.720746126</v>
+        <v>1940053.1166100926</v>
       </c>
       <c r="F66" s="118">
-        <v>2960104.2301325845</v>
+        <v>2148275.0942420294</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18520,19 +18520,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>1795654.7457131369</v>
+        <v>1438650.6850655614</v>
       </c>
       <c r="C67" s="277">
-        <v>2010493.0207018843</v>
+        <v>1611936.875204958</v>
       </c>
       <c r="D67" s="118">
-        <v>2259210.762496735</v>
+        <v>1812628.6256127842</v>
       </c>
       <c r="E67" s="118">
-        <v>2547535.3954563397</v>
+        <v>2045363.3647339698</v>
       </c>
       <c r="F67" s="118">
-        <v>3270856.7715516072</v>
+        <v>2315554.1619743276</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18555,19 +18555,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>1797311.1890186374</v>
+        <v>1436565.5038957726</v>
       </c>
       <c r="C68" s="277">
-        <v>2036121.5323853511</v>
+        <v>1628874.9614329012</v>
       </c>
       <c r="D68" s="118">
-        <v>2320324.0144922468</v>
+        <v>1857874.377422048</v>
       </c>
       <c r="E68" s="118">
-        <v>2659596.6334090345</v>
+        <v>2131397.3924941071</v>
       </c>
       <c r="F68" s="118">
-        <v>3553009.655774218</v>
+        <v>2458978.1491372208</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18590,19 +18590,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>1797862.3697535563</v>
+        <v>1435096.0455151205</v>
       </c>
       <c r="C69" s="277">
-        <v>2054314.0659700555</v>
+        <v>1641420.3669519655</v>
       </c>
       <c r="D69" s="118">
-        <v>2366873.5929891476</v>
+        <v>1893078.389670918</v>
       </c>
       <c r="E69" s="118">
-        <v>2749890.6059227362</v>
+        <v>2201683.5618318268</v>
       </c>
       <c r="F69" s="118">
-        <v>3804851.3817301556</v>
+        <v>2581948.9450207883</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F72" s="124">
         <f>F55</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G72" s="124"/>
       <c r="H72" s="124"/>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>106.9216257535157</v>
+        <v>93.197442898576469</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>107.85737186055866</v>
+        <v>93.954230234687188</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>108.79311796760156</v>
+        <v>94.711017570797864</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>109.72886407464449</v>
+        <v>95.467804906908583</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>111.60035628873035</v>
+        <v>96.224592243019288</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>106.80600816039551</v>
+        <v>93.103789592779009</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>108.62042804108418</v>
+        <v>94.572325905828762</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>110.45227029701201</v>
+        <v>96.05497480323487</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>112.30153492817901</v>
+        <v>97.551736284997403</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>116.05233131623039</v>
+        <v>99.062610351116277</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>106.69820620876828</v>
+        <v>93.01646716313104</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>109.33901707822247</v>
+        <v>95.154402015715021</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>112.03020537952824</v>
+        <v>97.333143919398765</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>114.77225845185316</v>
+        <v>99.553087631786639</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>120.41090826623044</v>
+        <v>101.81462791048305</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>106.59769156855641</v>
+        <v>92.93504764830773</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>110.01573029734573</v>
+        <v>95.702557606377127</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>113.53089888457866</v>
+        <v>98.54874531658956</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>117.14507451654721</v>
+        <v>101.47513134944906</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>124.67804653895773</v>
+        <v>104.48325099835387</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>106.64114969830128</v>
+        <v>92.859132016770872</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>110.79294336747475</v>
+        <v>96.218769398049588</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>115.10085193659067</v>
+        <v>99.704841750281517</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>119.5693951237228</v>
+        <v>103.32101016454675</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>129.00690325492431</v>
+        <v>107.07100671992558</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>106.55376513489477</v>
+        <v>92.788348211142065</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>111.39308368823161</v>
+        <v>96.704898917480065</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>116.45822036875911</v>
+        <v>100.80434605085568</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>121.75788187442198</v>
+        <v>105.09374226669185</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>133.09687881096397</v>
+        <v>109.58034560144966</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>106.60019265059809</v>
+        <v>92.72234932477491</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>112.09003140924142</v>
+        <v>97.162699210836536</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>117.88487796350358</v>
+        <v>101.85002846259057</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>123.99941058163517</v>
+        <v>106.79622624357714</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>137.24911666807725</v>
+        <v>112.01364391080631</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>106.52422300174243</v>
+        <v>92.660811901588744</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>112.62226337164468</v>
+        <v>97.5938211654193</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>119.11260971182318</v>
+        <v>102.84452362340139</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>126.01788741565956</v>
+        <v>108.43124582044599</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>141.16928493539487</v>
+        <v>114.37320590775826</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>106.57264753810173</v>
+        <v>92.603434350832416</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>113.24758057497303</v>
+        <v>97.999819462975083</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>120.40933216390016</v>
+        <v>103.79033720291372</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>128.0906047144787</v>
+        <v>110.00147441175125</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>145.15217161507249</v>
+        <v>116.66126602601467</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>106.50660169061719</v>
+        <v>92.549935469008304</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>113.71958829051256</v>
+        <v>98.382158186081256</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>121.51980829558968</v>
+        <v>104.6898522155968</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>129.95227864428043</v>
+        <v>111.50947949244538</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>148.90958263954434</v>
+        <v>118.87999098917243</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>106.54915225053509</v>
+        <v>92.332040033848429</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>116.02829499075985</v>
+        <v>99.984499163450877</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>126.65868322374183</v>
+        <v>108.56850076190673</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>138.58241727800879</v>
+        <v>118.19911331270535</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>166.96368012651538</v>
+        <v>129.00493747052019</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>106.53376531926703</v>
+        <v>92.178485859304459</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>117.68294682401807</v>
+        <v>101.17129305919531</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>130.59032679096222</v>
+        <v>111.58633084480518</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>145.55313388539517</v>
+        <v>123.66426178638852</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>183.09039910861861</v>
+        <v>137.68600088061612</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>106.61972759515258</v>
+        <v>92.070273934155296</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>119.01295623910286</v>
+        <v>102.0503068089955</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.76184145183558</v>
+        <v>113.93439056212891</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>151.36862966540517</v>
+        <v>128.12905741525307</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>197.73291901551912</v>
+        <v>145.12908831509645</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>106.64833150223502</v>
+        <v>91.994015370822339</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>119.95707040580695</v>
+        <v>102.70135934230261</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.17756416073738</v>
+        <v>115.76132723008853</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>156.05449808616487</v>
+        <v>131.77660699300381</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>210.80242031038654</v>
+        <v>151.51074318158336</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="C90" s="130">
         <f>Scenarios!C29</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>210.80242031038654</v>
+        <v>151.51074318158336</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>156.05449808616487</v>
+        <v>131.77660699300381</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>136.17756416073738</v>
+        <v>115.76132723008853</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>119.95707040580695</v>
+        <v>102.70135934230261</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>106.64833150223502</v>
+        <v>91.994015370822339</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>125485.1812230568</v>
+        <v>118134.44704364182</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.4892940159722023E-2</v>
+        <v>5.7526861635440518E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>156.05449808616487</v>
+        <v>131.77660699300381</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>136.17756416073738</v>
+        <v>115.76132723008853</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>119.95707040580695</v>
+        <v>102.70135934230261</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>136.09782750709027</v>
+        <v>115.69939121072511</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19777,7 +19777,7 @@
         <v>444</v>
       </c>
       <c r="C29" s="324">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D29" s="325">
         <f>C18</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>210.80242031038654</v>
+        <v>151.51074318158336</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>106.64833150223502</v>
+        <v>91.994015370822339</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>5.09</v>
+        <v>4.5810000000000004</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.26995508046657685</v>
+        <v>0.19048841663164309</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.5462548049219778E-2</v>
+        <v>3.1467955569648896E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>145.83104162734193</v>
+        <v>119.8858252143587</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19919,7 +19919,7 @@
     <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>2-stage DCF</v>
+        <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
         <v>251</v>
@@ -19931,7 +19931,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -19983,7 +19983,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>2.5118128298608065E-2</v>
+        <v>2.2781556385229107E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>145.83985968027483</v>
+        <v>119.89000081625294</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="E49" s="222" t="s">
         <v>254</v>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E50" s="126"/>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E51" s="221" t="s">
         <v>247</v>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.1523827165210597E-2</v>
+        <v>0.14612827877009313</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>5.09</v>
+        <v>4.5810000000000004</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20137,15 +20137,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>9.313944522400508</v>
+        <v>8.3825500701604572</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>67.203244989558513</v>
+        <v>55.246924061916467</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>76.517189511959018</v>
+        <v>63.629474132076922</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47530245510080227</v>
+        <v>0.46924939609577776</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20162,15 +20162,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>10.709380091599607</v>
+        <v>9.6384420824396493</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>84.234536680053139</v>
+        <v>69.248130087716248</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>94.943916771652752</v>
+        <v>78.886572170155901</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34894576825232204</v>
+        <v>0.34198582668881128</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20208,15 +20208,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>12.280149911027722</v>
+        <v>11.052134919924953</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>104.52591471057164</v>
+        <v>85.92941119754768</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>116.80606462159936</v>
+        <v>96.981546117472632</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19903154144584168</v>
+        <v>0.19105076897900708</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20233,15 +20233,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>13.296989906310651</v>
+        <v>11.967290915679589</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>118.21105009108433</v>
+        <v>97.17978512311781</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>131.50803999739497</v>
+        <v>109.14707603879739</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.8216411746876897E-2</v>
+        <v>8.9574802995768477E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.26995508046657685</v>
+        <v>0.19048841663164309</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>145.83104162734193</v>
+        <v>119.8858252143587</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="D19" s="343" t="s">
         <v>363</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>76.517189511959018</v>
+        <v>63.629474132076922</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>94.943916771652752</v>
+        <v>78.886572170155901</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>116.80606462159936</v>
+        <v>96.981546117472632</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>131.50803999739497</v>
+        <v>109.14707603879739</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
-        <v>160987.97999999998</v>
+        <v>135679.51550364122</v>
       </c>
       <c r="D34" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="C41" s="373">
         <f>Normalized_FCF!C9</f>
-        <v>11097</v>
+        <v>7974.2</v>
       </c>
       <c r="D41" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>989.94206765508</v>
+        <v>507.62526607571937</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-4525.9779323449202</v>
+        <v>-5008.294733924281</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-36192.744446613491</v>
+        <v>-34661.355192429241</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>125485.1812230568</v>
+        <v>118134.44704364182</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>131172.40159846353</v>
+        <v>103790.20955470968</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.4196448878206431E-2</v>
+        <v>6.6620470208222565E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,14 +20867,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.2956091527520103E-2</v>
+        <v>5.6660482374768097E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.83989502603092137</v>
+        <v>1.0614782273563756</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20894,11 +20894,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.1141273682688253</v>
+        <v>9.6671315574961933E-2</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>0.11539664872608364</v>
+        <v>0.11027130711998644</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20908,11 +20908,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.15727059464000756</v>
+        <v>0.13321568275625476</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.15901969737764152</v>
+        <v>0.15195683827249326</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.57104884476468376</v>
+        <v>0.67756727799881356</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>86587.65539082</v>
+        <v>166973.7889873801</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.4935265193022591</v>
+        <v>8.6652207575852511</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>13.347015049223478</v>
+        <v>17.518709287506468</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>145.60279694711016</v>
+        <v>122.1661438905825</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C118" s="396">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>210.8 HKD</v>
+        <v>151.51 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>156.05 HKD</v>
+        <v>131.78 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>136.18 HKD</v>
+        <v>115.76 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>119.96 HKD</v>
+        <v>102.7 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>106.65 HKD</v>
+        <v>91.99 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>145.83104162734193</v>
+        <v>119.8858252143587</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>5.09</v>
+        <v>4.5810000000000004</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21550,15 +21550,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>9.313944522400508</v>
+        <v>8.3825500701604572</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>67.203244989558513</v>
+        <v>55.246924061916467</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>76.517189511959018</v>
+        <v>63.629474132076922</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21571,15 +21571,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>10.709380091599607</v>
+        <v>9.6384420824396493</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>84.234536680053139</v>
+        <v>69.248130087716248</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>94.943916771652752</v>
+        <v>78.886572170155901</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21611,15 +21611,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>12.280149911027722</v>
+        <v>11.052134919924953</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>104.52591471057164</v>
+        <v>85.92941119754768</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>116.80606462159936</v>
+        <v>96.981546117472632</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21632,15 +21632,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>13.296989906310651</v>
+        <v>11.967290915679589</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>118.21105009108433</v>
+        <v>97.17978512311781</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>131.50803999739497</v>
+        <v>109.14707603879739</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D920D52-8678-42F4-91C6-D86007F61FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89FB43-B499-43C0-A124-4952AA1109F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>80.849999999999994</v>
+        <v>79.3</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1749966.4445801999</v>
+        <v>1716417.3043316</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19048841663164309</v>
+        <v>0.19972450617404428</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>119.8858252143587</v>
+        <v>120.26549467131863</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.629474132076922</v>
+        <v>63.804437015468594</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>78.886572170155901</v>
+        <v>79.105875827605686</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>96.981546117472632</v>
+        <v>97.253678146658942</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.14707603879739</v>
+        <v>109.45483716217629</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6620470208222565E-2</v>
+        <v>6.8137741683054476E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6660482374768097E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7708749949163298</v>
+        <v>-4.7859839997991402</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6652207575852511</v>
+        <v>8.6926628647200008</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.624363524837548</v>
+        <v>13.667510866832741</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.518709287506468</v>
+        <v>17.574189731753602</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4477030545205587</v>
+        <v>1.4522878219988347</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.51 HKD</v>
+        <v>151.99 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2374743671833602E-2</v>
+        <v>-4.247778271649684E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>131.78 HKD</v>
+        <v>132.19 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.830060428741568E-3</v>
+        <v>4.716933907008166E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>115.76 HKD</v>
+        <v>116.13 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0865119237549494E-2</v>
+        <v>5.0741562486851688E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.7 HKD</v>
+        <v>103.03 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5382641270521373E-2</v>
+        <v>9.5248425961308988E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>91.99 HKD</v>
+        <v>92.29 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13810364947030609</v>
+        <v>0.13795866316482533</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>119.8858252143587</v>
+        <v>120.26549467131863</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.246924061916467</v>
+        <v>55.421886945308138</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.629474132076922</v>
+        <v>63.804437015468594</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.248130087716248</v>
+        <v>69.467433745166034</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>78.886572170155901</v>
+        <v>79.105875827605686</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>85.92941119754768</v>
+        <v>86.201543226733989</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>96.981546117472632</v>
+        <v>97.253678146658942</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.17978512311781</v>
+        <v>97.487546246496706</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.14707603879739</v>
+        <v>109.45483716217629</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.193769578134095</v>
+        <v>74.428735706574827</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4477030545205587</v>
+        <v>1.4522878219988347</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103263.71245999145</v>
+        <v>-103590.74092697869</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7708749949163298</v>
+        <v>-4.7859839997991402</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>187555.29450406937</v>
+        <v>188149.26811760539</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.6652207575852511</v>
+        <v>8.6926628647200008</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>294893.98883399041</v>
+        <v>295827.89607782982</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.624363524837548</v>
+        <v>13.667510866832743</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>379185.57087806833</v>
+        <v>380386.42326845654</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.518709287506468</v>
+        <v>17.574189731753602</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6660482374768097E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6660482374768097E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.3766233766233774E-2</v>
+        <v>5.4817150063051712E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9090909090909095E-2</v>
+        <v>5.0050441361916775E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5194805194805204E-2</v>
+        <v>4.6078184110971004E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3862650163347947</v>
+        <v>5.4033229154662186</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1306691841663188</v>
+        <v>6.1500845557149697</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6003882674237397</v>
+        <v>5.6181242789034602</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.4818237355582342</v>
+        <v>5.4991842620183737</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.971444844675446</v>
+        <v>4.9871890392965312</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6620470208222565E-2</v>
+        <v>6.8137741683054476E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.5827695536998377E-2</v>
+        <v>7.7554660223391803E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.9268871582235506E-2</v>
+        <v>7.0846460011392942E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.7802396234486514E-2</v>
+        <v>6.9346585901871052E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.1489732154303603E-2</v>
+        <v>6.2890151819628384E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9159232126437176E-2</v>
+        <v>8.0706480673675224E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5392874194024864E-2</v>
+        <v>7.6866505404626861E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1769376143740168E-2</v>
+        <v>7.3172182360925514E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6461845802935196E-2</v>
+        <v>6.7760910884833686E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.518709287506468</v>
+        <v>17.574189731753602</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2644238.1258166456</v>
+        <v>2652612.2305242415</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>119.89000081625294</v>
+        <v>120.2696834970323</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.197442898576469</v>
+        <v>93.492592241479088</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>93.954230234687188</v>
+        <v>94.251776266576371</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>94.711017570797864</v>
+        <v>95.010960291673612</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>95.467804906908583</v>
+        <v>95.770144316770867</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.224592243019288</v>
+        <v>96.529328341868137</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.103789592779009</v>
+        <v>93.398642342654966</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>94.572325905828762</v>
+        <v>94.871829400557203</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.05497480323487</v>
+        <v>96.35917373631672</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>97.551736284997403</v>
+        <v>97.860675349933572</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.062610351116277</v>
+        <v>99.376334241407662</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.01646716313104</v>
+        <v>93.311043369392394</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.154402015715021</v>
+        <v>95.455748902021696</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.333143919398765</v>
+        <v>97.641390718634668</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>99.553087631786639</v>
+        <v>99.868364827003532</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>101.81462791048305</v>
+        <v>102.13706723490054</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>92.93504764830773</v>
+        <v>93.22936600504498</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>95.702557606377127</v>
+        <v>96.005640460510392</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>98.54874531658956</v>
+        <v>98.860841834685289</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>101.47513134944906</v>
+        <v>101.79649551360689</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>104.48325099835387</v>
+        <v>104.81414165283303</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>92.859132016770872</v>
+        <v>93.15320995437142</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.218769398049588</v>
+        <v>96.523487056383189</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>99.704841750281517</v>
+        <v>100.02059953946069</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>103.32101016454675</v>
+        <v>103.64822008908608</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.07100671992558</v>
+        <v>107.41009260355546</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>92.788348211142065</v>
+        <v>93.082201981715386</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>96.704898917480065</v>
+        <v>97.011156111703954</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.80434605085568</v>
+        <v>101.12358588805827</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.09374226669185</v>
+        <v>105.42656630143439</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>109.58034560144966</v>
+        <v>109.92737837395296</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>92.72234932477491</v>
+        <v>93.015994081803029</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.162699210836536</v>
+        <v>97.470406224407</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>101.85002846259057</v>
+        <v>102.17257989791335</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>106.79622624357714</v>
+        <v>107.13444191795541</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.01364391080631</v>
+        <v>112.36838275736869</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>92.660811901588744</v>
+        <v>92.954261774192446</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>97.5938211654193</v>
+        <v>97.902893510029415</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>102.84452362340139</v>
+        <v>103.17022455064266</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>108.43124582044599</v>
+        <v>108.77463947974249</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>114.37320590775826</v>
+        <v>114.73541731098398</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>92.603434350832416</v>
+        <v>92.896702513017061</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>97.999819462975083</v>
+        <v>98.310177573878946</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>103.79033720291372</v>
+        <v>104.11903345114041</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.00147441175125</v>
+        <v>110.34984086775241</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>116.66126602601467</v>
+        <v>117.03072354479272</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>92.549935469008304</v>
+        <v>92.843034204228815</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>98.382158186081256</v>
+        <v>98.693727135173177</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>104.6898522155968</v>
+        <v>105.02139716070472</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>111.50947949244538</v>
+        <v>111.86262168793915</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>118.87999098917243</v>
+        <v>119.25647504424364</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.332040033848429</v>
+        <v>92.624448710495358</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>99.984499163450877</v>
+        <v>100.30114260677642</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>108.56850076190673</v>
+        <v>108.91232909735444</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>118.19911331270535</v>
+        <v>118.57344107901417</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.00493747052019</v>
+        <v>129.41348647510023</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.178485859304459</v>
+        <v>92.470408241346007</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.17129305919531</v>
+        <v>101.49169499017454</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>111.58633084480518</v>
+        <v>111.93971642279364</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>123.66426178638852</v>
+        <v>124.05589726984822</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>137.68600088061612</v>
+        <v>138.12204216482849</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.070273934155296</v>
+        <v>92.36185361710973</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.0503068089955</v>
+        <v>102.37349251088719</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>113.93439056212891</v>
+        <v>114.29521226991997</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.12905741525307</v>
+        <v>128.53483257309728</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>145.12908831509645</v>
+        <v>145.58870130146212</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>91.994015370822339</v>
+        <v>92.285353548600682</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>102.70135934230261</v>
+        <v>103.02660687895525</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>115.76132723008853</v>
+        <v>116.12793470989544</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>131.77660699300381</v>
+        <v>132.19393366800981</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>151.51074318158336</v>
+        <v>151.99056639241329</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>151.51074318158336</v>
+        <v>151.99056639241329</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>131.77660699300381</v>
+        <v>132.19393366800981</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>115.76132723008853</v>
+        <v>116.12793470989544</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>102.70135934230261</v>
+        <v>103.02660687895525</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>91.994015370822339</v>
+        <v>92.285353548600682</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>131.77660699300381</v>
+        <v>132.19393366800981</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>115.76132723008853</v>
+        <v>116.12793470989544</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>102.70135934230261</v>
+        <v>103.02660687895525</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>115.69939121072511</v>
+        <v>116.06580254378328</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>151.51074318158336</v>
+        <v>151.99056639241329</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>91.994015370822339</v>
+        <v>92.285353548600682</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>80.849999999999994</v>
+        <v>79.3</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19048841663164309</v>
+        <v>0.19972450617404428</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1467955569648896E-2</v>
+        <v>3.1348866084834517E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>119.8858252143587</v>
+        <v>120.26549467131863</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>119.89000081625294</v>
+        <v>120.2696834970323</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009313</v>
+        <v>0.14612827877009316</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.246924061916467</v>
+        <v>55.421886945308138</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>63.629474132076922</v>
+        <v>63.804437015468594</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46924939609577776</v>
+        <v>0.46947013197888654</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.248130087716248</v>
+        <v>69.467433745166034</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>78.886572170155901</v>
+        <v>79.105875827605686</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34198582668881128</v>
+        <v>0.34223963370541766</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>85.92941119754768</v>
+        <v>86.201543226733989</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>96.981546117472632</v>
+        <v>97.253678146658942</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19105076897900708</v>
+        <v>0.19134180246420784</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.17978512311781</v>
+        <v>97.487546246496706</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.14707603879739</v>
+        <v>109.45483716217629</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.9574802995768477E-2</v>
+        <v>8.988993508643095E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>80.849999999999994</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1749966.4445801999</v>
+        <v>1716417.3043316</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19048841663164309</v>
+        <v>0.19972450617404428</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>119.8858252143587</v>
+        <v>120.26549467131863</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>63.629474132076922</v>
+        <v>63.804437015468594</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>78.886572170155901</v>
+        <v>79.105875827605686</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>96.981546117472632</v>
+        <v>97.253678146658942</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.14707603879739</v>
+        <v>109.45483716217629</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6620470208222565E-2</v>
+        <v>6.8137741683054476E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.6660482374768097E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7708749949163298</v>
+        <v>-4.7859839997991402</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6652207575852511</v>
+        <v>8.6926628647200008</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.624363524837548</v>
+        <v>13.667510866832741</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.518709287506468</v>
+        <v>17.574189731753602</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4477030545205587</v>
+        <v>1.4522878219988347</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.1661438905825</v>
+        <v>122.55303494652591</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.51 HKD</v>
+        <v>151.99 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>131.78 HKD</v>
+        <v>132.19 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>115.76 HKD</v>
+        <v>116.13 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.7 HKD</v>
+        <v>103.03 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>91.99 HKD</v>
+        <v>92.29 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>119.8858252143587</v>
+        <v>120.26549467131863</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.246924061916467</v>
+        <v>55.421886945308138</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>63.629474132076922</v>
+        <v>63.804437015468594</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.248130087716248</v>
+        <v>69.467433745166034</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>78.886572170155901</v>
+        <v>79.105875827605686</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>85.92941119754768</v>
+        <v>86.201543226733989</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>96.981546117472632</v>
+        <v>97.253678146658942</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.17978512311781</v>
+        <v>97.487546246496706</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.14707603879739</v>
+        <v>109.45483716217629</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89FB43-B499-43C0-A124-4952AA1109F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40CB57A-7E46-473E-806E-1615A6CF1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.3</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1716417.3043316</v>
+        <v>1740226.3716048</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19972450617404428</v>
+        <v>0.19353650913892836</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.26549467131863</v>
+        <v>120.12395886489134</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.804437015468594</v>
+        <v>63.739213141538961</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.105875827605686</v>
+        <v>79.024122293207242</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.253678146658942</v>
+        <v>97.152230886418451</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.45483716217629</v>
+        <v>109.34010784174797</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8137741683054476E-2</v>
+        <v>6.7126417336250729E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.697761194029851E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7859839997991402</v>
+        <v>-4.7803515604464319</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6926628647200008</v>
+        <v>8.682432806198884</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.667510866832741</v>
+        <v>13.651426102223592</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.574189731753602</v>
+        <v>17.553507347976044</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4522878219988347</v>
+        <v>1.4505786806643819</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.99 HKD</v>
+        <v>151.81 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.247778271649684E-2</v>
+        <v>-4.243944712349753E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.19 HKD</v>
+        <v>132.04 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.716933907008166E-3</v>
+        <v>4.7590224537474284E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.13 HKD</v>
+        <v>115.99 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0741562486851688E-2</v>
+        <v>5.0787531491188954E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.03 HKD</v>
+        <v>102.91 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5248425961308988E-2</v>
+        <v>9.5298360356707204E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.29 HKD</v>
+        <v>92.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13795866316482533</v>
+        <v>0.1380126047682638</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.26549467131863</v>
+        <v>120.12395886489134</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.421886945308138</v>
+        <v>55.356663071378506</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.804437015468594</v>
+        <v>63.739213141538961</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.467433745166034</v>
+        <v>69.385680210767589</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.105875827605686</v>
+        <v>79.024122293207242</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.201543226733989</v>
+        <v>86.100095966493498</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.253678146658942</v>
+        <v>97.152230886418451</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.487546246496706</v>
+        <v>97.372816926068381</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.45483716217629</v>
+        <v>109.34010784174797</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.428735706574827</v>
+        <v>74.341143407899438</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4522878219988347</v>
+        <v>1.4505786806643819</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103590.74092697869</v>
+        <v>-103468.82899292336</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7859839997991402</v>
+        <v>-4.7803515604464319</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>188149.26811760539</v>
+        <v>187927.84252529807</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.6926628647200008</v>
+        <v>8.682432806198884</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>295827.89607782982</v>
+        <v>295479.74767541816</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.667510866832743</v>
+        <v>13.651426102223592</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>380386.42326845654</v>
+        <v>379938.76120779285</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.574189731753602</v>
+        <v>17.553507347976044</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.697761194029851E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.697761194029851E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4817150063051712E-2</v>
+        <v>5.4067164179104482E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0050441361916775E-2</v>
+        <v>4.9365671641791044E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6078184110971004E-2</v>
+        <v>4.5447761194029851E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4033229154662186</v>
+        <v>5.3969639538345584</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1500845557149697</v>
+        <v>6.1428467592084317</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6181242789034602</v>
+        <v>5.6115125258599408</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.4991842620183737</v>
+        <v>5.4927124848777718</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9871890392965312</v>
+        <v>4.9813198095194338</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8137741683054476E-2</v>
+        <v>6.7126417336250729E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.7554660223391803E-2</v>
+        <v>7.6403566656821284E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.0846460011392942E-2</v>
+        <v>6.9794931913680844E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.9346585901871052E-2</v>
+        <v>6.8317319463653867E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.2890151819628384E-2</v>
+        <v>6.1956714048749174E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0706480673675224E-2</v>
+        <v>7.960228753012992E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6866505404626861E-2</v>
+        <v>7.5814849236155599E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3172182360925514E-2</v>
+        <v>7.2171070413201394E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7760910884833686E-2</v>
+        <v>6.6833833745862076E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.574189731753602</v>
+        <v>17.553507347976044</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2652612.2305242415</v>
+        <v>2649490.4738457175</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.2696834970323</v>
+        <v>120.12814276093812</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.492592241479088</v>
+        <v>93.382564427815325</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.251776266576371</v>
+        <v>94.140854998613747</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.010960291673612</v>
+        <v>94.899145569412113</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>95.770144316770867</v>
+        <v>95.657436140210521</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.529328341868137</v>
+        <v>96.415726711008929</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.398642342654966</v>
+        <v>93.288725094991293</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>94.871829400557203</v>
+        <v>94.76017841605713</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.35917373631672</v>
+        <v>96.245772353827832</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>97.860675349933572</v>
+        <v>97.745506908303426</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.376334241407662</v>
+        <v>99.259382079483856</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.311043369392394</v>
+        <v>93.201229213570272</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.455748902021696</v>
+        <v>95.343410725257925</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.641390718634668</v>
+        <v>97.526480344600841</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>99.868364827003532</v>
+        <v>99.750833613325028</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.13706723490054</v>
+        <v>102.01686607315654</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.22936600504498</v>
+        <v>93.119647972152066</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.005640460510392</v>
+        <v>95.892655137652127</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>98.860841834685289</v>
+        <v>98.744496335825488</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>101.79649551360689</v>
+        <v>101.67669515754162</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>104.81414165283303</v>
+        <v>104.69078994580882</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.15320995437142</v>
+        <v>93.043581546587319</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.523487056383189</v>
+        <v>96.409892299906801</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.02059953946069</v>
+        <v>99.902889166640549</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>103.64822008908608</v>
+        <v>103.5262405100293</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.41009260355546</v>
+        <v>107.28368582232014</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.082201981715386</v>
+        <v>92.972657140466325</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.011156111703954</v>
+        <v>96.896987436389068</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.12358588805827</v>
+        <v>101.00457745328983</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.42656630143439</v>
+        <v>105.30249385554195</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>109.92737837395296</v>
+        <v>109.79800909651293</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.015994081803029</v>
+        <v>92.906527158069139</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.470406224407</v>
+        <v>97.355697075407363</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.17257989791335</v>
+        <v>102.05233694269057</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.13444191795541</v>
+        <v>107.00835953934434</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.36838275736869</v>
+        <v>112.23614075633621</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>92.954261774192446</v>
+        <v>92.844867500822346</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>97.902893510029415</v>
+        <v>97.787675383480504</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.17022455064266</v>
+        <v>103.04880750603674</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>108.77463947974249</v>
+        <v>108.64662681609629</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>114.73541731098398</v>
+        <v>114.60038963858914</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>92.896702513017061</v>
+        <v>92.787375978913914</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.310177573878946</v>
+        <v>98.194480130477103</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.11903345114041</v>
+        <v>103.99649979005821</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.34984086775241</v>
+        <v>110.21997441055265</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.03072354479272</v>
+        <v>116.89299461531921</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>92.843034204228815</v>
+        <v>92.733770830281316</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>98.693727135173177</v>
+        <v>98.577578307135937</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.02139716070472</v>
+        <v>104.89780154269404</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>111.86262168793915</v>
+        <v>111.73097489753644</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.25647504424364</v>
+        <v>119.11612671396659</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.624448710495358</v>
+        <v>92.515442581356211</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.30114260677642</v>
+        <v>100.18310207367732</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>108.91232909735444</v>
+        <v>108.78415439212583</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>118.57344107901417</v>
+        <v>118.43389658497752</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.41348647510023</v>
+        <v>129.26118475114458</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.470408241346007</v>
+        <v>92.361583396473677</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.49169499017454</v>
+        <v>101.37225334204956</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>111.93971642279364</v>
+        <v>111.80797890258103</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.05589726984822</v>
+        <v>123.90990068529055</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.12204216482849</v>
+        <v>137.95949167870103</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.36185361710973</v>
+        <v>92.253156525973623</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.37349251088719</v>
+        <v>102.25301310938548</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.29521226991997</v>
+        <v>114.1607026578021</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.53483257309728</v>
+        <v>128.38356490291514</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>145.58870130146212</v>
+        <v>145.41736359315499</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.285353548600682</v>
+        <v>92.17674648743467</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.02660687895525</v>
+        <v>102.90535885242916</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.12793470989544</v>
+        <v>115.99126823766397</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.19393366800981</v>
+        <v>132.03835974335558</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>151.99056639241329</v>
+        <v>151.81169457683157</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>151.99056639241329</v>
+        <v>151.81169457683157</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.19393366800981</v>
+        <v>132.03835974335558</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.12793470989544</v>
+        <v>115.99126823766397</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.02660687895525</v>
+        <v>102.90535885242916</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.285353548600682</v>
+        <v>92.17674648743467</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.19393366800981</v>
+        <v>132.03835974335558</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.12793470989544</v>
+        <v>115.99126823766397</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.02660687895525</v>
+        <v>102.90535885242916</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.06580254378328</v>
+        <v>115.92920919249359</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>151.99056639241329</v>
+        <v>151.81169457683157</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.285353548600682</v>
+        <v>92.17674648743467</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.3</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19972450617404428</v>
+        <v>0.19353650913892836</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1348866084834517E-2</v>
+        <v>3.1393173091321724E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.26549467131863</v>
+        <v>120.12395886489134</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.2696834970323</v>
+        <v>120.12814276093812</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.421886945308138</v>
+        <v>55.356663071378506</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>63.804437015468594</v>
+        <v>63.739213141538961</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46947013197888654</v>
+        <v>0.46938800765608102</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.467433745166034</v>
+        <v>69.385680210767589</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.105875827605686</v>
+        <v>79.024122293207242</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34223963370541766</v>
+        <v>0.34214520533668791</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.201543226733989</v>
+        <v>86.100095966493498</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.253678146658942</v>
+        <v>97.152230886418451</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19134180246420784</v>
+        <v>0.1912335240658376</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.487546246496706</v>
+        <v>97.372816926068381</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.45483716217629</v>
+        <v>109.34010784174797</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.988993508643095E-2</v>
+        <v>8.9772690852392256E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.3</v>
+        <v>80.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1716417.3043316</v>
+        <v>1740226.3716048</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19972450617404428</v>
+        <v>0.19353650913892836</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.26549467131863</v>
+        <v>120.12395886489134</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>63.804437015468594</v>
+        <v>63.739213141538961</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.105875827605686</v>
+        <v>79.024122293207242</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.253678146658942</v>
+        <v>97.152230886418451</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.45483716217629</v>
+        <v>109.34010784174797</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8137741683054476E-2</v>
+        <v>6.7126417336250729E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.697761194029851E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7859839997991402</v>
+        <v>-4.7803515604464319</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6926628647200008</v>
+        <v>8.682432806198884</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.667510866832741</v>
+        <v>13.651426102223592</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.574189731753602</v>
+        <v>17.553507347976044</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4522878219988347</v>
+        <v>1.4505786806643819</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.55303494652591</v>
+        <v>122.40880702247605</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.99 HKD</v>
+        <v>151.81 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.19 HKD</v>
+        <v>132.04 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.13 HKD</v>
+        <v>115.99 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.03 HKD</v>
+        <v>102.91 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.29 HKD</v>
+        <v>92.18 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.26549467131863</v>
+        <v>120.12395886489134</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.421886945308138</v>
+        <v>55.356663071378506</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>63.804437015468594</v>
+        <v>63.739213141538961</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.467433745166034</v>
+        <v>69.385680210767589</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.105875827605686</v>
+        <v>79.024122293207242</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.201543226733989</v>
+        <v>86.100095966493498</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.253678146658942</v>
+        <v>97.152230886418451</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.487546246496706</v>
+        <v>97.372816926068381</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.45483716217629</v>
+        <v>109.34010784174797</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40CB57A-7E46-473E-806E-1615A6CF1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A7DEB-3F92-49BB-95D4-B9DD298A06C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>80.400000000000006</v>
+        <v>80.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1740226.3716048</v>
+        <v>1735897.4502824002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19353650913892836</v>
+        <v>0.19464980730215867</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.12395886489134</v>
+        <v>120.14856330049892</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.739213141538961</v>
+        <v>63.75055159112771</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.024122293207242</v>
+        <v>79.038334241572628</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.152230886418451</v>
+        <v>97.169866371354445</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.34010784174797</v>
+        <v>109.36005226604621</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7126417336250729E-2</v>
+        <v>6.7307598366971477E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.697761194029851E-2</v>
+        <v>5.7119700748129679E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7803515604464319</v>
+        <v>-4.7813306977747558</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.682432806198884</v>
+        <v>8.6842111888039515</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.651426102223592</v>
+        <v>13.654222260772293</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.553507347976044</v>
+        <v>17.557102751801491</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4505786806643819</v>
+        <v>1.4508757959949072</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.81 HKD</v>
+        <v>151.84 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.243944712349753E-2</v>
+        <v>-4.244611781713583E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.04 HKD</v>
+        <v>132.07 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.7590224537474284E-3</v>
+        <v>4.7516987095969406E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>115.99 HKD</v>
+        <v>116.02 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0787531491188954E-2</v>
+        <v>5.0779532508434304E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.91 HKD</v>
+        <v>102.93 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5298360356707204E-2</v>
+        <v>9.5289671354866282E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.18 HKD</v>
+        <v>92.2 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1380126047682638</v>
+        <v>0.13800321846954341</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.12395886489134</v>
+        <v>120.14856330049892</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.356663071378506</v>
+        <v>55.368001520967255</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.739213141538961</v>
+        <v>63.75055159112771</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.385680210767589</v>
+        <v>69.399892159132975</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.024122293207242</v>
+        <v>79.038334241572628</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.100095966493498</v>
+        <v>86.117731451429492</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.152230886418451</v>
+        <v>97.169866371354445</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.372816926068381</v>
+        <v>97.392761350366627</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.34010784174797</v>
+        <v>109.36005226604621</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.341143407899438</v>
+        <v>74.356370360900812</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4505786806643819</v>
+        <v>1.4508757959949072</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103468.82899292336</v>
+        <v>-103490.02203521406</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7803515604464319</v>
+        <v>-4.7813306977747567</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>187927.84252529807</v>
+        <v>187966.3349171904</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.682432806198884</v>
+        <v>8.6842111888039515</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>295479.74767541816</v>
+        <v>295540.26942722959</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.651426102223592</v>
+        <v>13.654222260772295</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>379938.76120779285</v>
+        <v>380016.5823092059</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.553507347976044</v>
+        <v>17.557102751801491</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.697761194029851E-2</v>
+        <v>5.7119700748129679E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.697761194029851E-2</v>
+        <v>5.7119700748129679E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4067164179104482E-2</v>
+        <v>5.4201995012468834E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9365671641791044E-2</v>
+        <v>4.9488778054862848E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5447761194029851E-2</v>
+        <v>4.5561097256857856E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3969639538345584</v>
+        <v>5.3980693890311118</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1428467592084317</v>
+        <v>6.1441049701345651</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6115125258599408</v>
+        <v>5.6126619060494418</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.4927124848777718</v>
+        <v>5.4938375318036492</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9813198095194338</v>
+        <v>4.982340110245886</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7126417336250729E-2</v>
+        <v>6.7307598366971477E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6403566656821284E-2</v>
+        <v>7.6609787657538217E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.9794931913680844E-2</v>
+        <v>6.9983315536776086E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.8317319463653867E-2</v>
+        <v>6.8501714860394622E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.1956714048749174E-2</v>
+        <v>6.2123941524262913E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.960228753012992E-2</v>
+        <v>7.9800796975342203E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5814849236155599E-2</v>
+        <v>7.6003913698091147E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2171070413201394E-2</v>
+        <v>7.2351048144905131E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6833833745862076E-2</v>
+        <v>6.7000501660440276E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.553507347976044</v>
+        <v>17.557102751801491</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2649490.4738457175</v>
+        <v>2650033.156740726</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.12814276093812</v>
+        <v>120.1527480535138</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.382564427815325</v>
+        <v>93.401691547126475</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.140854998613747</v>
+        <v>94.160137435079747</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>94.899145569412113</v>
+        <v>94.918583323032976</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>95.657436140210521</v>
+        <v>95.677029210986234</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.415726711008929</v>
+        <v>96.435475098939492</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.288725094991293</v>
+        <v>93.307832993625368</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>94.76017841605713</v>
+        <v>94.779587705677898</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.245772353827832</v>
+        <v>96.265485930792494</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>97.745506908303426</v>
+        <v>97.765527668969185</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.259382079483856</v>
+        <v>99.279712920207913</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.201229213570272</v>
+        <v>93.220319190827126</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.343410725257925</v>
+        <v>95.362939475658465</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.526480344600841</v>
+        <v>97.546456243067297</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>99.750833613325028</v>
+        <v>99.771265115796595</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.01686607315654</v>
+        <v>102.0377617165894</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.119647972152066</v>
+        <v>93.138721239500086</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>95.892655137652127</v>
+        <v>95.912296387248546</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>98.744496335825488</v>
+        <v>98.764721714881063</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>101.67669515754162</v>
+        <v>101.69752112533718</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>104.69078994580882</v>
+        <v>104.7122332767169</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.043581546587319</v>
+        <v>93.062639233600763</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.409892299906801</v>
+        <v>96.429639492801911</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>99.902889166640549</v>
+        <v>99.923351813948713</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>103.5262405100293</v>
+        <v>103.54744531165585</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.28368582232014</v>
+        <v>107.30566024411328</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>92.972657140466325</v>
+        <v>92.991700300361273</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>96.896987436389068</v>
+        <v>96.916834398730941</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.00457745328983</v>
+        <v>101.02526575432074</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.30249385554195</v>
+        <v>105.32406247893624</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>109.79800909651293</v>
+        <v>109.82049851552796</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>92.906527158069139</v>
+        <v>92.925556772865264</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.355697075407363</v>
+        <v>97.375637993125679</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.05233694269057</v>
+        <v>102.0732398514578</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.00835953934434</v>
+        <v>107.03027756732676</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.23614075633621</v>
+        <v>112.2591295665967</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>92.844867500822346</v>
+        <v>92.863884486155712</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>97.787675383480504</v>
+        <v>97.80770478132024</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.04880750603674</v>
+        <v>103.06991451726647</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>108.64662681609629</v>
+        <v>108.66888040279738</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>114.60038963858914</v>
+        <v>114.62386270702703</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>92.787375978913914</v>
+        <v>92.806381188524412</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.194480130477103</v>
+        <v>98.214592852254015</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>103.99649979005821</v>
+        <v>104.01780091272082</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.21997441055265</v>
+        <v>110.24255025877378</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>116.89299461531921</v>
+        <v>116.91693726744431</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>92.733770830281316</v>
+        <v>92.75276506019685</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>98.577578307135937</v>
+        <v>98.597769497142735</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>104.89780154269404</v>
+        <v>104.91928727483128</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>111.73097489753644</v>
+        <v>111.75386023700757</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.11612671396659</v>
+        <v>119.14052471997017</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.515442581356211</v>
+        <v>92.534392092105037</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.18310207367732</v>
+        <v>100.20362211570085</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>108.78415439212583</v>
+        <v>108.80643614796504</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>118.43389658497752</v>
+        <v>118.45815485293519</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.26118475114458</v>
+        <v>129.28766072252301</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.361583396473677</v>
+        <v>92.380501392956376</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.37225334204956</v>
+        <v>101.39301695243437</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>111.80797890258103</v>
+        <v>111.83088001442681</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>123.90990068529055</v>
+        <v>123.93528057787287</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>137.95949167870103</v>
+        <v>137.98774928410748</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.253156525973623</v>
+        <v>92.272052313881289</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.25301310938548</v>
+        <v>102.27395712172495</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.1607026578021</v>
+        <v>114.18408566718678</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.38356490291514</v>
+        <v>128.40986111547403</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>145.41736359315499</v>
+        <v>145.44714876001566</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.17674648743467</v>
+        <v>92.195626624627096</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>102.90535885242916</v>
+        <v>102.9264364817338</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>115.99126823766397</v>
+        <v>116.01502619334046</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.03835974335558</v>
+        <v>132.06540455065911</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>151.81169457683157</v>
+        <v>151.84278946497037</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>151.81169457683157</v>
+        <v>151.84278946497037</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.03835974335558</v>
+        <v>132.06540455065911</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>115.99126823766397</v>
+        <v>116.01502619334046</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>102.90535885242916</v>
+        <v>102.9264364817338</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.17674648743467</v>
+        <v>92.195626624627096</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.03835974335558</v>
+        <v>132.06540455065911</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>115.99126823766397</v>
+        <v>116.01502619334046</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>102.90535885242916</v>
+        <v>102.9264364817338</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>115.92920919249359</v>
+        <v>115.95295443690253</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>151.81169457683157</v>
+        <v>151.84278946497037</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.17674648743467</v>
+        <v>92.195626624627096</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>80.400000000000006</v>
+        <v>80.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19353650913892836</v>
+        <v>0.19464980730215867</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1393173091321724E-2</v>
+        <v>3.1385463313033997E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.12395886489134</v>
+        <v>120.14856330049892</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.12814276093812</v>
+        <v>120.1527480535138</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.356663071378506</v>
+        <v>55.368001520967255</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>63.739213141538961</v>
+        <v>63.75055159112771</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46938800765608102</v>
+        <v>0.46940229795604238</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.385680210767589</v>
+        <v>69.399892159132975</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.024122293207242</v>
+        <v>79.038334241572628</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34214520533668791</v>
+        <v>0.34216163664069033</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.100095966493498</v>
+        <v>86.117731451429492</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.152230886418451</v>
+        <v>97.169866371354445</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.1912335240658376</v>
+        <v>0.19125236538761892</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.372816926068381</v>
+        <v>97.392761350366627</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.34010784174797</v>
+        <v>109.36005226604621</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.9772690852392256E-2</v>
+        <v>8.9793092302485444E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>80.400000000000006</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1740226.3716048</v>
+        <v>1735897.4502824002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19353650913892836</v>
+        <v>0.19464980730215867</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.12395886489134</v>
+        <v>120.14856330049892</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>63.739213141538961</v>
+        <v>63.75055159112771</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.024122293207242</v>
+        <v>79.038334241572628</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.152230886418451</v>
+        <v>97.169866371354445</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.34010784174797</v>
+        <v>109.36005226604621</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7126417336250729E-2</v>
+        <v>6.7307598366971477E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.697761194029851E-2</v>
+        <v>5.7119700748129679E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7803515604464319</v>
+        <v>-4.7813306977747558</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.682432806198884</v>
+        <v>8.6842111888039515</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.651426102223592</v>
+        <v>13.654222260772293</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.553507347976044</v>
+        <v>17.557102751801491</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4505786806643819</v>
+        <v>1.4508757959949072</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.40880702247605</v>
+        <v>122.43387945297742</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.81 HKD</v>
+        <v>151.84 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.04 HKD</v>
+        <v>132.07 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>115.99 HKD</v>
+        <v>116.02 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.91 HKD</v>
+        <v>102.93 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.18 HKD</v>
+        <v>92.2 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.12395886489134</v>
+        <v>120.14856330049892</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.356663071378506</v>
+        <v>55.368001520967255</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>63.739213141538961</v>
+        <v>63.75055159112771</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.385680210767589</v>
+        <v>69.399892159132975</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.024122293207242</v>
+        <v>79.038334241572628</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.100095966493498</v>
+        <v>86.117731451429492</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.152230886418451</v>
+        <v>97.169866371354445</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.372816926068381</v>
+        <v>97.392761350366627</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.34010784174797</v>
+        <v>109.36005226604621</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A7DEB-3F92-49BB-95D4-B9DD298A06C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AD5DA-EFFA-457E-A967-6E0F6DD7B41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>80.2</v>
+        <v>78.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1735897.4502824002</v>
+        <v>1699101.619042</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19464980730215867</v>
+        <v>0.20530762147104514</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.14856330049892</v>
+        <v>120.69825603350384</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.75055159112771</v>
+        <v>64.003866214632282</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.038334241572628</v>
+        <v>79.355846289517714</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.169866371354445</v>
+        <v>97.563864350700428</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.36005226604621</v>
+        <v>109.80563473237734</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7307598366971477E-2</v>
+        <v>6.9079823478540248E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7119700748129679E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7813306977747558</v>
+        <v>-4.8032058052788429</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6842111888039515</v>
+        <v>8.7239423986597551</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.654222260772293</v>
+        <v>13.71669181134701</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.557102751801491</v>
+        <v>17.637428404727924</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4508757959949072</v>
+        <v>1.4575137104205371</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.84 HKD</v>
+        <v>152.54 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.244611781713583E-2</v>
+        <v>-4.2594441266483242E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.07 HKD</v>
+        <v>132.67 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.7516987095969406E-3</v>
+        <v>4.5888554036050801E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.02 HKD</v>
+        <v>116.55 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0779532508434304E-2</v>
+        <v>5.0601676146451807E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.93 HKD</v>
+        <v>103.4 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5289671354866282E-2</v>
+        <v>9.5096473443269297E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.2 HKD</v>
+        <v>92.62 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13800321846954341</v>
+        <v>0.13779451732867148</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.14856330049892</v>
+        <v>120.69825603350384</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.368001520967255</v>
+        <v>55.621316144471827</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.75055159112771</v>
+        <v>64.003866214632282</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.399892159132975</v>
+        <v>69.717404207078062</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.038334241572628</v>
+        <v>79.355846289517714</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.117731451429492</v>
+        <v>86.511729430775475</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.169866371354445</v>
+        <v>97.563864350700428</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.392761350366627</v>
+        <v>97.838343816697758</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.36005226604621</v>
+        <v>109.80563473237734</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.356370360900812</v>
+        <v>74.696558835213068</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4508757959949072</v>
+        <v>1.4575137104205371</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103490.02203521406</v>
+        <v>-103963.50013173523</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7813306977747567</v>
+        <v>-4.8032058052788429</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>187966.3349171904</v>
+        <v>188826.30132473807</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.6842111888039515</v>
+        <v>8.7239423986597551</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>295540.26942722959</v>
+        <v>296892.39827464777</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.654222260772295</v>
+        <v>13.71669181134701</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>380016.5823092059</v>
+        <v>381755.19946765061</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.557102751801491</v>
+        <v>17.63742840472792</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7119700748129679E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7119700748129679E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4201995012468834E-2</v>
+        <v>5.5375796178343956E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9488778054862848E-2</v>
+        <v>5.0560509554140133E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5561097256857856E-2</v>
+        <v>4.6547770700636946E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.3980693890311118</v>
+        <v>5.4227661430654086</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1441049701345651</v>
+        <v>6.1722149180201278</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6126619060494418</v>
+        <v>5.6383404441677243</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.4938375318036492</v>
+        <v>5.5189724354977443</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.982340110245886</v>
+        <v>5.0051348576546513</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7307598366971477E-2</v>
+        <v>6.9079823478540248E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6609787657538217E-2</v>
+        <v>7.8626941630829658E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.9983315536776086E-2</v>
+        <v>7.1825992919334072E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.8501714860394622E-2</v>
+        <v>7.0305381343920309E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.2123941524262913E-2</v>
+        <v>6.3759679715345879E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9800796975342203E-2</v>
+        <v>8.1528967100922875E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6003913698091147E-2</v>
+        <v>7.7649858325947896E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2351048144905131E-2</v>
+        <v>7.3917886130208818E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7000501660440276E-2</v>
+        <v>6.845146793843708E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.557102751801491</v>
+        <v>17.637428404727924</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2650033.156740726</v>
+        <v>2662157.3463978181</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.1527480535138</v>
+        <v>120.70245993221847</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.401691547126475</v>
+        <v>93.829014435419452</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.160137435079747</v>
+        <v>94.59093029572638</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>94.918583323032976</v>
+        <v>95.35284615603328</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>95.677029210986234</v>
+        <v>96.114762016340208</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.435475098939492</v>
+        <v>96.876677876647122</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.307832993625368</v>
+        <v>93.734726468836953</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>94.779587705677898</v>
+        <v>95.213214618624889</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.265485930792494</v>
+        <v>96.705910989584027</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>97.765527668969185</v>
+        <v>98.212815581714437</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.279712920207913</v>
+        <v>99.733928395016036</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.220319190827126</v>
+        <v>93.646812280881264</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.362939475658465</v>
+        <v>95.799235286342849</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.546456243067297</v>
+        <v>97.992741880233723</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>99.771265115796595</v>
+        <v>100.22772949531391</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.0377617165894</v>
+        <v>102.50459556434346</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.138721239500086</v>
+        <v>93.564841010060078</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>95.912296387248546</v>
+        <v>96.351105565499154</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>98.764721714881063</v>
+        <v>99.216581048963477</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>101.69752112533718</v>
+        <v>102.16279833541412</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>104.7122332767169</v>
+        <v>105.19130312247914</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.062639233600763</v>
+        <v>93.488410920716348</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.429639492801911</v>
+        <v>96.870815571977332</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>99.923351813948713</v>
+        <v>100.38051200663652</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>103.54744531165585</v>
+        <v>104.02118612590662</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.30566024411328</v>
+        <v>107.79659530006528</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>92.991700300361273</v>
+        <v>93.417147434148731</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>96.916834398730941</v>
+        <v>97.360239447541872</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.02526575432074</v>
+        <v>101.48746732302487</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.32406247893624</v>
+        <v>105.80593150978285</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>109.82049851552796</v>
+        <v>110.32293922984576</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>92.925556772865264</v>
+        <v>93.350701292826969</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.375637993125679</v>
+        <v>97.821142118236708</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.0732398514578</v>
+        <v>102.54023601553409</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.03027756732676</v>
+        <v>107.51995271760808</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.2591295665967</v>
+        <v>112.7727272829662</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>92.863884486155712</v>
+        <v>93.288746848704108</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>97.80770478132024</v>
+        <v>98.255185658937663</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.06991451726647</v>
+        <v>103.54147057624218</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>108.66888040279738</v>
+        <v>109.16605233910923</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>114.62386270702703</v>
+        <v>115.14827933447698</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>92.806381188524412</v>
+        <v>93.230980467237572</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.214592852254015</v>
+        <v>98.663935287010318</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.01780091272082</v>
+        <v>104.4936936549575</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.24255025877378</v>
+        <v>110.74692190567905</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>116.91693726744431</v>
+        <v>117.45184496018437</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>92.75276506019685</v>
+        <v>93.177119039296727</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>98.597769497142735</v>
+        <v>99.04886500668718</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>104.91928727483128</v>
+        <v>105.39930441513434</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>111.75386023700757</v>
+        <v>112.26514629128928</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.14052471997017</v>
+        <v>119.68560556693096</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.534392092105037</v>
+        <v>92.957746991146465</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.20362211570085</v>
+        <v>100.66206457547466</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>108.80643614796504</v>
+        <v>109.30423741675848</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>118.45815485293519</v>
+        <v>119.00011378360479</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.28766072252301</v>
+        <v>129.87916581933075</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.380501392956376</v>
+        <v>92.803152225326713</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.39301695243437</v>
+        <v>101.85690102283144</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>111.83088001442681</v>
+        <v>112.34251844255954</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>123.93528057787287</v>
+        <v>124.50229795390418</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>137.98774928410748</v>
+        <v>138.6190582314768</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.272052313881289</v>
+        <v>92.694206979930271</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.27395712172495</v>
+        <v>102.74187158912359</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.18408566718678</v>
+        <v>114.70649026689122</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.40986111547403</v>
+        <v>128.99735018369373</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>145.44714876001566</v>
+        <v>146.11258527056052</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.195626624627096</v>
+        <v>92.617431634842973</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>102.9264364817338</v>
+        <v>103.39733611310596</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.01502619334046</v>
+        <v>116.54580754491062</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.06540455065911</v>
+        <v>132.66961812732322</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>151.84278946497037</v>
+        <v>152.53748672672066</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>151.84278946497037</v>
+        <v>152.53748672672066</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.06540455065911</v>
+        <v>132.66961812732322</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.01502619334046</v>
+        <v>116.54580754491062</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>102.9264364817338</v>
+        <v>103.39733611310596</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.195626624627096</v>
+        <v>92.617431634842973</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.06540455065911</v>
+        <v>132.66961812732322</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.01502619334046</v>
+        <v>116.54580754491062</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>102.9264364817338</v>
+        <v>103.39733611310596</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>115.95295443690253</v>
+        <v>116.48345180344197</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>151.84278946497037</v>
+        <v>152.53748672672066</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.195626624627096</v>
+        <v>92.617431634842973</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>80.2</v>
+        <v>78.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19464980730215867</v>
+        <v>0.20530762147104514</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1385463313033997E-2</v>
+        <v>3.121403702211821E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.14856330049892</v>
+        <v>120.69825603350384</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.1527480535138</v>
+        <v>120.70245993221847</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009316</v>
+        <v>0.1461282787700931</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.368001520967255</v>
+        <v>55.621316144471827</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>63.75055159112771</v>
+        <v>64.003866214632282</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46940229795604238</v>
+        <v>0.46972004138265366</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.399892159132975</v>
+        <v>69.717404207078062</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.038334241572628</v>
+        <v>79.355846289517714</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34216163664069033</v>
+        <v>0.3425269850834477</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.117731451429492</v>
+        <v>86.511729430775475</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.169866371354445</v>
+        <v>97.563864350700428</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19125236538761892</v>
+        <v>0.19167130034075797</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.392761350366627</v>
+        <v>97.838343816697758</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.36005226604621</v>
+        <v>109.80563473237734</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.9793092302485444E-2</v>
+        <v>9.0246716556558026E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>80.2</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1735897.4502824002</v>
+        <v>1699101.619042</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19464980730215867</v>
+        <v>0.20530762147104514</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.14856330049892</v>
+        <v>120.69825603350384</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>63.75055159112771</v>
+        <v>64.003866214632282</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.038334241572628</v>
+        <v>79.355846289517714</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.169866371354445</v>
+        <v>97.563864350700428</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.36005226604621</v>
+        <v>109.80563473237734</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7307598366971477E-2</v>
+        <v>6.9079823478540248E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7119700748129679E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7813306977747558</v>
+        <v>-4.8032058052788429</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.6842111888039515</v>
+        <v>8.7239423986597551</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.654222260772293</v>
+        <v>13.71669181134701</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.557102751801491</v>
+        <v>17.637428404727924</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4508757959949072</v>
+        <v>1.4575137104205371</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.43387945297742</v>
+        <v>122.99402775571303</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>151.84 HKD</v>
+        <v>152.54 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.07 HKD</v>
+        <v>132.67 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.02 HKD</v>
+        <v>116.55 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>102.93 HKD</v>
+        <v>103.4 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.2 HKD</v>
+        <v>92.62 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.14856330049892</v>
+        <v>120.69825603350384</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.368001520967255</v>
+        <v>55.621316144471827</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>63.75055159112771</v>
+        <v>64.003866214632282</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.399892159132975</v>
+        <v>69.717404207078062</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.038334241572628</v>
+        <v>79.355846289517714</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.117731451429492</v>
+        <v>86.511729430775475</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.169866371354445</v>
+        <v>97.563864350700428</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.392761350366627</v>
+        <v>97.838343816697758</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.36005226604621</v>
+        <v>109.80563473237734</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AD5DA-EFFA-457E-A967-6E0F6DD7B41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C6755C-2895-4AB6-AB17-09CE8D645B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1699101.619042</v>
+        <v>1692608.2370584002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20530762147104514</v>
+        <v>0.20744728707916196</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.69825603350384</v>
+        <v>120.87002974929135</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.003866214632282</v>
+        <v>64.083024609004411</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.355846289517714</v>
+        <v>79.455065764340816</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.563864350700428</v>
+        <v>97.686984946737908</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.80563473237734</v>
+        <v>109.94487498667915</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9079823478540248E-2</v>
+        <v>6.9443524836715065E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.8580562659846548E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8032058052788429</v>
+        <v>-4.8100415669209653</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7239423986597551</v>
+        <v>8.7363580213156311</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.71669181134701</v>
+        <v>13.736212947759235</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.637428404727924</v>
+        <v>17.662529402153897</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4575137104205371</v>
+        <v>1.4595879951208952</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.54 HKD</v>
+        <v>152.75 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2594441266483242E-2</v>
+        <v>-4.2640514743617922E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.67 HKD</v>
+        <v>132.86 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5888554036050801E-3</v>
+        <v>4.5382719495928809E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.55 HKD</v>
+        <v>116.71 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0601676146451807E-2</v>
+        <v>5.0546429574161181E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.4 HKD</v>
+        <v>103.54 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5096473443269297E-2</v>
+        <v>9.5036461772337613E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.62 HKD</v>
+        <v>92.75 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13779451732867148</v>
+        <v>0.13772969039240254</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.69825603350384</v>
+        <v>120.87002974929135</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.621316144471827</v>
+        <v>55.700474538843949</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.003866214632282</v>
+        <v>64.083024609004411</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.717404207078062</v>
+        <v>69.816623681901163</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.355846289517714</v>
+        <v>79.455065764340816</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.511729430775475</v>
+        <v>86.634850026812956</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.563864350700428</v>
+        <v>97.686984946737908</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.838343816697758</v>
+        <v>97.977584070999569</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.80563473237734</v>
+        <v>109.94487498667915</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.696558835213068</v>
+        <v>74.802864476150461</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4575137104205371</v>
+        <v>1.4595879951208952</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103963.50013173523</v>
+        <v>-104111.45750337238</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8032058052788429</v>
+        <v>-4.8100415669209653</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>188826.30132473807</v>
+        <v>189095.03259296753</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7239423986597551</v>
+        <v>8.7363580213156311</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>296892.39827464777</v>
+        <v>297314.92559290957</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.71669181134701</v>
+        <v>13.736212947759235</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>381755.19946765061</v>
+        <v>382298.50068250473</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.63742840472792</v>
+        <v>17.662529402153901</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.8580562659846548E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.8580562659846548E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5375796178343956E-2</v>
+        <v>5.5588235294117654E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0560509554140133E-2</v>
+        <v>5.0754475703324808E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6547770700636946E-2</v>
+        <v>4.6726342710997446E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4227661430654086</v>
+        <v>5.4304836422311187</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1722149180201278</v>
+        <v>6.180999007583222</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6383404441677243</v>
+        <v>5.6463647414591529</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5189724354977443</v>
+        <v>5.5268268522368835</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0051348576546513</v>
+        <v>5.0122579979614867</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9079823478540248E-2</v>
+        <v>6.9443524836715065E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8626941630829658E-2</v>
+        <v>7.9040908025360887E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1825992919334072E-2</v>
+        <v>7.2204152704081231E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0305381343920309E-2</v>
+        <v>7.0675535194845054E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.3759679715345879E-2</v>
+        <v>6.4095370817921826E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1528967100922875E-2</v>
+        <v>8.1841738074455814E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7649858325947896E-2</v>
+        <v>7.7947747808016749E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3917886130208818E-2</v>
+        <v>7.4201458583393762E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.845146793843708E-2</v>
+        <v>6.8714069477842851E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.637428404727924</v>
+        <v>17.662529402153897</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2662157.3463978181</v>
+        <v>2665946.0395772364</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.70245993221847</v>
+        <v>120.87423963085388</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.829014435419452</v>
+        <v>93.962548746418776</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.59093029572638</v>
+        <v>94.72554893986144</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.35284615603328</v>
+        <v>95.488549133304062</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.114762016340208</v>
+        <v>96.251549326746726</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.876677876647122</v>
+        <v>97.014549520189391</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.734726468836953</v>
+        <v>93.868126592359957</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.213214618624889</v>
+        <v>95.348718876967908</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.705910989584027</v>
+        <v>96.843539603411628</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.212815581714437</v>
+        <v>98.352588771691131</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.733928395016036</v>
+        <v>99.875866381806361</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.646812280881264</v>
+        <v>93.780087287876214</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.799235286342849</v>
+        <v>95.935573549674274</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.992741880233723</v>
+        <v>98.132201868688767</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.22772949531391</v>
+        <v>100.37037024329273</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.50459556434346</v>
+        <v>102.6504766718592</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.564841010060078</v>
+        <v>93.697999358287632</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.351105565499154</v>
+        <v>96.488229232129669</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.216581048963477</v>
+        <v>99.357782764336932</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.16279833541412</v>
+        <v>102.30819300856048</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.19130312247914</v>
+        <v>105.34100786221344</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.488410920716348</v>
+        <v>93.621460496200399</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.870815571977332</v>
+        <v>97.008678872483912</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.38051200663652</v>
+        <v>100.52337018956874</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.02118612590662</v>
+        <v>104.16922559431876</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.79659530006528</v>
+        <v>107.95000780437518</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.417147434148731</v>
+        <v>93.550095589825318</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.360239447541872</v>
+        <v>97.498799279717289</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.48746732302487</v>
+        <v>101.63190088769132</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.80593150978285</v>
+        <v>105.95651096805399</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.32293922984576</v>
+        <v>110.47994714222895</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.350701292826969</v>
+        <v>93.483554884580514</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.821142118236708</v>
+        <v>97.960357891657381</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.54023601553409</v>
+        <v>102.68616784534636</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.51995271760808</v>
+        <v>107.67297151345942</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.7727272829662</v>
+        <v>112.93322165166289</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.288746848704108</v>
+        <v>93.421512268967646</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.255185658937663</v>
+        <v>98.39501914858927</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.54147057624218</v>
+        <v>103.68882732954977</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.16605233910923</v>
+        <v>109.3214138088138</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.14827933447698</v>
+        <v>115.31215450929585</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.230980467237572</v>
+        <v>93.363663676321607</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.663935287010318</v>
+        <v>98.804350495443543</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.4936936549575</v>
+        <v>104.64240558026066</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.74692190567905</v>
+        <v>110.90453321600725</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.45184496018437</v>
+        <v>117.61899849245505</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.177119039296727</v>
+        <v>93.309725594600337</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.04886500668718</v>
+        <v>99.189828034206101</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.39930441513434</v>
+        <v>105.54930517534237</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.26514629128928</v>
+        <v>112.42491828771757</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.68560556693096</v>
+        <v>119.85593811248825</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.957746991146465</v>
+        <v>93.090041343497944</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.66206457547466</v>
+        <v>100.80532345459362</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.30423741675848</v>
+        <v>109.45979554683774</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.00011378360479</v>
+        <v>119.16947076021326</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.87916581933075</v>
+        <v>130.06400549845569</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.803152225326713</v>
+        <v>92.935226563584891</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.85690102283144</v>
+        <v>102.00186035316706</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.34251844255954</v>
+        <v>112.50240055244231</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.50229795390418</v>
+        <v>124.67948545475498</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.6190582314768</v>
+        <v>138.81633623278262</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.694206979930271</v>
+        <v>92.826126270963783</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.74187158912359</v>
+        <v>102.8880903799314</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.70649026689122</v>
+        <v>114.86973670230468</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.99735018369373</v>
+        <v>129.18093489233812</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.11258527056052</v>
+        <v>146.32052780858922</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.617431634842973</v>
+        <v>92.74924166177658</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.39733611310596</v>
+        <v>103.54448773907271</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.54580754491062</v>
+        <v>116.71167163507519</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.66961812732322</v>
+        <v>132.85842908472029</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>152.53748672672066</v>
+        <v>152.75457296933104</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>152.53748672672066</v>
+        <v>152.75457296933104</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.66961812732322</v>
+        <v>132.85842908472029</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.54580754491062</v>
+        <v>116.71167163507519</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.39733611310596</v>
+        <v>103.54448773907271</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.617431634842973</v>
+        <v>92.74924166177658</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.66961812732322</v>
+        <v>132.85842908472029</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.54580754491062</v>
+        <v>116.71167163507519</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.39733611310596</v>
+        <v>103.54448773907271</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.48345180344197</v>
+        <v>116.64922715100359</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>152.53748672672066</v>
+        <v>152.75457296933104</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.617431634842973</v>
+        <v>92.74924166177658</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20530762147104514</v>
+        <v>0.20744728707916196</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.121403702211821E-2</v>
+        <v>3.1160787650782597E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.69825603350384</v>
+        <v>120.87002974929135</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.70245993221847</v>
+        <v>120.87423963085388</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.1461282787700931</v>
+        <v>0.14612827877009316</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.621316144471827</v>
+        <v>55.700474538843949</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.003866214632282</v>
+        <v>64.083024609004411</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46972004138265366</v>
+        <v>0.46981874049402117</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.717404207078062</v>
+        <v>69.816623681901163</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.355846289517714</v>
+        <v>79.455065764340816</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.3425269850834477</v>
+        <v>0.34264047151186661</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.511729430775475</v>
+        <v>86.634850026812956</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.563864350700428</v>
+        <v>97.686984946737908</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19167130034075797</v>
+        <v>0.19180143208899447</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.838343816697758</v>
+        <v>97.977584070999569</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.80563473237734</v>
+        <v>109.94487498667915</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0246716556558026E-2</v>
+        <v>9.0387623675390438E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1699101.619042</v>
+        <v>1692608.2370584002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20530762147104514</v>
+        <v>0.20744728707916196</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.69825603350384</v>
+        <v>120.87002974929135</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.003866214632282</v>
+        <v>64.083024609004411</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.355846289517714</v>
+        <v>79.455065764340816</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.563864350700428</v>
+        <v>97.686984946737908</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.80563473237734</v>
+        <v>109.94487498667915</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9079823478540248E-2</v>
+        <v>6.9443524836715065E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.8580562659846548E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8032058052788429</v>
+        <v>-4.8100415669209653</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7239423986597551</v>
+        <v>8.7363580213156311</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.71669181134701</v>
+        <v>13.736212947759235</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.637428404727924</v>
+        <v>17.662529402153897</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4575137104205371</v>
+        <v>1.4595879951208952</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.99402775571303</v>
+        <v>123.16906873692994</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.54 HKD</v>
+        <v>152.75 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.67 HKD</v>
+        <v>132.86 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.55 HKD</v>
+        <v>116.71 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.4 HKD</v>
+        <v>103.54 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.62 HKD</v>
+        <v>92.75 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.69825603350384</v>
+        <v>120.87002974929135</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.621316144471827</v>
+        <v>55.700474538843949</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.003866214632282</v>
+        <v>64.083024609004411</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.717404207078062</v>
+        <v>69.816623681901163</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.355846289517714</v>
+        <v>79.455065764340816</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.511729430775475</v>
+        <v>86.634850026812956</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.563864350700428</v>
+        <v>97.686984946737908</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.838343816697758</v>
+        <v>97.977584070999569</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.80563473237734</v>
+        <v>109.94487498667915</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C6755C-2895-4AB6-AB17-09CE8D645B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA5BCD-B44B-4DF6-8EB1-31DB36E5864B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20744728707916196</v>
+        <v>0.20696811599645942</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.87002974929135</v>
+        <v>120.71369875586933</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.083024609004411</v>
+        <v>64.010982676551862</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.455065764340816</v>
+        <v>79.364766273555546</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.686984946737908</v>
+        <v>97.574933082452347</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.94487498667915</v>
+        <v>109.81815264630512</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9443524836715065E-2</v>
+        <v>6.9353707904867126E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8100415669209653</v>
+        <v>-4.8038203508087696</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7363580213156311</v>
+        <v>8.7250585823132933</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.736212947759235</v>
+        <v>13.718446791662197</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.662529402153897</v>
+        <v>17.63968502316672</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4595879951208952</v>
+        <v>1.4577001918189734</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.75 HKD</v>
+        <v>152.56 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2640514743617922E-2</v>
+        <v>-4.2598588698183115E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.86 HKD</v>
+        <v>132.69 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5382719495928809E-3</v>
+        <v>4.5843019879555445E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.71 HKD</v>
+        <v>116.56 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0546429574161181E-2</v>
+        <v>5.0596702960234441E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.54 HKD</v>
+        <v>103.41 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5036461772337613E-2</v>
+        <v>9.5091071305291847E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.75 HKD</v>
+        <v>92.63 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13772969039240254</v>
+        <v>0.13778868172196021</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.87002974929135</v>
+        <v>120.71369875586933</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.700474538843949</v>
+        <v>55.628432606391407</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.083024609004411</v>
+        <v>64.010982676551862</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.816623681901163</v>
+        <v>69.726324191115893</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.455065764340816</v>
+        <v>79.364766273555546</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.634850026812956</v>
+        <v>86.522798162527394</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.686984946737908</v>
+        <v>97.574933082452347</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.977584070999569</v>
+        <v>97.850861730625539</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.94487498667915</v>
+        <v>109.81815264630512</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.802864476150461</v>
+        <v>74.706115876529651</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4595879951208952</v>
+        <v>1.4577001918189734</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104111.45750337238</v>
+        <v>-103976.80172797565</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8100415669209653</v>
+        <v>-4.8038203508087696</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>189095.03259296753</v>
+        <v>188850.46068082566</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7363580213156311</v>
+        <v>8.7250585823132933</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>297314.92559290957</v>
+        <v>296930.38413318177</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.736212947759235</v>
+        <v>13.718446791662197</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>382298.50068250473</v>
+        <v>381804.0430860318</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.662529402153901</v>
+        <v>17.63968502316672</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4304836422311187</v>
+        <v>5.4234599581606098</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.180999007583222</v>
+        <v>6.1730046212394747</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6463647414591529</v>
+        <v>5.6390618408882984</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5268268522368835</v>
+        <v>5.5196785596942748</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0122579979614867</v>
+        <v>5.0057752389704113</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9443524836715065E-2</v>
+        <v>6.9353707904867126E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9040908025360887E-2</v>
+        <v>7.8938678020965145E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.2204152704081231E-2</v>
+        <v>7.2110765228750623E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0675535194845054E-2</v>
+        <v>7.0584124804274617E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.4095370817921826E-2</v>
+        <v>6.4012471086578149E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.662529402153897</v>
+        <v>17.63968502316672</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2665946.0395772364</v>
+        <v>2662497.9557665423</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.87423963085388</v>
+        <v>120.71790319245125</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.962548746418776</v>
+        <v>93.841019376231131</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.72554893986144</v>
+        <v>94.603032719761799</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.488549133304062</v>
+        <v>95.365046063292425</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.251549326746726</v>
+        <v>96.127059406823065</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.014549520189391</v>
+        <v>96.889072750353719</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.868126592359957</v>
+        <v>93.746719345987259</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.348718876967908</v>
+        <v>95.225396660745488</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.843539603411628</v>
+        <v>96.718284014543897</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.352588771691131</v>
+        <v>98.225381407382557</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.875866381806361</v>
+        <v>99.746688839261381</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.780087287876214</v>
+        <v>93.658793909862439</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.935573549674274</v>
+        <v>95.811492306800091</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.132201868688767</v>
+        <v>98.005279548601294</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.37037024329273</v>
+        <v>100.24055311887555</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.6504766718592</v>
+        <v>102.51771050123244</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.697999358287632</v>
+        <v>93.576812151237874</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.488229232129669</v>
+        <v>96.363433194926074</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.357782764336932</v>
+        <v>99.229275301271215</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.30819300856048</v>
+        <v>102.17586954110196</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.34100786221344</v>
+        <v>105.20476180981042</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.621460496200399</v>
+        <v>93.500372283056493</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.008678872483912</v>
+        <v>96.883209695632132</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.52337018956874</v>
+        <v>100.39335517793631</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.16922559431876</v>
+        <v>104.03449510277392</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.95000780437518</v>
+        <v>107.8103873211588</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.550095589825318</v>
+        <v>93.429099678691543</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.498799279717289</v>
+        <v>97.37269619046954</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.63190088769132</v>
+        <v>101.50045212357587</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.95651096805399</v>
+        <v>105.81946883566167</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.47994714222895</v>
+        <v>110.33705448367843</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.483554884580514</v>
+        <v>93.362645035927031</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.960357891657381</v>
+        <v>97.833657831295483</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.68616784534636</v>
+        <v>102.55335551243587</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.67297151345942</v>
+        <v>107.53370934370308</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.93322165166289</v>
+        <v>112.78715597460652</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.421512268967646</v>
+        <v>93.300682665051028</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.39501914858927</v>
+        <v>98.267756905639686</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.68882732954977</v>
+        <v>103.55471817596708</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.3214138088138</v>
+        <v>109.18001957520205</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.31215450929585</v>
+        <v>115.16301196580956</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.363663676321607</v>
+        <v>93.242908892672475</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.804350495443543</v>
+        <v>98.676558831129327</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.64240558026066</v>
+        <v>104.50706308673796</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.90453321600725</v>
+        <v>110.76109140591896</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.61899849245505</v>
+        <v>117.46687232091553</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.309725594600337</v>
+        <v>93.189040573438376</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.189828034206101</v>
+        <v>99.061537800588127</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.54930517534237</v>
+        <v>105.41278971516344</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.42491828771757</v>
+        <v>112.27951004054692</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.85593811248825</v>
+        <v>119.70091872586677</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.090041343497944</v>
+        <v>92.969640457760505</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.80532345459362</v>
+        <v>100.67494376998056</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.45979554683774</v>
+        <v>109.31822233292274</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.16947076021326</v>
+        <v>119.01533923738528</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.06400549845569</v>
+        <v>129.89578319198156</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.935226563584891</v>
+        <v>92.815025912333937</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.00186035316706</v>
+        <v>101.86993309052816</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.50240055244231</v>
+        <v>112.35689209118681</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.67948545475498</v>
+        <v>124.51822738390882</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.81633623278262</v>
+        <v>138.6367938285035</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.826126270963783</v>
+        <v>92.706066727952518</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.8880903799314</v>
+        <v>102.7550168842621</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.86973670230468</v>
+        <v>114.72116637358013</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.18093489233812</v>
+        <v>129.01385473255993</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.32052780858922</v>
+        <v>146.13127962591071</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.74924166177658</v>
+        <v>92.629281559853879</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.54448773907271</v>
+        <v>103.41056527156609</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.71167163507519</v>
+        <v>116.5607189828048</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.85842908472029</v>
+        <v>132.6865925240246</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>152.75457296933104</v>
+        <v>152.55700311523583</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>152.75457296933104</v>
+        <v>152.55700311523583</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.85842908472029</v>
+        <v>132.6865925240246</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.71167163507519</v>
+        <v>116.5607189828048</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.54448773907271</v>
+        <v>103.41056527156609</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.74924166177658</v>
+        <v>92.629281559853879</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.85842908472029</v>
+        <v>132.6865925240246</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.71167163507519</v>
+        <v>116.5607189828048</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.54448773907271</v>
+        <v>103.41056527156609</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.64922715100359</v>
+        <v>116.49835526323909</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>152.75457296933104</v>
+        <v>152.55700311523583</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.74924166177658</v>
+        <v>92.629281559853879</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20744728707916196</v>
+        <v>0.20696811599645942</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1160787650782597E-2</v>
+        <v>3.1209243622619884E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.87002974929135</v>
+        <v>120.71369875586933</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.87423963085388</v>
+        <v>120.71790319245125</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.700474538843949</v>
+        <v>55.628432606391407</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.083024609004411</v>
+        <v>64.010982676551862</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46981874049402117</v>
+        <v>0.46972892607650696</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.816623681901163</v>
+        <v>69.726324191115893</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.455065764340816</v>
+        <v>79.364766273555546</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34264047151186661</v>
+        <v>0.34253720090159456</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.634850026812956</v>
+        <v>86.522798162527394</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.686984946737908</v>
+        <v>97.574933082452347</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19180143208899447</v>
+        <v>0.19168301453683967</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.977584070999569</v>
+        <v>97.850861730625539</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.94487498667915</v>
+        <v>109.81815264630512</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0387623675390438E-2</v>
+        <v>9.0259400729649553E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20744728707916196</v>
+        <v>0.20696811599645942</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.87002974929135</v>
+        <v>120.71369875586933</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.083024609004411</v>
+        <v>64.010982676551862</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.455065764340816</v>
+        <v>79.364766273555546</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.686984946737908</v>
+        <v>97.574933082452347</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.94487498667915</v>
+        <v>109.81815264630512</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9443524836715065E-2</v>
+        <v>6.9353707904867126E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8100415669209653</v>
+        <v>-4.8038203508087696</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7363580213156311</v>
+        <v>8.7250585823132933</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.736212947759235</v>
+        <v>13.718446791662197</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.662529402153897</v>
+        <v>17.63968502316672</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4595879951208952</v>
+        <v>1.4577001918189734</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.16906873692994</v>
+        <v>123.00976421028716</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.75 HKD</v>
+        <v>152.56 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.86 HKD</v>
+        <v>132.69 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.71 HKD</v>
+        <v>116.56 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.54 HKD</v>
+        <v>103.41 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.75 HKD</v>
+        <v>92.63 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.87002974929135</v>
+        <v>120.71369875586933</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.700474538843949</v>
+        <v>55.628432606391407</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.083024609004411</v>
+        <v>64.010982676551862</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.816623681901163</v>
+        <v>69.726324191115893</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.455065764340816</v>
+        <v>79.364766273555546</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.634850026812956</v>
+        <v>86.522798162527394</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.686984946737908</v>
+        <v>97.574933082452347</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.977584070999569</v>
+        <v>97.850861730625539</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.94487498667915</v>
+        <v>109.81815264630512</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA5BCD-B44B-4DF6-8EB1-31DB36E5864B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B987E31-B3AB-8E4B-BA9A-5B50636D9C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3275,27 +3286,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4047,7 +4058,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4089,17 +4100,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4108,7 +4119,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4182,10 +4193,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4196,7 +4207,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4234,7 +4245,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4244,7 +4255,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4255,19 +4266,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4275,8 +4286,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4299,29 +4310,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4338,15 +4349,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4357,11 +4368,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4422,14 +4433,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4442,7 +4453,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4479,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4496,7 +4507,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4542,7 +4553,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4557,13 +4568,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4579,53 +4590,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4642,7 +4653,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4655,21 +4666,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4679,14 +4690,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4695,8 +4706,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4708,7 +4719,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4716,7 +4727,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4755,7 +4766,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4769,39 +4780,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4812,7 +4823,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4823,10 +4834,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4835,7 +4846,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4848,7 +4859,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4857,8 +4868,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4866,10 +4877,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4878,10 +4889,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4898,16 +4909,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4928,7 +4939,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4946,7 +4957,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4956,10 +4967,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4974,7 +4985,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4988,34 +4999,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,30 +5036,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5330,7 +5341,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5339,7 +5350,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5352,7 +5363,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5360,7 +5371,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5374,7 +5385,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5388,7 +5399,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5398,7 +5409,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5408,16 +5419,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.2</v>
+        <v>78.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5426,43 +5437,43 @@
         <v>21644606612</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1692608.2370584002</v>
+        <v>1699101.619042</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20696811599645942</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.20553937277082149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5477,7 +5488,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5488,10 +5499,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1310185977458953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>1.1315830089569092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5505,14 +5516,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.71369875586933</v>
+        <v>120.7739384062487</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5521,7 +5532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5537,11 +5548,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5556,13 +5567,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.010982676551862</v>
+        <v>64.03874288409996</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5571,13 +5582,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.364766273555546</v>
+        <v>79.399561739478642</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5586,13 +5597,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.574933082452347</v>
+        <v>97.618110477933342</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5601,13 +5612,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.81815264630512</v>
+        <v>109.86698307533452</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5616,11 +5627,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5630,25 +5641,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5657,16 +5668,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5679,20 +5690,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5705,7 +5716,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5718,16 +5729,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5740,16 +5751,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5764,7 +5775,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5779,7 +5790,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5792,12 +5803,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5810,16 +5821,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5832,8 +5843,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5841,7 +5852,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5854,25 +5865,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5885,7 +5896,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5898,23 +5909,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9353707904867126E-2</v>
+        <v>6.9123139141263654E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8580562659846548E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5924,7 +5935,7 @@
         <v>1.0614782273563756</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5935,7 +5946,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5948,7 +5959,7 @@
         <v>0.11027130711998644</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5962,7 +5973,7 @@
         <v>0.15195683827249326</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5976,7 +5987,7 @@
         <v>0.48913824057450628</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5990,7 +6001,7 @@
         <v>1.4835789300471205</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6000,45 +6011,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6052,21 +6063,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8038203508087696</v>
+        <v>-4.8062175970318615</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6076,7 +6087,7 @@
         <v>6.4100114768294941E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6086,16 +6097,16 @@
         <v>0.67756727799881356</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6109,7 +6120,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6123,30 +6134,30 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7250585823132933</v>
+        <v>8.7294126405846821</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6160,38 +6171,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.718446791662197</v>
+        <v>13.725292696037547</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.63968502316672</v>
+        <v>17.648487739590369</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6201,42 +6212,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6245,7 +6256,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6254,7 +6265,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6263,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6272,76 +6283,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4577001918189734</v>
+        <v>1.4584276266570915</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6358,7 +6369,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (30yrs)</v>
@@ -6369,7 +6380,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.56 HKD</v>
+        <v>152.63 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,10 +6388,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2598588698183115E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
+        <v>-4.2614757061473781E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (30yrs)</v>
@@ -6391,7 +6402,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.69 HKD</v>
+        <v>132.75 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,10 +6410,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5843019879555445E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
+        <v>4.5665509464310585E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (30yrs)</v>
@@ -6413,7 +6424,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.56 HKD</v>
+        <v>116.62 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,10 +6432,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0596702960234441E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
+        <v>5.0577315496882672E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (30yrs)</v>
@@ -6435,7 +6446,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.41 HKD</v>
+        <v>103.46 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,10 +6454,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5091071305291847E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6">
+        <v>9.5070011630285764E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (30yrs)</v>
@@ -6457,7 +6468,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.63 HKD</v>
+        <v>92.68 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,32 +6476,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13778868172196021</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+        <v>0.13776593222835196</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.71369875586933</v>
+        <v>120.7739384062487</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6499,7 +6510,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6509,30 +6520,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6541,7 +6552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6554,14 +6565,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6580,7 +6591,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6590,18 +6601,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.628432606391407</v>
+        <v>55.656192813939505</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.010982676551862</v>
+        <v>64.03874288409996</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6611,25 +6622,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.726324191115893</v>
+        <v>69.761119657038989</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.364766273555546</v>
+        <v>79.399561739478642</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6648,7 +6659,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6658,18 +6669,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.522798162527394</v>
+        <v>86.56597555800839</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.574933082452347</v>
+        <v>97.618110477933342</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6679,18 +6690,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.850861730625539</v>
+        <v>97.899692159654933</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.81815264630512</v>
+        <v>109.86698307533452</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6700,21 +6711,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6723,92 +6734,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6824,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6852,15 +6863,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6909,7 +6920,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6925,7 +6936,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6933,7 +6944,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6957,7 +6968,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6985,7 +6996,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7013,7 +7024,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7041,7 +7052,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7057,7 +7068,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7081,7 +7092,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7097,7 +7108,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7113,7 +7124,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7137,7 +7148,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7161,7 +7172,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7185,7 +7196,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7209,7 +7220,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7233,13 +7244,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7263,7 +7274,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7279,7 +7290,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7295,7 +7306,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7319,7 +7330,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7343,7 +7354,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7367,7 +7378,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7396,7 +7407,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7404,7 +7415,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7432,7 +7443,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7457,7 +7468,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7482,7 +7493,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7507,7 +7518,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7532,7 +7543,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7548,12 +7559,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7602,7 +7613,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7651,7 +7662,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7700,7 +7711,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7749,7 +7760,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7798,7 +7809,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7847,7 +7858,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7896,7 +7907,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7945,7 +7956,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7994,7 +8005,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8043,7 +8054,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8092,7 +8103,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8141,7 +8152,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8190,12 +8201,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8244,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8293,12 +8304,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8347,7 +8358,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8396,7 +8407,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8445,7 +8456,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8494,13 +8505,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8549,7 +8560,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8598,7 +8609,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8647,7 +8658,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8696,7 +8707,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8745,12 +8756,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8800,7 +8811,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8899,7 +8910,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8948,7 +8959,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8998,7 +9009,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9014,13 +9025,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9069,7 +9080,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9103,7 +9114,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9137,7 +9148,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9186,7 +9197,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9267,7 +9278,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9278,7 +9289,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9294,7 +9305,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9305,7 +9316,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9325,7 +9336,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9348,7 +9359,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9369,7 +9380,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9390,7 +9401,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9412,7 +9423,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9433,7 +9444,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9455,7 +9466,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9475,7 +9486,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9488,7 +9499,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9512,12 +9523,12 @@
         <v>266242.2</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9537,7 +9548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9557,7 +9568,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9577,7 +9588,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9598,7 +9609,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9618,7 +9629,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9639,7 +9650,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9659,7 +9670,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9679,7 +9690,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9691,7 +9702,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9704,7 +9715,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9728,7 +9739,7 @@
         <v>236515.5</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9745,7 +9756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9764,7 +9775,7 @@
         <v>32419.400000000023</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9779,7 +9790,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9798,7 +9809,7 @@
         <v>27896.400000000023</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9814,7 +9825,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9831,7 +9842,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9851,7 +9862,7 @@
         <v>725965.4</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9862,7 +9873,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9875,7 +9886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9894,7 +9905,7 @@
         <v>223207.7</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9910,7 +9921,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9926,7 +9937,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9942,7 +9953,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9961,7 +9972,7 @@
         <v>86465.600000000006</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9981,7 +9992,7 @@
         <v>502757.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10001,7 +10012,7 @@
         <v>240224.10000000003</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10020,7 +10031,7 @@
         <v>262533.59999999998</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10031,7 +10042,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10045,7 +10056,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10059,25 +10070,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.706115876529651</v>
+        <v>74.743396403495396</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4577001918189734</v>
+        <v>1.4584276266570915</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10090,7 +10101,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10104,7 +10115,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10115,10 +10126,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10130,7 +10141,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10144,7 +10155,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10158,10 +10169,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10173,7 +10184,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10184,7 +10195,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10195,10 +10206,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10210,7 +10221,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10226,7 +10237,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10237,7 +10248,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10251,7 +10262,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10267,7 +10278,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10277,7 +10288,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10287,7 +10298,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10297,7 +10308,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10307,10 +10318,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10322,7 +10333,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10338,7 +10349,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10354,7 +10365,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10367,7 +10378,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10380,10 +10391,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10395,7 +10406,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10409,7 +10420,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10423,7 +10434,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10437,7 +10448,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10451,7 +10462,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10462,7 +10473,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10470,68 +10481,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103976.80172797565</v>
+        <v>-104028.68917942658</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8038203508087696</v>
+        <v>-4.8062175970318624</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>188850.46068082566</v>
+        <v>188944.70255927561</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7250585823132933</v>
+        <v>8.7294126405846821</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>296930.38413318177</v>
+        <v>297078.56104028958</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.718446791662197</v>
+        <v>13.725292696037547</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>381804.0430860318</v>
+        <v>381994.57442013861</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.63968502316672</v>
+        <v>17.648487739590365</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10557,19 +10568,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10626,7 +10637,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10649,7 +10660,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10669,7 +10680,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10726,7 +10737,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10781,7 +10792,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10836,7 +10847,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10891,7 +10902,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10948,7 +10959,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11005,7 +11016,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11060,7 +11071,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11115,7 +11126,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11170,7 +11181,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11227,7 +11238,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11284,7 +11295,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11339,7 +11350,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11394,7 +11405,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11420,7 +11431,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11445,7 +11456,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11502,7 +11513,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11521,7 +11532,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11544,7 +11555,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11565,7 +11576,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11622,7 +11633,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11679,7 +11690,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11736,7 +11747,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11793,18 +11804,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11861,7 +11872,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11919,7 +11930,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11976,7 +11987,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12031,18 +12042,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12099,18 +12110,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12165,18 +12176,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12234,10 +12245,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12260,14 +12271,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12322,7 +12333,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12377,7 +12388,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12434,7 +12445,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12489,11 +12500,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12503,7 +12514,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12527,7 +12538,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12551,7 +12562,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12606,11 +12617,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12620,7 +12631,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12675,7 +12686,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12730,7 +12741,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12785,7 +12796,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12840,7 +12851,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12896,7 +12907,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12951,11 +12962,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12965,7 +12976,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12990,7 +13001,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13014,7 +13025,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13039,7 +13050,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13066,10 +13077,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13092,7 +13103,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13113,7 +13124,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13170,7 +13181,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13227,7 +13238,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13284,7 +13295,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13341,7 +13352,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13398,7 +13409,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13455,7 +13466,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13512,7 +13523,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13569,7 +13580,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13627,7 +13638,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13684,7 +13695,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13741,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13800,7 +13811,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13826,7 +13837,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13850,7 +13861,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13907,18 +13918,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13974,7 +13985,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14030,7 +14041,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14085,7 +14096,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14106,31 +14117,31 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8580562659846548E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8580562659846548E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5588235294117654E-2</v>
+        <v>5.5375796178343956E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0754475703324808E-2</v>
+        <v>5.0560509554140133E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6726342710997446E-2</v>
+        <v>4.6547770700636946E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14161,11 +14172,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14186,7 +14197,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14243,7 +14254,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14300,10 +14311,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14326,7 +14337,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14336,7 +14347,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14393,7 +14404,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14450,7 +14461,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14507,7 +14518,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14564,7 +14575,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14621,11 +14632,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14648,7 +14659,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14705,7 +14716,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14762,7 +14773,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14789,18 +14800,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14854,7 +14865,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14909,11 +14920,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14972,7 +14983,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15030,7 +15041,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15087,7 +15098,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15146,7 +15157,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15206,7 +15217,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15225,7 +15236,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15248,7 +15259,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15269,7 +15280,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15277,26 +15288,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4234599581606098</v>
+        <v>5.4261664225891977</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1730046212394747</v>
+        <v>6.1760851302786826</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6390618408882984</v>
+        <v>5.6418758969338318</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5196785596942748</v>
+        <v>5.5224330400065291</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0057752389704113</v>
+        <v>5.0082732665628154</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15327,33 +15338,33 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9353707904867126E-2</v>
+        <v>6.9123139141263654E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8938678020965145E-2</v>
+        <v>7.8676243697817616E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.2110765228750623E-2</v>
+        <v>7.1871030534188945E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0584124804274617E-2</v>
+        <v>7.0349465477790182E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.4012471086578149E-2</v>
+        <v>6.3799659446660065E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15384,26 +15395,26 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1841738074455814E-2</v>
+        <v>8.1528967100922875E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7947747808016749E-2</v>
+        <v>7.7649858325947896E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4201458583393762E-2</v>
+        <v>7.3917886130208818E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8714069477842851E-2</v>
+        <v>6.845146793843708E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15434,688 +15445,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16137,16 +16148,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16161,7 +16172,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16176,7 +16187,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16208,7 +16219,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16236,7 +16247,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16269,7 +16280,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16299,7 +16310,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16316,7 +16327,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.63968502316672</v>
+        <v>17.648487739590369</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16334,14 +16345,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1310185977458953</v>
+        <v>1.1315830089569092</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16360,13 +16371,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2662497.9557665423</v>
+        <v>2663826.6197677632</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16382,13 +16393,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16398,7 +16409,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16413,7 +16424,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16431,7 +16442,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16456,7 +16467,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16472,7 +16483,7 @@
         <v>2.2781556385229107E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>549</v>
       </c>
@@ -16491,7 +16502,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16511,17 +16522,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.71790319245125</v>
+        <v>120.77814494096691</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16560,7 +16571,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16609,7 +16620,7 @@
         <v>98978.752509011683</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16658,7 +16669,7 @@
         <v>94390.342694858176</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16715,7 +16726,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16772,7 +16783,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16829,7 +16840,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16878,7 +16889,7 @@
         <v>78067.435109780447</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16927,7 +16938,7 @@
         <v>74448.422176768421</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16976,7 +16987,7 @@
         <v>70997.17771970146</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17025,7 +17036,7 @@
         <v>67705.924407566403</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17074,7 +17085,7 @@
         <v>64567.245447152869</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17123,7 +17134,7 @@
         <v>61574.06786941363</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17172,7 +17183,7 @@
         <v>58719.646590628065</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17229,7 +17240,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17286,7 +17297,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17343,7 +17354,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17392,7 +17403,7 @@
         <v>48565.267049642898</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17441,7 +17452,7 @@
         <v>46313.90155645505</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17490,7 +17501,7 @@
         <v>44166.903791313183</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17539,7 +17550,7 @@
         <v>42119.435524844732</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17588,7 +17599,7 @@
         <v>40166.882816007455</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17637,7 +17648,7 @@
         <v>38304.845614637961</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17686,7 +17697,7 @@
         <v>36529.127846000323</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17735,7 +17746,7 @@
         <v>34835.72795499042</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17784,7 +17795,7 @@
         <v>33220.829888687673</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17833,7 +17844,7 @@
         <v>31680.79449693326</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17882,7 +17893,7 @@
         <v>30212.151331556186</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17939,7 +17950,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17996,7 +18007,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -18053,7 +18064,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -18110,7 +18121,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18156,7 +18167,7 @@
         <v>351549.24104346032</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18169,10 +18180,10 @@
         <v>1972635.5401994288</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18187,7 +18198,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>1972635.5401994288</v>
@@ -18219,7 +18230,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18246,7 +18257,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18272,7 +18283,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18298,7 +18309,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18324,7 +18335,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18350,7 +18361,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18376,7 +18387,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18402,7 +18413,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18428,7 +18439,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18454,7 +18465,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18480,7 +18491,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18515,7 +18526,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18550,7 +18561,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18585,7 +18596,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18620,7 +18631,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18641,7 +18652,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18665,7 +18676,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18693,29 +18704,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18724,29 +18735,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.841019376231131</v>
+        <v>93.887848777175094</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.603032719761799</v>
+        <v>94.650242387550961</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.365046063292425</v>
+        <v>95.412635997926785</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.127059406823065</v>
+        <v>96.175029608302637</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.889072750353719</v>
+        <v>96.937423218678504</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18755,29 +18766,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.746719345987259</v>
+        <v>93.793501688470485</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.225396660745488</v>
+        <v>95.272916906261955</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.718284014543897</v>
+        <v>96.766549254316828</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.225381407382557</v>
+        <v>98.274398732635149</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.746688839261381</v>
+        <v>99.796465341216873</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18786,29 +18797,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.658793909862439</v>
+        <v>93.705532374992998</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.811492306800091</v>
+        <v>95.85930503110869</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.005279548601294</v>
+        <v>98.054187036617861</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.24055311887555</v>
+        <v>100.29057607348592</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.51771050123244</v>
+        <v>102.56886982367833</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18817,29 +18828,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.576812151237874</v>
+        <v>93.623509705083904</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.363433194926074</v>
+        <v>96.411521353808169</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.229275301271215</v>
+        <v>99.278793598806232</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.17586954110196</v>
+        <v>102.2268582749557</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.20476180981042</v>
+        <v>105.25726204909547</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18848,29 +18859,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.500372283056493</v>
+        <v>93.547031691182681</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.883209695632132</v>
+        <v>96.931557238121897</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.39335517793631</v>
+        <v>100.44345438522315</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.03449510277392</v>
+        <v>104.08641134489866</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.8103873211588</v>
+        <v>107.86418784343941</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18879,29 +18890,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.429099678691543</v>
+        <v>93.475723519712972</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.37269619046954</v>
+        <v>97.421288000972112</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.50045212357587</v>
+        <v>101.5511038044728</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.81946883566167</v>
+        <v>105.87227583165043</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.33705448367843</v>
+        <v>110.39211588643958</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18910,30 +18921,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.362645035927031</v>
+        <v>93.409235714146831</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.833657831295483</v>
+        <v>97.882479675078187</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.55335551243587</v>
+        <v>102.60453262278018</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.53370934370308</v>
+        <v>107.58737179561717</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.78715597460652</v>
+        <v>112.84344004934881</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18942,29 +18953,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.300682665051028</v>
+        <v>93.347242422243667</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.267756905639686</v>
+        <v>98.316795377499716</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.55471817596708</v>
+        <v>103.60639499543616</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.18001957520205</v>
+        <v>109.23450358385564</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.16301196580956</v>
+        <v>115.22048166186688</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18973,30 +18984,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.242908892672475</v>
+        <v>93.289439819070566</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.676558831129327</v>
+        <v>98.725801307052848</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.50706308673796</v>
+        <v>104.559215154046</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.76109140591896</v>
+        <v>110.81636441545056</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.46687232091553</v>
+        <v>117.52549171036924</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19005,30 +19016,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.189040573438376</v>
+        <v>93.235544617976728</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.061537800588127</v>
+        <v>99.110972392226472</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.41278971516344</v>
+        <v>105.4653937664302</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.27951004054692</v>
+        <v>112.33554078518749</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.70091872586677</v>
+        <v>119.76065296952306</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19037,30 +19048,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.969640457760505</v>
+        <v>93.016035015253081</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.67494376998056</v>
+        <v>100.72518349817355</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.31822233292274</v>
+        <v>109.37277530877634</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.01533923738528</v>
+        <v>119.07473135691548</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.89578319198156</v>
+        <v>129.96060496984012</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19069,30 +19080,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.815025912333937</v>
+        <v>92.861343312666591</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.86993309052816</v>
+        <v>101.92076915318542</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.35689209118681</v>
+        <v>112.4129614517237</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.51822738390882</v>
+        <v>124.58036560484624</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.6367938285035</v>
+        <v>138.70597762517298</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19101,30 +19112,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.706066727952518</v>
+        <v>92.752329754479703</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.7550168842621</v>
+        <v>102.80629462950253</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.72116637358013</v>
+        <v>114.77841557582215</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.01385473255993</v>
+        <v>129.07823640243902</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.13127962591071</v>
+        <v>146.20420338920255</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19133,30 +19144,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.629281559853879</v>
+        <v>92.67550626834651</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.41056527156609</v>
+        <v>103.46217015453873</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.5607189828048</v>
+        <v>116.61888617535925</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.6865925240246</v>
+        <v>132.75280699699707</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>152.55700311523583</v>
+        <v>152.6331335016402</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19165,7 +19176,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19188,7 +19199,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19203,7 +19214,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>152.55700311523583</v>
+        <v>152.6331335016402</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19216,7 +19227,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19231,7 +19242,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.6865925240246</v>
+        <v>132.75280699699707</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19244,7 +19255,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19259,7 +19270,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.5607189828048</v>
+        <v>116.61888617535925</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19272,7 +19283,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19287,7 +19298,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.41056527156609</v>
+        <v>103.46217015453873</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19300,7 +19311,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19315,7 +19326,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.629281559853879</v>
+        <v>92.67550626834651</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19328,7 +19339,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19341,16 +19352,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19362,7 +19373,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19374,7 +19385,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19386,7 +19397,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19398,7 +19409,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19438,14 +19449,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19455,7 +19466,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19464,7 +19475,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19485,14 +19496,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19505,7 +19516,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19518,7 +19529,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19531,7 +19542,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19544,14 +19555,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19561,7 +19572,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19574,7 +19585,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19587,7 +19598,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19600,7 +19611,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19610,7 +19621,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19618,7 +19629,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19630,18 +19641,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19662,7 +19673,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19675,7 +19686,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.6865925240246</v>
+        <v>132.75280699699707</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19686,7 +19697,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19699,7 +19710,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.5607189828048</v>
+        <v>116.61888617535925</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19709,7 +19720,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19722,7 +19733,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.41056527156609</v>
+        <v>103.46217015453873</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19732,13 +19743,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.49835526323909</v>
+        <v>116.55649133448168</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19746,12 +19757,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19772,7 +19783,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19785,7 +19796,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>152.55700311523583</v>
+        <v>152.6331335016402</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19795,7 +19806,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19808,7 +19819,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.629281559853879</v>
+        <v>92.67550626834651</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19818,16 +19829,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19847,13 +19858,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.2</v>
+        <v>78.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,16 +19875,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20696811599645942</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.20553937277082149</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,16 +19895,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1209243622619884E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
+        <v>3.1190557034553371E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.71369875586933</v>
+        <v>120.7739384062487</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19906,7 +19917,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19916,7 +19927,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19925,7 +19936,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -19937,7 +19948,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19947,7 +19958,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19957,7 +19968,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19965,7 +19976,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19978,7 +19989,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19990,13 +20001,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.71790319245125</v>
+        <v>120.77814494096691</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20006,7 +20017,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20018,7 +20029,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20028,7 +20039,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20040,7 +20051,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20050,7 +20061,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20063,10 +20074,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009316</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="13.9">
+        <v>0.1461282787700931</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20076,12 +20087,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20091,7 +20102,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20104,13 +20115,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20131,7 +20142,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20141,11 +20152,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.628432606391407</v>
+        <v>55.656192813939505</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.010982676551862</v>
+        <v>64.03874288409996</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,10 +20164,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46972892607650696</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="13.15">
+        <v>0.46976356216278969</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20166,11 +20177,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.726324191115893</v>
+        <v>69.761119657038989</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.364766273555546</v>
+        <v>79.399561739478642</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,10 +20189,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34253720090159456</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="13.15">
+        <v>0.34257702624218966</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20202,7 +20213,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20212,11 +20223,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.522798162527394</v>
+        <v>86.56597555800839</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.574933082452347</v>
+        <v>97.618110477933342</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,10 +20235,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19168301453683967</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" ht="13.15">
+        <v>0.19172868115326203</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20237,11 +20248,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.850861730625539</v>
+        <v>97.899692159654933</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.81815264630512</v>
+        <v>109.86698307533452</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20260,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0259400729649553E-2</v>
+        <v>9.0308848703983924E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20268,7 +20279,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20277,7 +20288,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20291,7 +20302,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20300,7 +20311,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20317,7 +20328,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20333,7 +20344,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20343,7 +20354,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20354,16 +20365,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20372,43 +20383,43 @@
         <v>21644606612</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1692608.2370584002</v>
+        <v>1699101.619042</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20696811599645942</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.20553937277082149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20424,7 +20435,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20437,10 +20448,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1310185977458953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>1.1315830089569092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20456,14 +20467,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.71369875586933</v>
+        <v>120.7739384062487</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20473,7 +20484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20489,11 +20500,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20509,13 +20520,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.010982676551862</v>
+        <v>64.03874288409996</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20525,13 +20536,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.364766273555546</v>
+        <v>79.399561739478642</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20541,13 +20552,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.574933082452347</v>
+        <v>97.618110477933342</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20557,13 +20568,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.81815264630512</v>
+        <v>109.86698307533452</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20573,7 +20584,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20583,25 +20594,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20610,7 +20621,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20619,7 +20630,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20632,11 +20643,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20645,7 +20656,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20658,7 +20669,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20671,7 +20682,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20680,7 +20691,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20693,7 +20704,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20702,7 +20713,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20717,7 +20728,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20732,7 +20743,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20745,12 +20756,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20763,7 +20774,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20772,7 +20783,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20785,16 +20796,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20807,25 +20818,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20838,7 +20849,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20851,23 +20862,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9353707904867126E-2</v>
+        <v>6.9123139141263654E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.8580562659846548E-2</v>
+        <v>5.8356687898089177E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20877,7 +20888,7 @@
         <v>1.0614782273563756</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20888,7 +20899,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20901,7 +20912,7 @@
         <v>0.11027130711998644</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20915,7 +20926,7 @@
         <v>0.15195683827249326</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20929,7 +20940,7 @@
         <v>0.48913824057450628</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20943,7 +20954,7 @@
         <v>1.4835789300471205</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20953,43 +20964,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21002,20 +21013,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8038203508087696</v>
+        <v>-4.8062175970318615</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21024,7 +21035,7 @@
         <v>6.4100114768294941E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21033,12 +21044,12 @@
         <v>0.67756727799881356</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21051,7 +21062,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21064,25 +21075,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7250585823132933</v>
+        <v>8.7294126405846821</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21095,33 +21106,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.718446791662197</v>
+        <v>13.725292696037547</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.63968502316672</v>
+        <v>17.648487739590369</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21131,49 +21142,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21183,7 +21194,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21193,7 +21204,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21203,7 +21214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21212,97 +21223,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4577001918189734</v>
+        <v>1.4584276266570915</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.00976421028716</v>
+        <v>123.07114966418051</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21320,7 +21331,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21336,14 +21347,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.56 HKD</v>
+        <v>152.63 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21359,14 +21370,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.69 HKD</v>
+        <v>132.75 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21381,14 +21392,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.56 HKD</v>
+        <v>116.62 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21403,14 +21414,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.41 HKD</v>
+        <v>103.46 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21425,14 +21436,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.63 HKD</v>
+        <v>92.68 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21441,29 +21452,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.71369875586933</v>
+        <v>120.7739384062487</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21473,30 +21484,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21505,7 +21516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21518,14 +21529,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21544,7 +21555,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21554,18 +21565,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.628432606391407</v>
+        <v>55.656192813939505</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.010982676551862</v>
+        <v>64.03874288409996</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21575,18 +21586,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.726324191115893</v>
+        <v>69.761119657038989</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.364766273555546</v>
+        <v>79.399561739478642</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21605,7 +21616,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21615,18 +21626,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.522798162527394</v>
+        <v>86.56597555800839</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.574933082452347</v>
+        <v>97.618110477933342</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21636,18 +21647,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.850861730625539</v>
+        <v>97.899692159654933</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.81815264630512</v>
+        <v>109.86698307533452</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21657,50 +21668,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21709,60 +21720,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21785,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B987E31-B3AB-8E4B-BA9A-5B50636D9C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAFE84A-6805-457C-BEBF-42AB8D0B3E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3286,27 +3275,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4058,7 +4047,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4100,17 +4089,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4119,7 +4108,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,10 +4182,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4207,7 +4196,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4245,7 +4234,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4266,19 +4255,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4286,8 +4275,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4310,29 +4299,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4349,15 +4338,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4368,11 +4357,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4433,14 +4422,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4453,7 +4442,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4490,7 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4507,7 +4496,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4553,7 +4542,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4568,13 +4557,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4590,53 +4579,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4653,7 +4642,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4666,21 +4655,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4690,14 +4679,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4706,8 +4695,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4719,7 +4708,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4727,7 +4716,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,7 +4755,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4780,39 +4769,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4823,7 +4812,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4834,10 +4823,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4846,7 +4835,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4859,7 +4848,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4868,8 +4857,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4877,10 +4866,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4889,10 +4878,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,16 +4898,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4939,7 +4928,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4957,7 +4946,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4967,10 +4956,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4985,7 +4974,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4999,34 +4988,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5036,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5045,21 +5043,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5341,7 +5330,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5350,7 +5339,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5363,7 +5352,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5385,7 +5374,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5399,7 +5388,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5409,7 +5398,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5419,16 +5408,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.5</v>
+        <v>79.3</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5437,43 +5426,43 @@
         <v>21644606612</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1699101.619042</v>
+        <v>1716417.3043316</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20553937277082149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.20417207216016059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5488,7 +5477,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5499,10 +5488,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1315830089569092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.1404913400000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5516,14 +5505,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.7739384062487</v>
+        <v>121.72472523866365</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5532,7 +5521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5548,11 +5537,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5567,13 +5556,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.03874288409996</v>
+        <v>64.47689349811607</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5582,13 +5571,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.399561739478642</v>
+        <v>79.948752689610018</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5597,13 +5586,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.618110477933342</v>
+        <v>98.299596821608375</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5612,13 +5601,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.86698307533452</v>
+        <v>110.63769354011853</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,11 +5616,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5641,25 +5630,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5668,16 +5657,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5690,20 +5679,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5716,7 +5705,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5729,16 +5718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5751,16 +5740,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5775,7 +5764,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5790,7 +5779,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5803,12 +5792,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5821,16 +5810,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5843,8 +5832,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5852,7 +5841,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5865,25 +5854,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5896,7 +5885,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5909,23 +5898,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9123139141263654E-2</v>
+        <v>6.896448484596672E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5935,7 +5924,7 @@
         <v>1.0614782273563756</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5946,7 +5935,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5959,7 +5948,7 @@
         <v>0.11027130711998644</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5973,7 +5962,7 @@
         <v>0.15195683827249326</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5987,7 +5976,7 @@
         <v>0.48913824057450628</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -6001,7 +5990,7 @@
         <v>1.4835789300471205</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6011,45 +6000,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6063,21 +6052,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8062175970318615</v>
+        <v>-4.8440543063855621</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6087,7 +6076,7 @@
         <v>6.4100114768294941E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6097,16 +6086,16 @@
         <v>0.67756727799881356</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6120,7 +6109,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6134,30 +6123,30 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7294126405846821</v>
+        <v>8.7981345080911186</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6171,38 +6160,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.725292696037547</v>
+        <v>13.833344381182879</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.648487739590369</v>
+        <v>17.787424582888434</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6212,42 +6201,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6256,7 +6245,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6265,7 +6254,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6274,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6283,76 +6272,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4584276266570915</v>
+        <v>1.469909025721776</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6369,7 +6358,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (30yrs)</v>
@@ -6380,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.63 HKD</v>
+        <v>153.83 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6388,10 +6377,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2614757061473781E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-4.2867832949712033E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (30yrs)</v>
@@ -6402,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.75 HKD</v>
+        <v>133.8 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6410,10 +6399,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5665509464310585E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+        <v>4.2887044365356531E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (30yrs)</v>
@@ -6424,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.62 HKD</v>
+        <v>117.54 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6432,10 +6421,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0577315496882672E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+        <v>5.0273857600807444E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (30yrs)</v>
@@ -6446,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.46 HKD</v>
+        <v>104.28 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6454,10 +6443,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5070011630285764E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+        <v>9.474038259609327E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (30yrs)</v>
@@ -6468,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.68 HKD</v>
+        <v>93.41 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6476,32 +6465,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13776593222835196</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="463" t="s">
+        <v>0.13740985688570595</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.7739384062487</v>
+        <v>121.72472523866365</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6510,7 +6499,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6520,30 +6509,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6552,7 +6541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6565,14 +6554,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6591,7 +6580,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6601,18 +6590,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.656192813939505</v>
+        <v>56.094343427955614</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.03874288409996</v>
+        <v>64.47689349811607</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6622,25 +6611,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.761119657038989</v>
+        <v>70.310310607170365</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.399561739478642</v>
+        <v>79.948752689610018</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6659,7 +6648,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6669,18 +6658,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.56597555800839</v>
+        <v>87.247461901683423</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.618110477933342</v>
+        <v>98.299596821608375</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6690,18 +6679,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.899692159654933</v>
+        <v>98.67040262443895</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.86698307533452</v>
+        <v>110.63769354011853</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6711,21 +6700,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6734,80 +6723,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6863,15 +6852,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6920,7 +6909,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6936,7 +6925,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6944,7 +6933,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6968,7 +6957,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6996,7 +6985,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7024,7 +7013,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7052,7 +7041,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7068,7 +7057,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7092,7 +7081,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7108,7 +7097,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7124,7 +7113,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7148,7 +7137,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7172,7 +7161,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7196,7 +7185,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7220,7 +7209,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7244,13 +7233,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7274,7 +7263,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7290,7 +7279,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7306,7 +7295,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7330,7 +7319,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7354,7 +7343,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7378,7 +7367,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7407,7 +7396,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7404,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7443,7 +7432,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7468,7 +7457,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7493,7 +7482,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7518,7 +7507,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7543,7 +7532,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7559,12 +7548,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7613,7 +7602,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7662,7 +7651,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7711,7 +7700,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7760,7 +7749,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7809,7 +7798,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7858,7 +7847,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7907,7 +7896,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7956,7 +7945,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -8005,7 +7994,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8054,7 +8043,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8103,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8152,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8201,12 +8190,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8255,7 +8244,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8304,12 +8293,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8358,7 +8347,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8407,7 +8396,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8456,7 +8445,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8505,13 +8494,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8560,7 +8549,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8609,7 +8598,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8658,7 +8647,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8707,7 +8696,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8756,12 +8745,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8811,7 +8800,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8910,7 +8899,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8959,7 +8948,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9009,7 +8998,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9025,13 +9014,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9080,7 +9069,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9114,7 +9103,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9148,7 +9137,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9197,7 +9186,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9278,7 +9267,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9289,7 +9278,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9305,7 +9294,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9316,7 +9305,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9336,7 +9325,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9359,7 +9348,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9380,7 +9369,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9401,7 +9390,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9423,7 +9412,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9444,7 +9433,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9466,7 +9455,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9486,7 +9475,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9499,7 +9488,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9523,12 +9512,12 @@
         <v>266242.2</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9548,7 +9537,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9568,7 +9557,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9588,7 +9577,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9609,7 +9598,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9650,7 +9639,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9670,7 +9659,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9690,7 +9679,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9702,7 +9691,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9715,7 +9704,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9739,7 +9728,7 @@
         <v>236515.5</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9756,7 +9745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9775,7 +9764,7 @@
         <v>32419.400000000023</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9790,7 +9779,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9809,7 +9798,7 @@
         <v>27896.400000000023</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9825,7 +9814,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9842,7 +9831,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9862,7 +9851,7 @@
         <v>725965.4</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9873,7 +9862,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9886,7 +9875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9905,7 +9894,7 @@
         <v>223207.7</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9921,7 +9910,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9937,7 +9926,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9953,7 +9942,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9972,7 +9961,7 @@
         <v>86465.600000000006</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9992,7 +9981,7 @@
         <v>502757.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10012,7 +10001,7 @@
         <v>240224.10000000003</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10031,7 +10020,7 @@
         <v>262533.59999999998</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10042,7 +10031,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10056,7 +10045,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10070,25 +10059,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.743396403495396</v>
+        <v>75.331810079891142</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4584276266570915</v>
+        <v>1.469909025721776</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10101,7 +10090,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10115,7 +10104,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10126,10 +10115,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10141,7 +10130,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10155,7 +10144,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10169,10 +10158,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10184,7 +10173,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10195,7 +10184,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10206,10 +10195,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10221,7 +10210,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10237,7 +10226,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10248,7 +10237,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10262,7 +10251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10278,7 +10267,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10288,7 +10277,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10298,7 +10287,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10308,7 +10297,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10318,10 +10307,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10333,7 +10322,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10349,7 +10338,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10365,7 +10354,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10378,7 +10367,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10391,10 +10380,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10406,7 +10395,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10420,7 +10409,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10434,7 +10423,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10448,7 +10437,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10462,7 +10451,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10473,7 +10462,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10481,68 +10470,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104028.68917942658</v>
+        <v>-104847.64986888001</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8062175970318624</v>
+        <v>-4.8440543063855621</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>188944.70255927561</v>
+        <v>190432.16034709438</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7294126405846821</v>
+        <v>8.7981345080911186</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>297078.56104028958</v>
+        <v>299417.297259024</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.725292696037547</v>
+        <v>13.833344381182879</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>381994.57442013861</v>
+        <v>385001.80773723836</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.648487739590365</v>
+        <v>17.787424582888434</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10568,19 +10557,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10637,7 +10626,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10660,7 +10649,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10680,7 +10669,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10737,7 +10726,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10792,7 +10781,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10847,7 +10836,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10902,7 +10891,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10959,7 +10948,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11016,7 +11005,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11071,7 +11060,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11126,7 +11115,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11181,7 +11170,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11238,7 +11227,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11295,7 +11284,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11350,7 +11339,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11405,7 +11394,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11431,7 +11420,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11456,7 +11445,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11513,7 +11502,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11532,7 +11521,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11555,7 +11544,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11576,7 +11565,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11633,7 +11622,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11690,7 +11679,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11747,7 +11736,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11804,18 +11793,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11872,7 +11861,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11930,7 +11919,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11987,7 +11976,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12042,18 +12031,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12110,18 +12099,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12176,18 +12165,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12245,10 +12234,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12271,14 +12260,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12333,7 +12322,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12388,7 +12377,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12445,7 +12434,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12500,11 +12489,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12514,7 +12503,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12538,7 +12527,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12562,7 +12551,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12617,11 +12606,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12631,7 +12620,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12686,7 +12675,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12741,7 +12730,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12796,7 +12785,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12851,7 +12840,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12907,7 +12896,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12962,11 +12951,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12976,7 +12965,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -13001,7 +12990,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13025,7 +13014,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13050,7 +13039,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13077,10 +13066,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13103,7 +13092,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13124,7 +13113,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13181,7 +13170,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13238,7 +13227,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13295,7 +13284,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13352,7 +13341,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13409,7 +13398,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13466,7 +13455,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13523,7 +13512,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13580,7 +13569,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13638,7 +13627,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13695,7 +13684,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13752,7 +13741,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13811,7 +13800,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13837,7 +13826,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13861,7 +13850,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13918,18 +13907,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13985,7 +13974,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14041,7 +14030,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14096,7 +14085,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14117,31 +14106,31 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5375796178343956E-2</v>
+        <v>5.4817150063051712E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0560509554140133E-2</v>
+        <v>5.0050441361916775E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6547770700636946E-2</v>
+        <v>4.6078184110971004E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14172,11 +14161,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14197,7 +14186,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14254,7 +14243,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14311,10 +14300,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14337,7 +14326,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14347,7 +14336,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14404,7 +14393,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14461,7 +14450,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14518,7 +14507,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14575,7 +14564,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14632,11 +14621,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14659,7 +14648,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14716,7 +14705,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14773,7 +14762,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14800,18 +14789,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14865,7 +14854,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14920,11 +14909,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14983,7 +14972,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15041,7 +15030,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15098,7 +15087,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15157,7 +15146,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15217,7 +15206,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15236,7 +15225,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15259,7 +15248,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15280,7 +15269,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15288,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4261664225891977</v>
+        <v>5.4688836482851597</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1760851302786826</v>
+        <v>6.224706053759629</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6418758969338318</v>
+        <v>5.6862912847543425</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5224330400065291</v>
+        <v>5.5659081198674665</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0082732665628154</v>
+        <v>5.0477006491407224</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15338,33 +15327,33 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9123139141263654E-2</v>
+        <v>6.896448484596672E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8676243697817616E-2</v>
+        <v>7.8495662720802384E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1871030534188945E-2</v>
+        <v>7.1706069164619704E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0349465477790182E-2</v>
+        <v>7.0187996467433372E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.3799659446660065E-2</v>
+        <v>6.365322382270773E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15395,26 +15384,26 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1528967100922875E-2</v>
+        <v>8.0706480673675224E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7649858325947896E-2</v>
+        <v>7.6866505404626861E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3917886130208818E-2</v>
+        <v>7.3172182360925514E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.845146793843708E-2</v>
+        <v>6.7760910884833686E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15445,688 +15434,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16148,16 +16137,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16172,7 +16161,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16187,7 +16176,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16219,7 +16208,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16247,7 +16236,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16280,7 +16269,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16310,7 +16299,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16327,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.648487739590369</v>
+        <v>17.787424582888434</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16345,14 +16334,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1315830089569092</v>
+        <v>1.1404913400000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16371,13 +16360,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2663826.6197677632</v>
+        <v>2684797.462545054</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16393,13 +16382,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16409,7 +16398,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16424,7 +16413,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16442,7 +16431,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16467,7 +16456,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16483,7 +16472,7 @@
         <v>2.2781556385229107E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>549</v>
       </c>
@@ -16502,7 +16491,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16522,17 +16511,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.77814494096691</v>
+        <v>121.72896488911751</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16571,7 +16560,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16620,7 +16609,7 @@
         <v>98978.752509011683</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16669,7 +16658,7 @@
         <v>94390.342694858176</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16726,7 +16715,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16783,7 +16772,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16840,7 +16829,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16889,7 +16878,7 @@
         <v>78067.435109780447</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16938,7 +16927,7 @@
         <v>74448.422176768421</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16987,7 +16976,7 @@
         <v>70997.17771970146</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17036,7 +17025,7 @@
         <v>67705.924407566403</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17085,7 +17074,7 @@
         <v>64567.245447152869</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17134,7 +17123,7 @@
         <v>61574.06786941363</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17183,7 +17172,7 @@
         <v>58719.646590628065</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17240,7 +17229,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17297,7 +17286,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17354,7 +17343,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17403,7 +17392,7 @@
         <v>48565.267049642898</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17452,7 +17441,7 @@
         <v>46313.90155645505</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17501,7 +17490,7 @@
         <v>44166.903791313183</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17550,7 +17539,7 @@
         <v>42119.435524844732</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17599,7 +17588,7 @@
         <v>40166.882816007455</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17648,7 +17637,7 @@
         <v>38304.845614637961</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17697,7 +17686,7 @@
         <v>36529.127846000323</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17746,7 +17735,7 @@
         <v>34835.72795499042</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17795,7 +17784,7 @@
         <v>33220.829888687673</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17844,7 +17833,7 @@
         <v>31680.79449693326</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17893,7 +17882,7 @@
         <v>30212.151331556186</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17950,7 +17939,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -18007,7 +17996,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -18064,7 +18053,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -18121,7 +18110,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18167,7 +18156,7 @@
         <v>351549.24104346032</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18180,10 +18169,10 @@
         <v>1972635.5401994288</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18198,7 +18187,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>1972635.5401994288</v>
@@ -18230,7 +18219,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18257,7 +18246,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18283,7 +18272,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18309,7 +18298,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18335,7 +18324,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18361,7 +18350,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18387,7 +18376,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18413,7 +18402,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18439,7 +18428,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18465,7 +18454,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18491,7 +18480,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18526,7 +18515,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18561,7 +18550,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18596,7 +18585,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18631,7 +18620,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18652,7 +18641,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18676,7 +18665,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18704,29 +18693,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18735,29 +18724,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.887848777175094</v>
+        <v>94.626976204160499</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.650242387550961</v>
+        <v>95.395371720373248</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.412635997926785</v>
+        <v>96.16376723658594</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.175029608302637</v>
+        <v>96.932162752798675</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.937423218678504</v>
+        <v>97.700558269011395</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18766,29 +18755,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.793501688470485</v>
+        <v>94.531886372685392</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.272916906261955</v>
+        <v>96.022948213310485</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.766549254316828</v>
+        <v>97.528339107850968</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.274398732635149</v>
+        <v>99.048059056306883</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.796465341216873</v>
+        <v>100.58210805867813</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18797,29 +18786,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.705532374992998</v>
+        <v>94.443224525156154</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.85930503110869</v>
+        <v>96.613952649549788</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.054187036617861</v>
+        <v>98.826113754648503</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.29057607348592</v>
+        <v>101.08010865314922</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.56886982367833</v>
+        <v>103.3763381577489</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18828,29 +18817,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.623509705083904</v>
+        <v>94.360556135851482</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.411521353808169</v>
+        <v>97.170516267826414</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.278793598806232</v>
+        <v>100.06036097118319</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.2268582749557</v>
+        <v>103.03163414009342</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.25726204909547</v>
+        <v>106.08589461745389</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18859,29 +18848,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.547031691182681</v>
+        <v>94.283476052583751</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.931557238121897</v>
+        <v>97.694646108814169</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.44345438522315</v>
+        <v>101.23419049180359</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.08641134489866</v>
+        <v>104.90582644923327</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.86418784343941</v>
+        <v>108.71334330565269</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18890,29 +18879,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.475723519712972</v>
+        <v>94.211606511075345</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.421288000972112</v>
+        <v>98.188232252774682</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.5511038044728</v>
+        <v>102.35055982609991</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.87227583165043</v>
+        <v>106.70575006547014</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.39211588643958</v>
+        <v>111.26117233663334</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18921,30 +18910,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.409235714146831</v>
+        <v>94.144595283561699</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.882479675078187</v>
+        <v>98.65305463543217</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.60453262278018</v>
+        <v>103.41228171046568</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.58737179561717</v>
+        <v>108.43434803724078</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.84344004934881</v>
+        <v>113.7317944272812</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18953,29 +18942,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.347242422243667</v>
+        <v>94.082113952546635</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.316795377499716</v>
+        <v>99.090789466652694</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.60639499543616</v>
+        <v>104.42203119489746</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.23450358385564</v>
+        <v>110.09444678868485</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.22048166186688</v>
+        <v>116.12754918184886</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18984,30 +18973,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.289439819070566</v>
+        <v>94.023856301250547</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.725801307052848</v>
+        <v>99.503015275074816</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.559215154046</v>
+        <v>105.38235238288847</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.81636441545056</v>
+        <v>111.68876074112059</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.52549171036924</v>
+        <v>118.45070530749021</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19016,30 +19005,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.235544617976728</v>
+        <v>93.969536812862572</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.110972392226472</v>
+        <v>99.891218600488699</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.4653937664302</v>
+        <v>106.29566484139742</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.33554078518749</v>
+        <v>113.21989675138528</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.76065296952306</v>
+        <v>120.70346276265761</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19048,30 +19037,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.016035015253081</v>
+        <v>93.74829913169242</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.72518349817355</v>
+        <v>101.5181375032049</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.37277530877634</v>
+        <v>110.23380705089336</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.07473135691548</v>
+        <v>120.01214126621795</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.96060496984012</v>
+        <v>130.98371337856295</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19080,30 +19069,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.861343312666591</v>
+        <v>93.592389626359378</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.92076915318542</v>
+        <v>102.72313534691253</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.4129614517237</v>
+        <v>113.29792690827405</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.58036560484624</v>
+        <v>125.56111834635327</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.70597762517298</v>
+        <v>139.79793354582574</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19112,30 +19101,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.752329754479703</v>
+        <v>93.482517864349333</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.80629462950253</v>
+        <v>103.61563207856635</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.77841557582215</v>
+        <v>115.68200295249494</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.07823640243902</v>
+        <v>130.09439840843382</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.20420338920255</v>
+        <v>147.35518871981736</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19144,30 +19133,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.67550626834651</v>
+        <v>93.405089589136637</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.46217015453873</v>
+        <v>104.27667095110232</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.61888617535925</v>
+        <v>117.5369625654283</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.75280699699707</v>
+        <v>133.79789687751668</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>152.6331335016402</v>
+        <v>153.83473026530163</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19176,7 +19165,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19199,7 +19188,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19214,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>152.6331335016402</v>
+        <v>153.83473026530163</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19227,7 +19216,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19242,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.75280699699707</v>
+        <v>133.79789687751668</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19255,7 +19244,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19270,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.61888617535925</v>
+        <v>117.5369625654283</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19283,7 +19272,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19298,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.46217015453873</v>
+        <v>104.27667095110232</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19311,7 +19300,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19326,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.67550626834651</v>
+        <v>93.405089589136637</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19339,7 +19328,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19352,16 +19341,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19373,7 +19362,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19385,7 +19374,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19397,7 +19386,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19409,7 +19398,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19449,14 +19438,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19466,7 +19455,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19475,7 +19464,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19496,14 +19485,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19516,7 +19505,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19529,7 +19518,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19542,7 +19531,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19555,14 +19544,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19572,7 +19561,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19585,7 +19574,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19598,7 +19587,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19611,7 +19600,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19621,7 +19610,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19629,7 +19618,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19641,18 +19630,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19673,7 +19662,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19686,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.75280699699707</v>
+        <v>133.79789687751668</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19697,7 +19686,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19710,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.61888617535925</v>
+        <v>117.5369625654283</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19720,7 +19709,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19733,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.46217015453873</v>
+        <v>104.27667095110232</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19743,13 +19732,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.55649133448168</v>
+        <v>117.47407652426449</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19757,12 +19746,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19783,7 +19772,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19796,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>152.6331335016402</v>
+        <v>153.83473026530163</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19806,7 +19795,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19819,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.67550626834651</v>
+        <v>93.405089589136637</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19829,16 +19818,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19858,13 +19847,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.5</v>
+        <v>79.3</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19875,16 +19864,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20553937277082149</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.20417207216016059</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19895,16 +19884,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1190557034553371E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+        <v>3.0898068382988458E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.7739384062487</v>
+        <v>121.72472523866365</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19906,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19927,7 +19916,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19936,7 +19925,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -19948,7 +19937,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19958,7 +19947,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19968,7 +19957,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19976,7 +19965,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19989,7 +19978,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -20001,13 +19990,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.77814494096691</v>
+        <v>121.72896488911751</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20017,7 +20006,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20029,7 +20018,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20039,7 +20028,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20051,7 +20040,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20061,7 +20050,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20074,10 +20063,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.1461282787700931</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+        <v>0.14612827877009313</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20087,12 +20076,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20102,7 +20091,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20115,13 +20104,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20142,7 +20131,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20152,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.656192813939505</v>
+        <v>56.094343427955614</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.03874288409996</v>
+        <v>64.47689349811607</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20164,10 +20153,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46976356216278969</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.47030569695928837</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20177,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.761119657038989</v>
+        <v>70.310310607170365</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.399561739478642</v>
+        <v>79.948752689610018</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20189,10 +20178,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34257702624218966</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+        <v>0.34320038486136795</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20213,7 +20202,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20223,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.56597555800839</v>
+        <v>87.247461901683423</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.618110477933342</v>
+        <v>98.299596821608375</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20235,10 +20224,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19172868115326203</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.19244346923869426</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20248,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.899692159654933</v>
+        <v>98.67040262443895</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.86698307533452</v>
+        <v>110.63769354011853</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20260,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0308848703983924E-2</v>
+        <v>9.1082823779696009E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20279,7 +20268,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20288,7 +20277,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20302,7 +20291,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20311,7 +20300,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20328,7 +20317,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20344,7 +20333,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20354,7 +20343,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20365,16 +20354,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20383,43 +20372,43 @@
         <v>21644606612</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1699101.619042</v>
+        <v>1716417.3043316</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20553937277082149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.20417207216016059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20435,7 +20424,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20448,10 +20437,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1315830089569092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1.1404913400000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20467,14 +20456,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.7739384062487</v>
+        <v>121.72472523866365</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20484,7 +20473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20500,11 +20489,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20520,13 +20509,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.03874288409996</v>
+        <v>64.47689349811607</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20536,13 +20525,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.399561739478642</v>
+        <v>79.948752689610018</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20552,13 +20541,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.618110477933342</v>
+        <v>98.299596821608375</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20568,13 +20557,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.86698307533452</v>
+        <v>110.63769354011853</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,7 +20573,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20594,25 +20583,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20621,7 +20610,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20630,7 +20619,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20643,11 +20632,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20656,7 +20645,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20669,7 +20658,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20682,7 +20671,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20691,7 +20680,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20704,7 +20693,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20713,7 +20702,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20728,7 +20717,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20743,7 +20732,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20756,12 +20745,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20774,7 +20763,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20783,7 +20772,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20796,16 +20785,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20818,25 +20807,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20849,7 +20838,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20862,23 +20851,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9123139141263654E-2</v>
+        <v>6.896448484596672E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.8356687898089177E-2</v>
+        <v>5.7767969735182854E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,7 +20877,7 @@
         <v>1.0614782273563756</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20899,7 +20888,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20912,7 +20901,7 @@
         <v>0.11027130711998644</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20926,7 +20915,7 @@
         <v>0.15195683827249326</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20940,7 +20929,7 @@
         <v>0.48913824057450628</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20954,7 +20943,7 @@
         <v>1.4835789300471205</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20964,43 +20953,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21013,20 +21002,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8062175970318615</v>
+        <v>-4.8440543063855621</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21035,7 +21024,7 @@
         <v>6.4100114768294941E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21044,12 +21033,12 @@
         <v>0.67756727799881356</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21062,7 +21051,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21075,25 +21064,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7294126405846821</v>
+        <v>8.7981345080911186</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21106,33 +21095,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.725292696037547</v>
+        <v>13.833344381182879</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.648487739590369</v>
+        <v>17.787424582888434</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21142,49 +21131,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21194,7 +21183,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21204,7 +21193,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21214,7 +21203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21223,97 +21212,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4584276266570915</v>
+        <v>1.469909025721776</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.07114966418051</v>
+        <v>124.04002117814301</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21331,7 +21320,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21347,14 +21336,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.63 HKD</v>
+        <v>153.83 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21370,14 +21359,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.75 HKD</v>
+        <v>133.8 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21392,14 +21381,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.62 HKD</v>
+        <v>117.54 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21414,14 +21403,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.46 HKD</v>
+        <v>104.28 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21436,14 +21425,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.68 HKD</v>
+        <v>93.41 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21452,29 +21441,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.7739384062487</v>
+        <v>121.72472523866365</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21484,30 +21473,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21516,7 +21505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21529,14 +21518,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21555,7 +21544,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21565,18 +21554,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.656192813939505</v>
+        <v>56.094343427955614</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.03874288409996</v>
+        <v>64.47689349811607</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21586,18 +21575,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.761119657038989</v>
+        <v>70.310310607170365</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.399561739478642</v>
+        <v>79.948752689610018</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21616,7 +21605,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21626,18 +21615,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.56597555800839</v>
+        <v>87.247461901683423</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.618110477933342</v>
+        <v>98.299596821608375</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21647,18 +21636,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.899692159654933</v>
+        <v>98.67040262443895</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.86698307533452</v>
+        <v>110.63769354011853</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21668,50 +21657,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21720,57 +21709,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21785,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAFE84A-6805-457C-BEBF-42AB8D0B3E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CA7A02-101E-470B-9785-0269B91E3017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.3</v>
+        <v>78.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1716417.3043316</v>
+        <v>1708841.6920174002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20417207216016059</v>
+        <v>0.20405081897043281</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1404913400000001</v>
+        <v>1.1343930029869078</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>121.72472523866365</v>
+        <v>121.07384927731576</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.47689349811607</v>
+        <v>64.176950658785245</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.948752689610018</v>
+        <v>79.572795455618461</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>98.299596821608375</v>
+        <v>97.833074711748765</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>110.63769354011853</v>
+        <v>110.11009166598124</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.896448484596672E-2</v>
+        <v>6.889982146819526E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.8024065864471189E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8440543063855621</v>
+        <v>-4.8181525966276784</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7981345080911186</v>
+        <v>8.7510898814156928</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.833344381182879</v>
+        <v>13.759375914175825</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.787424582888434</v>
+        <v>17.692313198963838</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.469909025721776</v>
+        <v>1.4620492548466744</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.83 HKD</v>
+        <v>153.01 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2867832949712033E-2</v>
+        <v>-4.2695014309958541E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.8 HKD</v>
+        <v>133.08 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.2887044365356531E-3</v>
+        <v>4.4784377905076316E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>117.54 HKD</v>
+        <v>116.91 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0273857600807444E-2</v>
+        <v>5.0481079710779017E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.28 HKD</v>
+        <v>103.72 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.474038259609327E-2</v>
+        <v>9.4965475609913752E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>93.41 HKD</v>
+        <v>92.91 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13740985688570595</v>
+        <v>0.137653008623597</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>121.72472523866365</v>
+        <v>121.07384927731576</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>56.094343427955614</v>
+        <v>55.794400588624789</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.47689349811607</v>
+        <v>64.176950658785245</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>70.310310607170365</v>
+        <v>69.934353373178809</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.948752689610018</v>
+        <v>79.572795455618461</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>87.247461901683423</v>
+        <v>86.780939791823812</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>98.299596821608375</v>
+        <v>97.833074711748765</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.67040262443895</v>
+        <v>98.14280075030166</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>110.63769354011853</v>
+        <v>110.11009166598124</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>75.331810079891142</v>
+        <v>74.929002316639355</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.469909025721776</v>
+        <v>1.4620492548466744</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104847.64986888001</v>
+        <v>-104287.01755059241</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8440543063855621</v>
+        <v>-4.8181525966276784</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>190432.16034709438</v>
+        <v>189413.89790949639</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7981345080911186</v>
+        <v>8.7510898814156928</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>299417.297259024</v>
+        <v>297816.27888896363</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.833344381182879</v>
+        <v>13.759375914175825</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>385001.80773723836</v>
+        <v>382943.15924786759</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.787424582888434</v>
+        <v>17.692313198963838</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.8024065864471189E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.8024065864471189E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4817150063051712E-2</v>
+        <v>5.5060164661177961E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0050441361916775E-2</v>
+        <v>5.027232425585814E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6078184110971004E-2</v>
+        <v>4.6282457251424956E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4688836482851597</v>
+        <v>5.4396409049140155</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.224706053759629</v>
+        <v>6.1914218419538107</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6862912847543425</v>
+        <v>5.6558860380042519</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5659081198674665</v>
+        <v>5.5361465756028174</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0477006491407224</v>
+        <v>5.0207100192077805</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.896448484596672E-2</v>
+        <v>6.889982146819526E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8495662720802384E-2</v>
+        <v>7.8422062595995073E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1706069164619704E-2</v>
+        <v>7.1638835186880953E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0187996467433372E-2</v>
+        <v>7.0122185884772856E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.365322382270773E-2</v>
+        <v>6.3593540458616593E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0706480673675224E-2</v>
+        <v>8.1064267478435023E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6866505404626861E-2</v>
+        <v>7.7207268886471309E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3172182360925514E-2</v>
+        <v>7.3496568223196862E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7760910884833686E-2</v>
+        <v>6.8061307576533378E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.787424582888434</v>
+        <v>17.692313198963838</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1404913400000001</v>
+        <v>1.1343930029869078</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2684797.462545054</v>
+        <v>2670441.5449117869</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>121.72896488911751</v>
+        <v>121.07806625787607</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>94.626976204160499</v>
+        <v>94.120994991341433</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>95.395371720373248</v>
+        <v>94.885281809265237</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>96.16376723658594</v>
+        <v>95.649568627188998</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.932162752798675</v>
+        <v>96.413855445112787</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.700558269011395</v>
+        <v>97.178142263036563</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>94.531886372685392</v>
+        <v>94.026413616018971</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>96.022948213310485</v>
+        <v>95.50950257925993</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>97.528339107850968</v>
+        <v>97.006843977333958</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>99.048059056306883</v>
+        <v>98.518437810241096</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>100.58210805867813</v>
+        <v>100.04428407798129</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>94.443224525156154</v>
+        <v>93.938225853480532</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>96.613952649549788</v>
+        <v>96.097346847506699</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.826113754648503</v>
+        <v>98.297679275373952</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>101.08010865314922</v>
+        <v>100.53962180658809</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>103.3763381577489</v>
+        <v>102.82357311065496</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>94.360556135851482</v>
+        <v>93.85599950146333</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>97.170516267826414</v>
+        <v>96.65093445676473</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>100.06036097118319</v>
+        <v>99.525326831551808</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>103.03163414009342</v>
+        <v>102.48071226461832</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>106.08589461745389</v>
+        <v>105.51864126355063</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>94.283476052583751</v>
+        <v>93.779331574174577</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.694646108814169</v>
+        <v>97.172261715832875</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>101.23419049180359</v>
+        <v>100.69287975211257</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.90582644923327</v>
+        <v>104.34488305414848</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.71334330565269</v>
+        <v>108.1320406845404</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>94.211606511075345</v>
+        <v>93.707846327285282</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>98.188232252774682</v>
+        <v>97.663208598498443</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>102.35055982609991</v>
+        <v>101.80327973250603</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>106.70575006547014</v>
+        <v>106.13518227393038</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>111.26117233663334</v>
+        <v>110.66624618368198</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>94.144595283561699</v>
+        <v>93.641193416432799</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>98.65305463543217</v>
+        <v>98.125545522966775</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>103.41228171046568</v>
+        <v>102.85932446910402</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>108.43434803724078</v>
+        <v>107.85453723558574</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>113.7317944272812</v>
+        <v>113.12365757678894</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>94.082113952546635</v>
+        <v>93.579046180206717</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>99.090789466652694</v>
+        <v>98.560939736218955</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>104.42203119489746</v>
+        <v>103.86367470810632</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>110.09444678868485</v>
+        <v>109.50575925004264</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>116.12754918184886</v>
+        <v>115.50660195798362</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>94.023856301250547</v>
+        <v>93.521100039203361</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>99.503015275074816</v>
+        <v>98.97096132632123</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>105.38235238288847</v>
+        <v>104.81886094939516</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>111.68876074112059</v>
+        <v>111.09154822429956</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>118.45070530749021</v>
+        <v>117.81733590338447</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.969536812862572</v>
+        <v>93.467071003302792</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.891218600488699</v>
+        <v>99.357088884366306</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>106.29566484139742</v>
+        <v>105.72728982222932</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>113.21989675138528</v>
+        <v>112.61449707603354</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>120.70346276265761</v>
+        <v>120.05804760801566</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.74829913169242</v>
+        <v>93.247016305196567</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>101.5181375032049</v>
+        <v>100.97530846652323</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>110.23380705089336</v>
+        <v>109.64437433706622</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>120.01214126621795</v>
+        <v>119.37042268630815</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.98371337856295</v>
+        <v>130.28332855371303</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>93.592389626359378</v>
+        <v>93.091940465735163</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.72313534691253</v>
+        <v>102.1738630495999</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>113.29792690827405</v>
+        <v>112.69210999679154</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>125.56111834635327</v>
+        <v>124.88972875437545</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>139.79793354582574</v>
+        <v>139.05041808244982</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>93.482517864349333</v>
+        <v>92.982656200542905</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>103.61563207856635</v>
+        <v>103.0615874996398</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>115.68200295249494</v>
+        <v>115.06343811503301</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>130.09439840843382</v>
+        <v>129.39876885195676</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>147.35518871981736</v>
+        <v>146.56726375281039</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>93.405089589136637</v>
+        <v>92.905641943131158</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>104.27667095110232</v>
+        <v>103.71909172208059</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>117.5369625654283</v>
+        <v>116.90847904777249</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>133.79789687751668</v>
+        <v>133.08246429316924</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>153.83473026530163</v>
+        <v>153.01215845210754</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>153.83473026530163</v>
+        <v>153.01215845210754</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>133.79789687751668</v>
+        <v>133.08246429316924</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>117.5369625654283</v>
+        <v>116.90847904777249</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.27667095110232</v>
+        <v>103.71909172208059</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>93.405089589136637</v>
+        <v>92.905641943131158</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>133.79789687751668</v>
+        <v>133.08246429316924</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>117.5369625654283</v>
+        <v>116.90847904777249</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.27667095110232</v>
+        <v>103.71909172208059</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>117.47407652426449</v>
+        <v>116.84592926542885</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>153.83473026530163</v>
+        <v>153.01215845210754</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>93.405089589136637</v>
+        <v>92.905641943131158</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.3</v>
+        <v>78.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20417207216016059</v>
+        <v>0.20405081897043281</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.0898068382988458E-2</v>
+        <v>3.1097800144884582E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>121.72472523866365</v>
+        <v>121.07384927731576</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>121.72896488911751</v>
+        <v>121.07806625787607</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009313</v>
+        <v>0.14612827877009316</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>56.094343427955614</v>
+        <v>55.794400588624789</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.47689349811607</v>
+        <v>64.176950658785245</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47030569695928837</v>
+        <v>0.46993548944008545</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>70.310310607170365</v>
+        <v>69.934353373178809</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.948752689610018</v>
+        <v>79.572795455618461</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34320038486136795</v>
+        <v>0.34277471204075183</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>87.247461901683423</v>
+        <v>86.780939791823812</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>98.299596821608375</v>
+        <v>97.833074711748765</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19244346923869426</v>
+        <v>0.19195536199014163</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>98.67040262443895</v>
+        <v>98.14280075030166</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>110.63769354011853</v>
+        <v>110.11009166598124</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.1082823779696009E-2</v>
+        <v>9.0554299518654791E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.3</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1716417.3043316</v>
+        <v>1708841.6920174002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20417207216016059</v>
+        <v>0.20405081897043281</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1404913400000001</v>
+        <v>1.1343930029869078</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>121.72472523866365</v>
+        <v>121.07384927731576</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.47689349811607</v>
+        <v>64.176950658785245</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.948752689610018</v>
+        <v>79.572795455618461</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>98.299596821608375</v>
+        <v>97.833074711748765</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>110.63769354011853</v>
+        <v>110.11009166598124</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.896448484596672E-2</v>
+        <v>6.889982146819526E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7767969735182854E-2</v>
+        <v>5.8024065864471189E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8440543063855621</v>
+        <v>-4.8181525966276784</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7981345080911186</v>
+        <v>8.7510898814156928</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.833344381182879</v>
+        <v>13.759375914175825</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.787424582888434</v>
+        <v>17.692313198963838</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.469909025721776</v>
+        <v>1.4620492548466744</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>124.04002117814301</v>
+        <v>123.37676506586476</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.83 HKD</v>
+        <v>153.01 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.8 HKD</v>
+        <v>133.08 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>117.54 HKD</v>
+        <v>116.91 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.28 HKD</v>
+        <v>103.72 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>93.41 HKD</v>
+        <v>92.91 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>121.72472523866365</v>
+        <v>121.07384927731576</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>56.094343427955614</v>
+        <v>55.794400588624789</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.47689349811607</v>
+        <v>64.176950658785245</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>70.310310607170365</v>
+        <v>69.934353373178809</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.948752689610018</v>
+        <v>79.572795455618461</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>87.247461901683423</v>
+        <v>86.780939791823812</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>98.299596821608375</v>
+        <v>97.833074711748765</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>98.67040262443895</v>
+        <v>98.14280075030166</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>110.63769354011853</v>
+        <v>110.11009166598124</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CA7A02-101E-470B-9785-0269B91E3017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74CED8F-9A67-4A1D-9A93-B30EB46EA1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.95</v>
+        <v>77.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1708841.6920174002</v>
+        <v>1681785.9337524001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20405081897043281</v>
+        <v>0.20903480221731505</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>121.07384927731576</v>
+        <v>120.50521344629963</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.176950658785245</v>
+        <v>63.914906497026656</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.572795455618461</v>
+        <v>79.244341546006254</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.833074711748765</v>
+        <v>97.425499070027357</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>110.11009166598124</v>
+        <v>109.64915387143677</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.889982146819526E-2</v>
+        <v>6.9679447489002386E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8024065864471189E-2</v>
+        <v>5.8957528957528961E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8181525966276784</v>
+        <v>-4.7955236456023362</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7510898814156928</v>
+        <v>8.7099894844536863</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.759375914175825</v>
+        <v>13.6947535848791</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.692313198963838</v>
+        <v>17.609219423730451</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4620492548466744</v>
+        <v>1.4551825896008042</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.01 HKD</v>
+        <v>152.29 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2695014309958541E-2</v>
+        <v>-4.2542506530298764E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.08 HKD</v>
+        <v>132.46 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4784377905076316E-3</v>
+        <v>4.6458740277529583E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.91 HKD</v>
+        <v>116.36 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0481079710779017E-2</v>
+        <v>5.0663951316206726E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.72 HKD</v>
+        <v>103.23 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.4965475609913752E-2</v>
+        <v>9.5164120146054618E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.91 HKD</v>
+        <v>92.47 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.137653008623597</v>
+        <v>0.13786759214476152</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>121.07384927731576</v>
+        <v>120.50521344629963</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.794400588624789</v>
+        <v>55.532356426866201</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.176950658785245</v>
+        <v>63.914906497026656</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.934353373178809</v>
+        <v>69.605899463566601</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.572795455618461</v>
+        <v>79.244341546006254</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.780939791823812</v>
+        <v>86.373364150102404</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.833074711748765</v>
+        <v>97.425499070027357</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.14280075030166</v>
+        <v>97.681862955757182</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>110.11009166598124</v>
+        <v>109.64915387143677</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.929002316639355</v>
+        <v>74.577090522690014</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4620492548466744</v>
+        <v>1.4551825896008042</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104287.01755059241</v>
+        <v>-103797.22280760668</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8181525966276784</v>
+        <v>-4.7955236456023371</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>189413.89790949639</v>
+        <v>188524.29598565673</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7510898814156928</v>
+        <v>8.7099894844536863</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>297816.27888896363</v>
+        <v>296417.55399298487</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.759375914175825</v>
+        <v>13.6947535848791</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>382943.15924786759</v>
+        <v>381144.62717103492</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.692313198963838</v>
+        <v>17.609219423730451</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8024065864471189E-2</v>
+        <v>5.8957528957528961E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8024065864471189E-2</v>
+        <v>5.8957528957528961E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5060164661177961E-2</v>
+        <v>5.594594594594595E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.027232425585814E-2</v>
+        <v>5.108108108108108E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6282457251424956E-2</v>
+        <v>4.7027027027027032E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4396409049140155</v>
+        <v>5.4140930698954861</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1914218419538107</v>
+        <v>6.1623431901616561</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6558860380042519</v>
+        <v>5.6293225853961948</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5361465756028174</v>
+        <v>5.5101454917400705</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0207100192077805</v>
+        <v>4.9971297363382394</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.889982146819526E-2</v>
+        <v>6.9679447489002386E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8422062595995073E-2</v>
+        <v>7.9309436166816683E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1638835186880953E-2</v>
+        <v>7.2449454123503149E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0122185884772856E-2</v>
+        <v>7.0915643394338104E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.3593540458616593E-2</v>
+        <v>6.4313124019797163E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1064267478435023E-2</v>
+        <v>8.2368390185617049E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7207268886471309E-2</v>
+        <v>7.8449342066755592E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3496568223196862E-2</v>
+        <v>7.4678945446864764E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8061307576533378E-2</v>
+        <v>6.9156244957108245E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.692313198963838</v>
+        <v>17.609219423730451</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2670441.5449117869</v>
+        <v>2657899.5405389611</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>121.07806625787607</v>
+        <v>120.50941062137545</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>94.120994991341433</v>
+        <v>93.678946022696024</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.885281809265237</v>
+        <v>94.439643288685716</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.649568627188998</v>
+        <v>95.20034055467535</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.413855445112787</v>
+        <v>95.961037820665013</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.178142263036563</v>
+        <v>96.721735086654675</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>94.026413616018971</v>
+        <v>93.58480885856595</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.50950257925993</v>
+        <v>95.06093234139874</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>97.006843977333958</v>
+        <v>96.551241321033189</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.518437810241096</v>
+        <v>98.055735797469353</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>100.04428407798129</v>
+        <v>99.574415770707148</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.938225853480532</v>
+        <v>93.497035278957483</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>96.097346847506699</v>
+        <v>95.646015738359281</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.297679275373952</v>
+        <v>97.836014077849057</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.53962180658809</v>
+        <v>100.06742709454015</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.82357311065496</v>
+        <v>102.3406515855459</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.85599950146333</v>
+        <v>93.415195111490377</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.65093445676473</v>
+        <v>96.197003366266173</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.525326831551808</v>
+        <v>99.057895860555035</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.48071226461832</v>
+        <v>101.99940102086458</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.51864126355063</v>
+        <v>105.02306207266226</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.779331574174577</v>
+        <v>93.338887263036213</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.172261715832875</v>
+        <v>96.715882158047947</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.69287975211257</v>
+        <v>100.21996524830338</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.34488305414848</v>
+        <v>103.85481653985212</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.1320406845404</v>
+        <v>107.6241873935024</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.707846327285282</v>
+        <v>93.267737753988001</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.663208598498443</v>
+        <v>97.204523258000947</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.80327973250603</v>
+        <v>101.32515012056754</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>106.13518227393038</v>
+        <v>105.63670743454412</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.66624618368198</v>
+        <v>110.14649073492312</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.641193416432799</v>
+        <v>93.201397885411609</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>98.125545522966775</v>
+        <v>97.664688769378628</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.85932446910402</v>
+        <v>102.37623503404956</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.85453723558574</v>
+        <v>107.34798726814113</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>113.12365757678894</v>
+        <v>112.59236064175531</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.579046180206717</v>
+        <v>93.139542530095625</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.560939736218955</v>
+        <v>98.09803810876457</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.86367470810632</v>
+        <v>103.37586823848002</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.50575925004264</v>
+        <v>108.99145414795923</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.50660195798362</v>
+        <v>114.96411327868353</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.521100039203361</v>
+        <v>93.081868539125011</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.97096132632123</v>
+        <v>98.50613399014432</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.81886094939516</v>
+        <v>104.32656834898725</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>111.09154822429956</v>
+        <v>110.56979530060501</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.81733590338447</v>
+        <v>117.2639946235836</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.467071003302792</v>
+        <v>93.028093256168717</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.357088884366306</v>
+        <v>98.890448060254897</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.72728982222932</v>
+        <v>105.23073069184731</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.61449707603354</v>
+        <v>112.08559146584996</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>120.05804760801566</v>
+        <v>119.49418259439582</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.247016305196567</v>
+        <v>92.809072067667358</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.97530846652323</v>
+        <v>100.50106750710302</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.64437433706622</v>
+        <v>109.12941821491803</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.37042268630815</v>
+        <v>118.80978717411341</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.28332855371303</v>
+        <v>129.67143945262396</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>93.091940465735163</v>
+        <v>92.654724557893744</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.1738630495999</v>
+        <v>101.6939929548591</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.69210999679154</v>
+        <v>112.16283986951399</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.88972875437545</v>
+        <v>124.30317125149999</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>139.05041808244982</v>
+        <v>138.39735344040355</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.982656200542905</v>
+        <v>92.545953557533849</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>103.0615874996398</v>
+        <v>102.57754811538376</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>115.06343811503301</v>
+        <v>114.52303080046707</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.39876885195676</v>
+        <v>128.79103417681594</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.56726375281039</v>
+        <v>145.87889546914457</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.905641943131158</v>
+        <v>92.469301005531861</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.71909172208059</v>
+        <v>103.23196430137278</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.90847904777249</v>
+        <v>116.35940630801102</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>133.08246429316924</v>
+        <v>132.45742876213816</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>153.01215845210754</v>
+        <v>152.29352105521025</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>153.01215845210754</v>
+        <v>152.29352105521025</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>133.08246429316924</v>
+        <v>132.45742876213816</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.90847904777249</v>
+        <v>116.35940630801102</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.71909172208059</v>
+        <v>103.23196430137278</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.905641943131158</v>
+        <v>92.469301005531861</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>133.08246429316924</v>
+        <v>132.45742876213816</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.90847904777249</v>
+        <v>116.35940630801102</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.71909172208059</v>
+        <v>103.23196430137278</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.84592926542885</v>
+        <v>116.2971502971769</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>153.01215845210754</v>
+        <v>152.29352105521025</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.905641943131158</v>
+        <v>92.469301005531861</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.95</v>
+        <v>77.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20405081897043281</v>
+        <v>0.20903480221731505</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1097800144884582E-2</v>
+        <v>3.1274060824108531E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>121.07384927731576</v>
+        <v>120.50521344629963</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>121.07806625787607</v>
+        <v>120.50941062137545</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.794400588624789</v>
+        <v>55.532356426866201</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.176950658785245</v>
+        <v>63.914906497026656</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46993548944008545</v>
+        <v>0.46960878563557873</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.934353373178809</v>
+        <v>69.605899463566601</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.572795455618461</v>
+        <v>79.244341546006254</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34277471204075183</v>
+        <v>0.34239906075665627</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.780939791823812</v>
+        <v>86.373364150102404</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.833074711748765</v>
+        <v>97.425499070027357</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19195536199014163</v>
+        <v>0.1915246130538345</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>98.14280075030166</v>
+        <v>97.681862955757182</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>110.11009166598124</v>
+        <v>109.64915387143677</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0554299518654791E-2</v>
+        <v>9.0087883041679473E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.95</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1708841.6920174002</v>
+        <v>1681785.9337524001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20405081897043281</v>
+        <v>0.20903480221731505</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>121.07384927731576</v>
+        <v>120.50521344629963</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.176950658785245</v>
+        <v>63.914906497026656</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.572795455618461</v>
+        <v>79.244341546006254</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.833074711748765</v>
+        <v>97.425499070027357</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>110.11009166598124</v>
+        <v>109.64915387143677</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.889982146819526E-2</v>
+        <v>6.9679447489002386E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.8024065864471189E-2</v>
+        <v>5.8957528957528961E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8181525966276784</v>
+        <v>-4.7955236456023362</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7510898814156928</v>
+        <v>8.7099894844536863</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.759375914175825</v>
+        <v>13.6947535848791</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.692313198963838</v>
+        <v>17.609219423730451</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4620492548466744</v>
+        <v>1.4551825896008042</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.37676506586476</v>
+        <v>122.7973133531285</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.01 HKD</v>
+        <v>152.29 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.08 HKD</v>
+        <v>132.46 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.91 HKD</v>
+        <v>116.36 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.72 HKD</v>
+        <v>103.23 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.91 HKD</v>
+        <v>92.47 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>121.07384927731576</v>
+        <v>120.50521344629963</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.794400588624789</v>
+        <v>55.532356426866201</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.176950658785245</v>
+        <v>63.914906497026656</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.934353373178809</v>
+        <v>69.605899463566601</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.572795455618461</v>
+        <v>79.244341546006254</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.780939791823812</v>
+        <v>86.373364150102404</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.833074711748765</v>
+        <v>97.425499070027357</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>98.14280075030166</v>
+        <v>97.681862955757182</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>110.11009166598124</v>
+        <v>109.64915387143677</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74CED8F-9A67-4A1D-9A93-B30EB46EA1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58A07F3-04E3-4995-B0B7-919632517826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,58 +4992,58 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>77.7</v>
+        <v>79</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1681785.9337524001</v>
+        <v>1709923.9223480001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20903480221731505</v>
+        <v>0.20548107287719827</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.50521344629963</v>
+        <v>121.63079002459784</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.914906497026656</v>
+        <v>64.433605381035051</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.244341546006254</v>
+        <v>79.894494082207387</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.425499070027357</v>
+        <v>98.232267780656642</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>109.64915387143677</v>
+        <v>110.56154939295112</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="464"/>
-      <c r="D54" s="464"/>
-      <c r="E54" s="464"/>
-      <c r="F54" s="464"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="465"/>
+      <c r="E54" s="465"/>
+      <c r="F54" s="465"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9679447489002386E-2</v>
+        <v>6.9172953162396036E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8957528957528961E-2</v>
+        <v>5.7987341772151903E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7955236456023362</v>
+        <v>-4.8403161399832593</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7099894844536863</v>
+        <v>8.7913449700841362</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.6947535848791</v>
+        <v>13.822669161640221</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.609219423730451</v>
+        <v>17.773697991741098</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4551825896008042</v>
+        <v>1.468774693985001</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.29 HKD</v>
+        <v>153.72 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2542506530298764E-2</v>
+        <v>-4.2843005561615501E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.46 HKD</v>
+        <v>133.69 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.6458740277529583E-3</v>
+        <v>4.3159616937661844E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.36 HKD</v>
+        <v>117.45 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0663951316206726E-2</v>
+        <v>5.0303627170130892E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.23 HKD</v>
+        <v>104.2 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.5164120146054618E-2</v>
+        <v>9.4772719353202597E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.47 HKD</v>
+        <v>93.33 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13786759214476152</v>
+        <v>0.13744478779032487</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.50521344629963</v>
+        <v>121.63079002459784</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6491,13 +6491,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="465" t="s">
+      <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
-      <c r="C127" s="465"/>
-      <c r="D127" s="465"/>
-      <c r="E127" s="465"/>
-      <c r="F127" s="465"/>
+      <c r="C127" s="466"/>
+      <c r="D127" s="466"/>
+      <c r="E127" s="466"/>
+      <c r="F127" s="466"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.532356426866201</v>
+        <v>56.051055310874595</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.914906497026656</v>
+        <v>64.433605381035051</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.605899463566601</v>
+        <v>70.256051999767735</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.244341546006254</v>
+        <v>79.894494082207387</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.373364150102404</v>
+        <v>87.180132860731689</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.425499070027357</v>
+        <v>98.232267780656642</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.681862955757182</v>
+        <v>98.594258477271538</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>109.64915387143677</v>
+        <v>110.56154939295112</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6715,13 +6715,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="464" t="s">
+      <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="464"/>
-      <c r="D152" s="464"/>
-      <c r="E152" s="464"/>
-      <c r="F152" s="464"/>
+      <c r="C152" s="465"/>
+      <c r="D152" s="465"/>
+      <c r="E152" s="465"/>
+      <c r="F152" s="465"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.577090522690014</v>
+        <v>75.273676371296247</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4551825896008042</v>
+        <v>1.468774693985001</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-103797.22280760668</v>
+        <v>-104766.73872765197</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7955236456023371</v>
+        <v>-4.8403161399832593</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>188524.29598565673</v>
+        <v>190285.20346785607</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7099894844536863</v>
+        <v>8.791344970084138</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>296417.55399298487</v>
+        <v>299186.23633152648</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.6947535848791</v>
+        <v>13.822669161640224</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>381144.62717103492</v>
+        <v>384704.70107173058</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.609219423730451</v>
+        <v>17.773697991741102</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8957528957528961E-2</v>
+        <v>5.7987341772151903E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8957528957528961E-2</v>
+        <v>5.7987341772151903E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.594594594594595E-2</v>
+        <v>5.5025316455696208E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.108108108108108E-2</v>
+        <v>5.0240506329113928E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7027027027027032E-2</v>
+        <v>4.6253164556962031E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4140930698954861</v>
+        <v>5.4646632998292866</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1623431901616561</v>
+        <v>6.2199024356408774</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6293225853961948</v>
+        <v>5.6819031623903236</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5101454917400705</v>
+        <v>5.5616128974327044</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9971297363382394</v>
+        <v>5.0438053284481725</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9679447489002386E-2</v>
+        <v>6.9172953162396036E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9309436166816683E-2</v>
+        <v>7.8732942223302252E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.2449454123503149E-2</v>
+        <v>7.1922824840383842E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0915643394338104E-2</v>
+        <v>7.0400163258641832E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.4313124019797163E-2</v>
+        <v>6.3845637068964206E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2368390185617049E-2</v>
+        <v>8.1012960980030954E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8449342066755592E-2</v>
+        <v>7.7158403526416577E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4678945446864764E-2</v>
+        <v>7.345005140786573E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9156244957108245E-2</v>
+        <v>6.8018230799586216E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.609219423730451</v>
+        <v>17.773697991741098</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2657899.5405389611</v>
+        <v>2682725.5989703122</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>120.50941062137545</v>
+        <v>121.63502640330498</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18160,10 +18160,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="468" t="s">
+      <c r="J52" s="469" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="468"/>
+      <c r="K52" s="469"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>1972635.5401994288</v>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>93.678946022696024</v>
+        <v>94.553952377253452</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.439643288685716</v>
+        <v>95.321754921108592</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.20034055467535</v>
+        <v>96.08955746496369</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>95.961037820665013</v>
+        <v>96.85736000881883</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>96.721735086654675</v>
+        <v>97.625162552673956</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.58480885856595</v>
+        <v>94.458935926791582</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.06093234139874</v>
+        <v>95.948847112010313</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>96.551241321033189</v>
+        <v>97.453076293384839</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.055735797469353</v>
+        <v>98.971623470915219</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>99.574415770707148</v>
+        <v>100.50448864460137</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.497035278957483</v>
+        <v>94.370342499787512</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>95.646015738359281</v>
+        <v>96.539395468943439</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>97.836014077849057</v>
+        <v>98.749849444890302</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.06742709454015</v>
+        <v>101.00210493101709</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.3406515855459</v>
+        <v>103.2965624307128</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.415195111490377</v>
+        <v>94.28773790584431</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.197003366266173</v>
+        <v>97.095529585962012</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.057895860555035</v>
+        <v>99.983144190377971</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>101.99940102086458</v>
+        <v>102.95212442183755</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.02306207266226</v>
+        <v>106.00402792027538</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.338887263036213</v>
+        <v>94.210717305431089</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>96.715882158047947</v>
+        <v>97.619254954902587</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.21996524830338</v>
+        <v>101.15606786440821</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>103.85481653985212</v>
+        <v>104.82487041302176</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>107.6241873935024</v>
+        <v>108.62944900106336</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.267737753988001</v>
+        <v>94.138903225791694</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.204523258000947</v>
+        <v>98.112460197448016</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.32515012056754</v>
+        <v>102.27157569425515</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>105.63670743454412</v>
+        <v>106.62340502460192</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.14649073492312</v>
+        <v>111.17531186728201</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.201397885411609</v>
+        <v>94.071943710976427</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>97.664688769378628</v>
+        <v>98.576923875742594</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.37623503404956</v>
+        <v>103.33247824571799</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.34798726814113</v>
+        <v>108.35066903385842</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>112.59236064175531</v>
+        <v>113.64402737391823</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.139542530095625</v>
+        <v>94.009510596929545</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.09803810876457</v>
+        <v>99.014320906117874</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.37586823848002</v>
+        <v>104.34144850445189</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>108.99145414795923</v>
+        <v>110.00948668377376</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>114.96411327868353</v>
+        <v>116.03793331974735</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.081868539125011</v>
+        <v>93.951297903179551</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>98.50613399014432</v>
+        <v>99.426228599058675</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.32656834898725</v>
+        <v>105.30102861066031</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>110.56979530060501</v>
+        <v>111.60257030094181</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.2639946235836</v>
+        <v>118.35929666115737</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.028093256168717</v>
+        <v>93.897020333249472</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>98.890448060254897</v>
+        <v>99.814132347189442</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.23073069184731</v>
+        <v>106.21363626411728</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.08559146584996</v>
+        <v>113.13252473048323</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>119.49418259439582</v>
+        <v>120.61031565888834</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>92.809072067667358</v>
+        <v>93.675953381640625</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>100.50106750710302</v>
+        <v>101.43979575333258</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.12941821491803</v>
+        <v>110.14873940138902</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>118.80978717411341</v>
+        <v>119.91952765663096</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>129.67143945262396</v>
+        <v>130.88263298482025</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>92.654724557893744</v>
+        <v>93.520164191984861</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>101.6939929548591</v>
+        <v>102.64386369779274</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.16283986951399</v>
+        <v>113.21049467134377</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.30317125149999</v>
+        <v>125.46422258004877</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>138.39735344040355</v>
+        <v>139.69005120074067</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>92.545953557533849</v>
+        <v>93.410377218233435</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>102.57754811538376</v>
+        <v>103.53567168793265</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>114.52303080046707</v>
+        <v>115.59273091931026</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>128.79103417681594</v>
+        <v>129.99400430083327</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>145.87889546914457</v>
+        <v>147.24147442579073</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.469301005531861</v>
+        <v>93.333008694575682</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.23196430137278</v>
+        <v>104.19620043544779</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.35940630801102</v>
+        <v>117.44625905619812</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>132.45742876213816</v>
+        <v>133.69464477273598</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>152.29352105521025</v>
+        <v>153.71601569609729</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>152.29352105521025</v>
+        <v>153.71601569609729</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>132.45742876213816</v>
+        <v>133.69464477273598</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.35940630801102</v>
+        <v>117.44625905619812</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.23196430137278</v>
+        <v>104.19620043544779</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.469301005531861</v>
+        <v>93.333008694575682</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19471,7 +19471,7 @@
       <c r="C4" s="449">
         <v>2</v>
       </c>
-      <c r="D4" s="469" t="str">
+      <c r="D4" s="460" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19481,16 +19481,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 0941.HK – 中国移动: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="469"/>
-      <c r="F4" s="469"/>
-      <c r="G4" s="469"/>
+      <c r="E4" s="460"/>
+      <c r="F4" s="460"/>
+      <c r="G4" s="460"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="445"/>
-      <c r="D5" s="469"/>
-      <c r="E5" s="469"/>
-      <c r="F5" s="469"/>
-      <c r="G5" s="469"/>
+      <c r="D5" s="460"/>
+      <c r="E5" s="460"/>
+      <c r="F5" s="460"/>
+      <c r="G5" s="460"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19500,10 +19500,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000000 CNY</v>
       </c>
-      <c r="D6" s="469"/>
-      <c r="E6" s="469"/>
-      <c r="F6" s="469"/>
-      <c r="G6" s="469"/>
+      <c r="D6" s="460"/>
+      <c r="E6" s="460"/>
+      <c r="F6" s="460"/>
+      <c r="G6" s="460"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19513,10 +19513,10 @@
         <f>Normalized_FCF!G8</f>
         <v>142590</v>
       </c>
-      <c r="D7" s="469"/>
-      <c r="E7" s="469"/>
-      <c r="F7" s="469"/>
-      <c r="G7" s="469"/>
+      <c r="D7" s="460"/>
+      <c r="E7" s="460"/>
+      <c r="F7" s="460"/>
+      <c r="G7" s="460"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19526,10 +19526,10 @@
         <f>Normalized_FCF!G19</f>
         <v>118134.44704364182</v>
       </c>
-      <c r="D8" s="469"/>
-      <c r="E8" s="469"/>
-      <c r="F8" s="469"/>
-      <c r="G8" s="469"/>
+      <c r="D8" s="460"/>
+      <c r="E8" s="460"/>
+      <c r="F8" s="460"/>
+      <c r="G8" s="460"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19539,27 +19539,27 @@
         <f>Normalized_FCF!C19</f>
         <v>103790.20955470968</v>
       </c>
-      <c r="D9" s="469"/>
-      <c r="E9" s="469"/>
-      <c r="F9" s="469"/>
-      <c r="G9" s="469"/>
+      <c r="D9" s="460"/>
+      <c r="E9" s="460"/>
+      <c r="F9" s="460"/>
+      <c r="G9" s="460"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="448"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
-      <c r="F10" s="469"/>
-      <c r="G10" s="469"/>
+      <c r="D10" s="460"/>
+      <c r="E10" s="460"/>
+      <c r="F10" s="460"/>
+      <c r="G10" s="460"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="448"/>
-      <c r="D11" s="469"/>
-      <c r="E11" s="469"/>
-      <c r="F11" s="469"/>
-      <c r="G11" s="469"/>
+      <c r="D11" s="460"/>
+      <c r="E11" s="460"/>
+      <c r="F11" s="460"/>
+      <c r="G11" s="460"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19569,10 +19569,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.3768659363842009E-2</v>
       </c>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
-      <c r="G12" s="469"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+      <c r="G12" s="460"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19582,10 +19582,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.0952518792346746E-2</v>
       </c>
-      <c r="D13" s="469"/>
-      <c r="E13" s="469"/>
-      <c r="F13" s="469"/>
-      <c r="G13" s="469"/>
+      <c r="D13" s="460"/>
+      <c r="E13" s="460"/>
+      <c r="F13" s="460"/>
+      <c r="G13" s="460"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19595,10 +19595,10 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.7526861635440518E-2</v>
       </c>
-      <c r="D14" s="469"/>
-      <c r="E14" s="469"/>
-      <c r="F14" s="469"/>
-      <c r="G14" s="469"/>
+      <c r="D14" s="460"/>
+      <c r="E14" s="460"/>
+      <c r="F14" s="460"/>
+      <c r="G14" s="460"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>132.45742876213816</v>
+        <v>133.69464477273598</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.35940630801102</v>
+        <v>117.44625905619812</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.23196430137278</v>
+        <v>104.19620043544779</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.2971502971769</v>
+        <v>117.38342154431811</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>152.29352105521025</v>
+        <v>153.71601569609729</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.469301005531861</v>
+        <v>93.333008694575682</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>77.7</v>
+        <v>79</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20903480221731505</v>
+        <v>0.20548107287719827</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1274060824108531E-2</v>
+        <v>3.092676194393338E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.50521344629963</v>
+        <v>121.63079002459784</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>120.50941062137545</v>
+        <v>121.63502640330498</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009316</v>
+        <v>0.14612827877009318</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.532356426866201</v>
+        <v>56.051055310874595</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>63.914906497026656</v>
+        <v>64.433605381035051</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46960878563557873</v>
+        <v>0.4702525128053151</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.605899463566601</v>
+        <v>70.256051999767735</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.244341546006254</v>
+        <v>79.894494082207387</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34239906075665627</v>
+        <v>0.34313923254095424</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.373364150102404</v>
+        <v>87.180132860731689</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.425499070027357</v>
+        <v>98.232267780656642</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.1915246130538345</v>
+        <v>0.1923733475644549</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.681862955757182</v>
+        <v>98.594258477271538</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>109.64915387143677</v>
+        <v>110.56154939295112</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0087883041679473E-2</v>
+        <v>9.1006895781965635E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>77.7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1681785.9337524001</v>
+        <v>1709923.9223480001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20903480221731505</v>
+        <v>0.20548107287719827</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.50521344629963</v>
+        <v>121.63079002459784</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>63.914906497026656</v>
+        <v>64.433605381035051</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.244341546006254</v>
+        <v>79.894494082207387</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.425499070027357</v>
+        <v>98.232267780656642</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>109.64915387143677</v>
+        <v>110.56154939295112</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9679447489002386E-2</v>
+        <v>6.9172953162396036E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.8957528957528961E-2</v>
+        <v>5.7987341772151903E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.7955236456023362</v>
+        <v>-4.8403161399832593</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7099894844536863</v>
+        <v>8.7913449700841362</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.6947535848791</v>
+        <v>13.822669161640221</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.609219423730451</v>
+        <v>17.773697991741098</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4551825896008042</v>
+        <v>1.468774693985001</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>122.7973133531285</v>
+        <v>123.94429924556728</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>152.29 HKD</v>
+        <v>153.72 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>132.46 HKD</v>
+        <v>133.69 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.36 HKD</v>
+        <v>117.45 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.23 HKD</v>
+        <v>104.2 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.47 HKD</v>
+        <v>93.33 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.50521344629963</v>
+        <v>121.63079002459784</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.532356426866201</v>
+        <v>56.051055310874595</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>63.914906497026656</v>
+        <v>64.433605381035051</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.605899463566601</v>
+        <v>70.256051999767735</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.244341546006254</v>
+        <v>79.894494082207387</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.373364150102404</v>
+        <v>87.180132860731689</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.425499070027357</v>
+        <v>98.232267780656642</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.681862955757182</v>
+        <v>98.594258477271538</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>109.64915387143677</v>
+        <v>110.56154939295112</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58A07F3-04E3-4995-B0B7-919632517826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4FAA19-0268-46B6-854D-ADBC74DEC144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,36 +4995,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79</v>
+        <v>79.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1709923.9223480001</v>
+        <v>1730486.2986294001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20548107287719827</v>
+        <v>0.19891673811808264</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>121.63079002459784</v>
+        <v>121.12182318226319</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.433605381035051</v>
+        <v>64.199058449083594</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.894494082207387</v>
+        <v>79.600506014432852</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>98.232267780656642</v>
+        <v>97.867460506713343</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>110.56154939295112</v>
+        <v>110.14897944746811</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9172953162396036E-2</v>
+        <v>6.8064994251226946E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7987341772151903E-2</v>
+        <v>5.7298311444652909E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8403161399832593</v>
+        <v>-4.8200617256102989</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7913449700841362</v>
+        <v>8.7545573845690434</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.822669161640221</v>
+        <v>13.764827884160944</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.773697991741098</v>
+        <v>17.699323543119686</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.468774693985001</v>
+        <v>1.4626285724482797</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.72 HKD</v>
+        <v>153.07 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2843005561615501E-2</v>
+        <v>-4.2707815493214861E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.69 HKD</v>
+        <v>133.14 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.3159616937661844E-3</v>
+        <v>4.4643836154445995E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>117.45 HKD</v>
+        <v>116.95 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0303627170130892E-2</v>
+        <v>5.0465730009150445E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.2 HKD</v>
+        <v>103.76 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.4772719353202597E-2</v>
+        <v>9.4948802061391502E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>93.33 HKD</v>
+        <v>92.94 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13744478779032487</v>
+        <v>0.13763499730306819</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>121.63079002459784</v>
+        <v>121.12182318226319</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>56.051055310874595</v>
+        <v>55.816508378923139</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.433605381035051</v>
+        <v>64.199058449083594</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>70.256051999767735</v>
+        <v>69.9620639319932</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.894494082207387</v>
+        <v>79.600506014432852</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>87.180132860731689</v>
+        <v>86.81532558678839</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>98.232267780656642</v>
+        <v>97.867460506713343</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.594258477271538</v>
+        <v>98.181688531788524</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>110.56154939295112</v>
+        <v>110.14897944746811</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>75.273676371296247</v>
+        <v>74.958691938769988</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.468774693985001</v>
+        <v>1.4626285724482797</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104766.73872765197</v>
+        <v>-104328.3398963928</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8403161399832593</v>
+        <v>-4.8200617256102989</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>190285.20346785607</v>
+        <v>189488.95065117654</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.791344970084138</v>
+        <v>8.7545573845690434</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>299186.23633152648</v>
+        <v>297934.28463455196</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.822669161640224</v>
+        <v>13.764827884160944</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>384704.70107173058</v>
+        <v>383094.8953893357</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.773697991741102</v>
+        <v>17.699323543119689</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7987341772151903E-2</v>
+        <v>5.7298311444652909E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7987341772151903E-2</v>
+        <v>5.7298311444652909E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5025316455696208E-2</v>
+        <v>5.4371482176360231E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0240506329113928E-2</v>
+        <v>4.9643527204502817E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6253164556962031E-2</v>
+        <v>4.5703564727954976E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4646632998292866</v>
+        <v>5.4417962903855948</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.2199024356408774</v>
+        <v>6.1938751106382393</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6819031623903236</v>
+        <v>5.6581271077381405</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5616128974327044</v>
+        <v>5.5383402001648374</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0438053284481725</v>
+        <v>5.0226994088791903</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9172953162396036E-2</v>
+        <v>6.8064994251226946E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8732942223302252E-2</v>
+        <v>7.7471858794724693E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1922824840383842E-2</v>
+        <v>7.0770820609607765E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0400163258641832E-2</v>
+        <v>6.9272547844463253E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.3845637068964206E-2</v>
+        <v>6.2823006990358851E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1012960980030954E-2</v>
+        <v>8.005033042429574E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7158403526416577E-2</v>
+        <v>7.6241574466377859E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.345005140786573E-2</v>
+        <v>7.2577286569373262E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8018230799586216E-2</v>
+        <v>6.7210009170322826E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.773697991741098</v>
+        <v>17.699323543119686</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2682725.5989703122</v>
+        <v>2671499.6719112005</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>121.63502640330498</v>
+        <v>121.12604183374607</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>94.553952377253452</v>
+        <v>94.158289185704831</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>95.321754921108592</v>
+        <v>94.9228788421307</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>96.08955746496369</v>
+        <v>95.687468498556541</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.85736000881883</v>
+        <v>96.452058154982396</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.625162552673956</v>
+        <v>97.216647811408251</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>94.458935926791582</v>
+        <v>94.0636703337684</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.948847112010313</v>
+        <v>95.547346951316015</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>97.453076293384839</v>
+        <v>97.045281651034728</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.971623470915219</v>
+        <v>98.557474432924607</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>100.50448864460137</v>
+        <v>100.08392529698554</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>94.370342499787512</v>
+        <v>93.975447628000168</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>96.539395468943439</v>
+        <v>96.135424145047665</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.749849444890302</v>
+        <v>98.336628425419619</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>101.00210493101709</v>
+        <v>100.57945929658935</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>103.2965624307128</v>
+        <v>102.86431558603019</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>94.28773790584431</v>
+        <v>93.893188694882923</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>97.095529585962012</v>
+        <v>96.68923110604436</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.983144190377971</v>
+        <v>99.564762420638786</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.95212442183755</v>
+        <v>102.52131888593641</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>106.00402792027538</v>
+        <v>105.56045162389165</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>94.210717305431089</v>
+        <v>93.816490388946121</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.619254954902587</v>
+        <v>97.210764934115829</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>101.15606786440821</v>
+        <v>100.73277796853952</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.82487041302176</v>
+        <v>104.38622832838624</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.62944900106336</v>
+        <v>108.17488656969674</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>94.138903225791694</v>
+        <v>93.744976816977044</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>98.112460197448016</v>
+        <v>97.701906347964012</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>102.27157569425515</v>
+        <v>101.84361793017939</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>106.62340502460192</v>
+        <v>106.17723693045926</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>111.17531186728201</v>
+        <v>110.71009621411378</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>94.071943710976427</v>
+        <v>93.678297495793771</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>98.576923875742594</v>
+        <v>98.164426467298938</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>103.33247824571799</v>
+        <v>102.90008111048027</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>108.35066903385842</v>
+        <v>107.89727316368561</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>113.64402737391823</v>
+        <v>113.16848132385148</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>94.009510596929545</v>
+        <v>93.616125634550627</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>99.014320906117874</v>
+        <v>98.599993199726214</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>104.34144850445189</v>
+        <v>103.90482930992727</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>110.00948668377376</v>
+        <v>109.54914945293794</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>116.03793331974735</v>
+        <v>115.55236991511232</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.951297903179551</v>
+        <v>93.558156533158424</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>99.426228599058675</v>
+        <v>99.010177255438592</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>105.30102861066031</v>
+        <v>104.86039403107959</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>111.60257030094181</v>
+        <v>111.13556677501705</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>118.35929666115737</v>
+        <v>117.86401945815312</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.897020333249472</v>
+        <v>93.504106088969863</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.814132347189442</v>
+        <v>99.396457811400865</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>106.21363626411728</v>
+        <v>105.76918285679093</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>113.13252473048323</v>
+        <v>112.65911907500917</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>120.61031565888834</v>
+        <v>120.1056190150412</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.675953381640625</v>
+        <v>93.283964197111771</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>101.43979575333258</v>
+        <v>101.01531859157768</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>110.14873940138902</v>
+        <v>109.68781946434899</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.91952765663096</v>
+        <v>119.41772163108993</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.88263298482025</v>
+        <v>130.33495159252428</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>93.520164191984861</v>
+        <v>93.128826910908359</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.64386369779274</v>
+        <v>102.21434808599142</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>113.21049467134377</v>
+        <v>112.73676274885634</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>125.46422258004877</v>
+        <v>124.9392146508918</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>139.69005120074067</v>
+        <v>139.10551496406222</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>93.410377218233435</v>
+        <v>93.019499343277289</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>103.53567168793265</v>
+        <v>103.1024242850559</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>115.59273091931026</v>
+        <v>115.10903047437405</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.99400430083327</v>
+        <v>129.45004139573291</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>147.24147442579073</v>
+        <v>146.62533908469791</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>93.333008694575682</v>
+        <v>92.942454569988769</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>104.19620043544779</v>
+        <v>103.76018903481335</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>117.44625905619812</v>
+        <v>116.95480248008147</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>133.69464477273598</v>
+        <v>133.13519645234547</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>153.71601569609729</v>
+        <v>153.07278748793317</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>153.71601569609729</v>
+        <v>153.07278748793317</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>133.69464477273598</v>
+        <v>133.13519645234547</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>117.44625905619812</v>
+        <v>116.95480248008147</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.19620043544779</v>
+        <v>103.76018903481335</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>93.333008694575682</v>
+        <v>92.942454569988769</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>133.69464477273598</v>
+        <v>133.13519645234547</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>117.44625905619812</v>
+        <v>116.95480248008147</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.19620043544779</v>
+        <v>103.76018903481335</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>117.38342154431811</v>
+        <v>116.89222791321724</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>153.71601569609729</v>
+        <v>153.07278748793317</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>93.333008694575682</v>
+        <v>92.942454569988769</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79</v>
+        <v>79.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20548107287719827</v>
+        <v>0.19891673811808264</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.092676194393338E-2</v>
+        <v>3.1083005312308905E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>121.63079002459784</v>
+        <v>121.12182318226319</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>121.63502640330498</v>
+        <v>121.12604183374607</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20141,11 +20141,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>56.051055310874595</v>
+        <v>55.816508378923139</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.433605381035051</v>
+        <v>64.199058449083594</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.4702525128053151</v>
+        <v>0.46996291203049889</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>70.256051999767735</v>
+        <v>69.9620639319932</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.894494082207387</v>
+        <v>79.600506014432852</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34313923254095424</v>
+        <v>0.34280624314372621</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>87.180132860731689</v>
+        <v>86.81532558678839</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>98.232267780656642</v>
+        <v>97.867460506713343</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.1923733475644549</v>
+        <v>0.19199151783371737</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>98.594258477271538</v>
+        <v>98.181688531788524</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>110.56154939295112</v>
+        <v>110.14897944746811</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.1006895781965635E-2</v>
+        <v>9.0593449194396825E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1709923.9223480001</v>
+        <v>1730486.2986294001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20548107287719827</v>
+        <v>0.19891673811808264</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>121.63079002459784</v>
+        <v>121.12182318226319</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.433605381035051</v>
+        <v>64.199058449083594</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.894494082207387</v>
+        <v>79.600506014432852</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>98.232267780656642</v>
+        <v>97.867460506713343</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>110.56154939295112</v>
+        <v>110.14897944746811</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9172953162396036E-2</v>
+        <v>6.8064994251226946E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7987341772151903E-2</v>
+        <v>5.7298311444652909E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8403161399832593</v>
+        <v>-4.8200617256102989</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7913449700841362</v>
+        <v>8.7545573845690434</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.822669161640221</v>
+        <v>13.764827884160944</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.773697991741098</v>
+        <v>17.699323543119686</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.468774693985001</v>
+        <v>1.4626285724482797</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.94429924556728</v>
+        <v>123.42565147061129</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.72 HKD</v>
+        <v>153.07 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.69 HKD</v>
+        <v>133.14 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>117.45 HKD</v>
+        <v>116.95 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.2 HKD</v>
+        <v>103.76 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>93.33 HKD</v>
+        <v>92.94 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>121.63079002459784</v>
+        <v>121.12182318226319</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21554,11 +21554,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>56.051055310874595</v>
+        <v>55.816508378923139</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.433605381035051</v>
+        <v>64.199058449083594</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21575,11 +21575,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>70.256051999767735</v>
+        <v>69.9620639319932</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.894494082207387</v>
+        <v>79.600506014432852</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>87.180132860731689</v>
+        <v>86.81532558678839</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>98.232267780656642</v>
+        <v>97.867460506713343</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>98.594258477271538</v>
+        <v>98.181688531788524</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>110.56154939295112</v>
+        <v>110.14897944746811</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,12 +21754,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21774,15 +21777,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4FAA19-0268-46B6-854D-ADBC74DEC144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3017D603-5939-4B2F-98D6-2072F2327571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,55 +4995,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.95</v>
+        <v>80.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1730486.2986294001</v>
+        <v>1747801.983919</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19891673811808264</v>
+        <v>0.19578285339228979</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>121.12182318226319</v>
+        <v>121.46081669990011</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,13 +5562,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>64.199058449083594</v>
+        <v>63.604463677696899</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5577,13 +5577,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.600506014432852</v>
+        <v>79.939616145775531</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>97.867460506713343</v>
+        <v>98.110437633644253</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>110.14897944746811</v>
+        <v>110.42376854070062</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8064994251226946E-2</v>
+        <v>6.7579277884272246E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7298311444652909E-2</v>
+        <v>5.6730650154798765E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8200617256102989</v>
+        <v>-4.8335520251835877</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7545573845690434</v>
+        <v>8.779059477793675</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.764827884160944</v>
+        <v>13.803352629756102</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.699323543119686</v>
+        <v>17.748860082366189</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4626285724482797</v>
+        <v>1.4667221502342118</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.07 HKD</v>
+        <v>153.5 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2707815493214861E-2</v>
+        <v>-4.2797983605577808E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.14 HKD</v>
+        <v>133.51 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4643836154445995E-3</v>
+        <v>4.3653900780658396E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.95 HKD</v>
+        <v>117.28 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0465730009150445E-2</v>
+        <v>5.0357611505844682E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.76 HKD</v>
+        <v>104.05 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.4948802061391502E-2</v>
+        <v>9.4831359172600369E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.94 HKD</v>
+        <v>93.2 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13763499730306819</v>
+        <v>0.13750813200166487</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>121.12182318226319</v>
+        <v>121.46081669990011</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,19 +6586,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>8.3825500701604572</v>
+        <v>8.3196131087847078</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.816508378923139</v>
+        <v>55.284850568912191</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>64.199058449083594</v>
+        <v>63.604463677696899</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6607,19 +6607,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>9.6384420824396493</v>
+        <v>9.6497916666666672</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.9620639319932</v>
+        <v>70.289824479108859</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.600506014432852</v>
+        <v>79.939616145775531</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.81532558678839</v>
+        <v>87.0583027137193</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>97.867460506713343</v>
+        <v>98.110437633644253</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.181688531788524</v>
+        <v>98.456477625021037</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>110.14897944746811</v>
+        <v>110.42376854070062</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>74.958691938769988</v>
+        <v>75.168484938827021</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4626285724482797</v>
+        <v>1.4667221502342118</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104328.3398963928</v>
+        <v>-104620.33212373468</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8200617256102989</v>
+        <v>-4.8335520251835877</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>189488.95065117654</v>
+        <v>190019.28882019426</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.7545573845690434</v>
+        <v>8.779059477793675</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>297934.28463455196</v>
+        <v>298768.1375977865</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.764827884160944</v>
+        <v>13.803352629756102</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>383094.8953893357</v>
+        <v>384167.09429424605</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.699323543119689</v>
+        <v>17.748860082366189</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7298311444652909E-2</v>
+        <v>5.6730650154798765E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7298311444652909E-2</v>
+        <v>5.6730650154798765E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4371482176360231E-2</v>
+        <v>5.3832817337461307E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9643527204502817E-2</v>
+        <v>4.9151702786377711E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5703564727954976E-2</v>
+        <v>4.5250773993808051E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4417962903855948</v>
+        <v>5.4570266891549837</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1938751106382393</v>
+        <v>6.211210413694233</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6581271077381405</v>
+        <v>5.6739629691964231</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.5383402001648374</v>
+        <v>5.55384080424259</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0226994088791903</v>
+        <v>5.03675684705106</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8064994251226946E-2</v>
+        <v>6.7579277884272246E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.7471858794724693E-2</v>
+        <v>7.6919014411074099E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.0770820609607765E-2</v>
+        <v>7.0265795284166224E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.9272547844463253E-2</v>
+        <v>6.8778214294025877E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.2823006990358851E-2</v>
+        <v>6.2374697796297958E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.005033042429574E-2</v>
+        <v>7.9257262135262477E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6241574466377859E-2</v>
+        <v>7.5486239982500439E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2577286569373262E-2</v>
+        <v>7.1858254628128698E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7210009170322826E-2</v>
+        <v>6.6544151494332029E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.699323543119686</v>
+        <v>17.748860082366189</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2671499.6719112005</v>
+        <v>2678976.6157628815</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>121.12604183374607</v>
+        <v>121.46504715846669</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>94.158289185704831</v>
+        <v>94.421817663291435</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>94.9228788421307</v>
+        <v>95.188547239100714</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.687468498556541</v>
+        <v>95.955276814909936</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.452058154982396</v>
+        <v>96.722006390719201</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.216647811408251</v>
+        <v>97.488735966528466</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>94.0636703337684</v>
+        <v>94.326933993862909</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.547346951316015</v>
+        <v>95.814763098075645</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>97.045281651034728</v>
+        <v>97.316890189716034</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.557474432924607</v>
+        <v>98.833315268784148</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>100.08392529698554</v>
+        <v>100.3640383352799</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>93.975447628000168</v>
+        <v>94.238464372018143</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>96.135424145047665</v>
+        <v>96.404486191376066</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.336628425419619</v>
+        <v>98.611851161559613</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.57945929658935</v>
+        <v>100.86095922627305</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>102.86431558603019</v>
+        <v>103.15221032922068</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>93.893188694882923</v>
+        <v>94.1559752141209</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.68923110604436</v>
+        <v>96.959843137048253</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.564762420638786</v>
+        <v>99.843422435480747</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.52131888593641</v>
+        <v>102.80825365630905</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.56045162389165</v>
+        <v>105.855892262739</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>93.816490388946121</v>
+        <v>94.079062246384566</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.210764934115829</v>
+        <v>97.482836624347925</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>100.73277796853952</v>
+        <v>101.01470700368547</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.38622832838624</v>
+        <v>104.67838257280047</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.17488656969674</v>
+        <v>108.4776444406962</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>93.744976816977044</v>
+        <v>94.00734852355346</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.701906347964012</v>
+        <v>97.975352635697718</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.84361793017939</v>
+        <v>102.1286559636564</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>106.17723693045926</v>
+        <v>106.47440381661042</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.71009621411378</v>
+        <v>111.01994958295771</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.678297495793771</v>
+        <v>93.940482581519817</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>98.164426467298938</v>
+        <v>98.439167247784752</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>102.90008111048027</v>
+        <v>103.18807595355884</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>107.89727316368561</v>
+        <v>108.19925405542094</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>113.16848132385148</v>
+        <v>113.48521517545369</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.616125634550627</v>
+        <v>93.878136714821764</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.599993199726214</v>
+        <v>98.875953036323565</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>103.90482930992727</v>
+        <v>104.19563622367585</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.54914945293794</v>
+        <v>109.85575358546738</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.55236991511232</v>
+        <v>115.87577574999528</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.558156533158424</v>
+        <v>93.820005370581171</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>99.010177255438592</v>
+        <v>99.287285107581539</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>104.86039403107959</v>
+        <v>105.15387536168917</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>111.13556677501705</v>
+        <v>111.44661094299447</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>117.86401945815312</v>
+        <v>118.19389509500529</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.504106088969863</v>
+        <v>93.765803651009506</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.396457811400865</v>
+        <v>99.674646778416587</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>105.76918285679093</v>
+        <v>106.06520768875082</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.65911907500917</v>
+        <v>112.97442733297392</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>120.1056190150412</v>
+        <v>120.44176839925746</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.283964197111771</v>
+        <v>93.545045630097718</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>101.01531859157768</v>
+        <v>101.29803839619161</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.68781946434899</v>
+        <v>109.9948117039406</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.41772163108993</v>
+        <v>119.75194574083598</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.33495159252428</v>
+        <v>130.6997306434877</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>93.128826910908359</v>
+        <v>93.389474148528137</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.21434808599142</v>
+        <v>102.50042371216898</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>112.73676274885634</v>
+        <v>113.05228831449882</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>124.9392146508918</v>
+        <v>125.28889221313891</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>139.10551496406222</v>
+        <v>139.49484090551044</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>93.019499343277289</v>
+        <v>93.279840596923634</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>103.1024242850559</v>
+        <v>103.39098544246757</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>115.10903047437405</v>
+        <v>115.43119549903327</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.45004139573291</v>
+        <v>129.81234377641081</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>146.62533908469791</v>
+        <v>147.03571137075764</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>92.942454569988769</v>
+        <v>93.202580192149171</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>103.76018903481335</v>
+        <v>104.05059113203619</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.95480248008147</v>
+        <v>117.28213341727842</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>133.13519645234547</v>
+        <v>133.50781277681037</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>153.07278748793317</v>
+        <v>153.50120477328841</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>153.07278748793317</v>
+        <v>153.50120477328841</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>133.13519645234547</v>
+        <v>133.50781277681037</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>116.95480248008147</v>
+        <v>117.28213341727842</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.76018903481335</v>
+        <v>104.05059113203619</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>92.942454569988769</v>
+        <v>93.202580192149171</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>133.13519645234547</v>
+        <v>133.50781277681037</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>116.95480248008147</v>
+        <v>117.28213341727842</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.76018903481335</v>
+        <v>104.05059113203619</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>116.89222791321724</v>
+        <v>117.21938371787425</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>153.07278748793317</v>
+        <v>153.50120477328841</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>92.942454569988769</v>
+        <v>93.202580192149171</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.95</v>
+        <v>80.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19891673811808264</v>
+        <v>0.19578285339228979</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.1083005312308905E-2</v>
+        <v>3.0978794990503863E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>121.12182318226319</v>
+        <v>121.46081669990011</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>121.12604183374607</v>
+        <v>121.46504715846669</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.14612827877009318</v>
+        <v>0.14612827877009316</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20137,23 +20137,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>8.3825500701604572</v>
+        <v>8.3196131087847078</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.816508378923139</v>
+        <v>55.284850568912191</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>64.199058449083594</v>
+        <v>63.604463677696899</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.46996291203049889</v>
+        <v>0.47633759260117658</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20162,23 +20162,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>9.6384420824396493</v>
+        <v>9.6497916666666672</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.9620639319932</v>
+        <v>70.289824479108859</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>79.600506014432852</v>
+        <v>79.939616145775531</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.34280624314372621</v>
+        <v>0.34184852104784769</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20212,11 +20212,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.81532558678839</v>
+        <v>87.0583027137193</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>97.867460506713343</v>
+        <v>98.110437633644253</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.19199151783371737</v>
+        <v>0.19224618852966313</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20237,11 +20237,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>98.181688531788524</v>
+        <v>98.456477625021037</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>110.14897944746811</v>
+        <v>110.42376854070062</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>9.0593449194396825E-2</v>
+        <v>9.0869207527801588E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.95</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20378,14 +20378,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>1730486.2986294001</v>
+        <v>1747801.983919</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19891673811808264</v>
+        <v>0.19578285339228979</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20393,13 +20393,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>121.12182318226319</v>
+        <v>121.46081669990011</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20515,14 +20515,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>64.199058449083594</v>
+        <v>63.604463677696899</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20531,14 +20531,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>79.600506014432852</v>
+        <v>79.939616145775531</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>97.867460506713343</v>
+        <v>98.110437633644253</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>110.14897944746811</v>
+        <v>110.42376854070062</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20584,22 +20584,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20789,10 +20789,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20808,22 +20808,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8064994251226946E-2</v>
+        <v>6.7579277884272246E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7298311444652909E-2</v>
+        <v>5.6730650154798765E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20958,22 +20958,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20981,13 +20981,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8200617256102989</v>
+        <v>-4.8335520251835877</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.7545573845690434</v>
+        <v>8.779059477793675</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21101,7 +21101,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.764827884160944</v>
+        <v>13.803352629756102</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>17.699323543119686</v>
+        <v>17.748860082366189</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21136,33 +21136,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21225,23 +21225,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.4626285724482797</v>
+        <v>1.4667221502342118</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>123.42565147061129</v>
+        <v>123.77109290023448</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,13 +21285,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.07 HKD</v>
+        <v>153.5 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.14 HKD</v>
+        <v>133.51 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>116.95 HKD</v>
+        <v>117.28 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.76 HKD</v>
+        <v>104.05 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>92.94 HKD</v>
+        <v>93.2 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>121.12182318226319</v>
+        <v>121.46081669990011</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21455,13 +21455,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21474,22 +21474,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21550,19 +21550,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>8.3825500701604572</v>
+        <v>8.3196131087847078</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.816508378923139</v>
+        <v>55.284850568912191</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>64.199058449083594</v>
+        <v>63.604463677696899</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21571,19 +21571,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>9.6384420824396493</v>
+        <v>9.6497916666666672</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.9620639319932</v>
+        <v>70.289824479108859</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>79.600506014432852</v>
+        <v>79.939616145775531</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21615,11 +21615,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.81532558678839</v>
+        <v>87.0583027137193</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>97.867460506713343</v>
+        <v>98.110437633644253</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>98.181688531788524</v>
+        <v>98.456477625021037</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>110.14897944746811</v>
+        <v>110.42376854070062</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21658,13 +21658,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21672,13 +21672,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,22 +21715,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21754,15 +21754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21777,12 +21774,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0941.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0941.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3017D603-5939-4B2F-98D6-2072F2327571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F6B18F-0698-4163-929C-C36E56536478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,36 +4995,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>80.75</v>
+        <v>80</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>1747801.983919</v>
+        <v>1731568.52896</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19578285339228979</v>
+        <v>0.19961297901107458</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.138018667316437</v>
+        <v>1.1377999782562256</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>121.46081669990011</v>
+        <v>121.43747600029695</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>63.604463677696899</v>
+        <v>63.593839781655404</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>79.939616145775531</v>
+        <v>79.926108796468156</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>98.110437633644253</v>
+        <v>98.093707944623461</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>110.42376854070062</v>
+        <v>110.40484850434102</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7579277884272246E-2</v>
+        <v>6.8199725393187582E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6730650154798765E-2</v>
+        <v>5.7262500000000008E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.8335520251835877</v>
+        <v>-4.832623178425421</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.779059477793675</v>
+        <v>8.7773724366915591</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>13.803352629756102</v>
+        <v>13.800700087841753</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>17.748860082366189</v>
+        <v>17.74544934610789</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.4667221502342118</v>
+        <v>1.4664402953773119</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>153.5 HKD</v>
+        <v>153.47 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.2797983605577808E-2</v>
+        <v>-4.2791791375741246E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>133.51 HKD</v>
+        <v>133.48 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.3653900780658396E-3</v>
+        <v>4.372188369972765E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>117.28 HKD</v>
+        <v>117.26 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.0357611505844682E-2</v>
+        <v>5.0365036427075204E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.05 HKD</v>
+        <v>104.03 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.4831359172600369E-2</v>
+        <v>9.483942441471617E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>93.2 HKD</v>
+        <v>93.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13750813200166487</v>
+        <v>0.13751684429337915</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>121.46081669990011</v>
+        <v>121.43747600029695</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.284850568912191</v>
+        <v>55.274226672870697</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>63.604463677696899</v>
+        <v>63.593839781655404</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>70.289824479108859</v>
+        <v>70.276317129801484</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>79.939616145775531</v>
+        <v>79.926108796468156</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>87.0583027137193</v>
+        <v>87.041573024698508</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>98.110437633644253</v>
+        <v>98.093707944623461</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>98.456477625021037</v>
+        <v>98.437557588661434</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>110.42376854070062</v>
+        <v>110.40484850434102</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>75.168484938827021</v>
+        <v>75.154040074431649</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.4667221502342118</v>
+        <v>1.4664402953773119</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10476,11 +10476,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-104620.33212373468</v>
+        <v>-104600.22760105133</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.8335520251835877</v>
+        <v>-4.832623178425421</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>190019.28882019426</v>
+        <v>189982.77347920067</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.779059477793675</v>
+        <v>8.7773724366915591</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10510,11 +10510,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>298768.1375977865</v>
+        <v>298710.7243715286</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>13.803352629756102</v>
+        <v>13.800700087841754</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10527,11 +10527,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>384167.09429424605</v>
+        <v>384093.27024967794</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>17.748860082366189</v>
+        <v>17.745449346107893</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14113,24 +14113,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6730650154798765E-2</v>
+        <v>5.7262500000000008E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6730650154798765E-2</v>
+        <v>5.7262500000000008E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.3832817337461307E-2</v>
+        <v>5.4337500000000004E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9151702786377711E-2</v>
+        <v>4.9612500000000004E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5250773993808051E-2</v>
+        <v>4.5675000000000007E-2</v>
       </c>
       <c r="K92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15277,26 +15277,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.4570266891549837</v>
+        <v>5.4559780314550066</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.211210413694233</v>
+        <v>6.210016827150219</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>5.6739629691964231</v>
+        <v>5.6728726236115534</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>5.55384080424259</v>
+        <v>5.5527735421133073</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>5.03675684705106</v>
+        <v>5.0357889511342098</v>
       </c>
       <c r="K123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7579277884272246E-2</v>
+        <v>6.8199725393187582E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6919014411074099E-2</v>
+        <v>7.7625210339377734E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.0265795284166224E-2</v>
+        <v>7.0910907795144418E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.8778214294025877E-2</v>
+        <v>6.9409669276416341E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>6.2374697796297958E-2</v>
+        <v>6.2947361889177628E-2</v>
       </c>
       <c r="K124" s="74" t="str">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -15391,19 +15391,19 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9257262135262477E-2</v>
+        <v>8.0000298967780561E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5486239982500439E-2</v>
+        <v>7.6193923482336376E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1858254628128698E-2</v>
+        <v>7.2531925765267402E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6544151494332029E-2</v>
+        <v>6.7168002914591393E-2</v>
       </c>
       <c r="K125" s="22" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>17.748860082366189</v>
+        <v>17.74544934610789</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.138018667316437</v>
+        <v>1.1377999782562256</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>2678976.6157628815</v>
+        <v>2678461.8062125151</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>121.46504715846669</v>
+        <v>121.44170564591113</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>123.77109290023448</v>
+        <v>123.74730824294804</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>94.421817663291435</v>
+        <v>94.403672953401099</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>95.188547239100714</v>
+        <v>95.170255189474062</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>95.955276814909936</v>
+        <v>95.936837425546969</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>96.722006390719201</v>
+        <v>96.703419661619918</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>97.488735966528466</v>
+        <v>97.470001897692853</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>94.326933993862909</v>
+        <v>94.308807517434914</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>95.814763098075645</v>
+        <v>95.796350710741336</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>97.316890189716034</v>
+        <v>97.298189143881288</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>98.833315268784148</v>
+        <v>98.814322816854798</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>100.3640383352799</v>
+        <v>100.34475172966181</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>94.238464372018143</v>
+        <v>94.220354896487407</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>96.404486191376066</v>
+        <v>96.385960479021037</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>98.611851161559613</v>
+        <v>98.59290126761185</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>100.86095922627305</v>
+        <v>100.84157712910832</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>103.15221032922068</v>
+        <v>103.13238793035897</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>94.1559752141209</v>
+        <v>94.137881590242642</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>96.959843137048253</v>
+        <v>96.941210703694694</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>99.843422435480747</v>
+        <v>99.82423587479613</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>102.80825365630905</v>
+        <v>102.7884973543961</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>105.855892262739</v>
+        <v>105.83555030679257</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>94.079062246384566</v>
+        <v>94.060983402601849</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>97.482836624347925</v>
+        <v>97.464103689168226</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>101.01470700368547</v>
+        <v>100.99529536134901</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>104.67838257280047</v>
+        <v>104.6582668947657</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>108.4776444406962</v>
+        <v>108.45679867181912</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>94.00734852355346</v>
+        <v>93.989283460745611</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>97.975352635697718</v>
+        <v>97.956525055441674</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>102.1286559636564</v>
+        <v>102.10903025765106</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>106.47440381661042</v>
+        <v>106.45394300346565</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>111.01994958295771</v>
+        <v>110.9986152682085</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>93.940482581519817</v>
+        <v>93.922430368105779</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>98.439167247784752</v>
+        <v>98.42025053789969</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>103.18807595355884</v>
+        <v>103.16824666252575</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>108.19925405542094</v>
+        <v>108.17846178384885</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>113.48521517545369</v>
+        <v>113.46340711925271</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>93.878136714821764</v>
+        <v>93.860096482194507</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>98.875953036323565</v>
+        <v>98.856952390843816</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>104.19563622367585</v>
+        <v>104.17561331331567</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>109.85575358546738</v>
+        <v>109.83464299018421</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>115.87577574999528</v>
+        <v>115.8535083081441</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>93.820005370581171</v>
+        <v>93.801976308850669</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>99.287285107581539</v>
+        <v>99.268205417858766</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>105.15387536168917</v>
+        <v>105.13366830987107</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>111.44661094299447</v>
+        <v>111.42519463822651</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>118.19389509500529</v>
+        <v>118.17118218828119</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>93.765803651009506</v>
+        <v>93.747785005033549</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>99.674646778416587</v>
+        <v>99.655492650758674</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>106.06520768875082</v>
+        <v>106.04482550939231</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>112.97442733297392</v>
+        <v>112.95271743308307</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>120.44176839925746</v>
+        <v>120.41862352659597</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>93.545045630097718</v>
+        <v>93.527069406417198</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>101.29803839619161</v>
+        <v>101.27857230705412</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>109.9948117039406</v>
+        <v>109.97367438634599</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>119.75194574083598</v>
+        <v>119.72893342897794</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>130.6997306434877</v>
+        <v>130.67461453416087</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>93.389474148528137</v>
+        <v>93.371527820474185</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>102.50042371216898</v>
+        <v>102.4807265648579</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>113.05228831449882</v>
+        <v>113.03056345233594</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>125.28889221313891</v>
+        <v>125.26481588567617</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>139.49484090551044</v>
+        <v>139.46803467065854</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>93.279840596923634</v>
+        <v>93.261915336765199</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>103.39098544246757</v>
+        <v>103.37111715902888</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>115.43119549903327</v>
+        <v>115.4090134906113</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>129.81234377641081</v>
+        <v>129.78739819310923</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>147.03571137075764</v>
+        <v>147.0074560332481</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19140,23 +19140,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>93.202580192149171</v>
+        <v>93.18466977885204</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>104.05059113203619</v>
+        <v>104.0305960944831</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>117.28213341727842</v>
+        <v>117.25959572060152</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>133.50781277681037</v>
+        <v>133.48215704817818</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>153.50120477328841</v>
+        <v>153.47170698456378</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>153.50120477328841</v>
+        <v>153.47170698456378</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>133.50781277681037</v>
+        <v>133.48215704817818</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>117.28213341727842</v>
+        <v>117.25959572060152</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.05059113203619</v>
+        <v>104.0305960944831</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>93.202580192149171</v>
+        <v>93.18466977885204</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>133.50781277681037</v>
+        <v>133.48215704817818</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>117.28213341727842</v>
+        <v>117.25959572060152</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E24" s="326">
       